--- a/Отчет_HR_3кв_2026_ОТ_и_экология_задачи.xlsx
+++ b/Отчет_HR_3кв_2026_ОТ_и_экология_задачи.xlsx
@@ -14464,7 +14464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I577"/>
+  <dimension ref="A1:I544"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col width="28.77734375" customWidth="1" style="38" min="1" max="1"/>
@@ -22681,15 +22681,15 @@
         </is>
       </c>
     </row>
-    <row r="317" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
+    <row r="317" ht="28.6" customFormat="1" customHeight="1" s="372">
       <c r="A317" s="742" t="inlineStr">
         <is>
-          <t>ОХРАНА ТРУДА. ЛНА, программы, инструкции, журналы</t>
+          <t>Распределение обязанностей и ответственности по охране труда</t>
         </is>
       </c>
       <c r="B317" s="742" t="inlineStr">
         <is>
-          <t>Распределение обязанностей и ответственности по охране труда между руководителями и должностными лицами подразделений</t>
+          <t>Назначение ответственных лиц по охране труда в подразделениях (приказ)</t>
         </is>
       </c>
       <c r="C317" s="743" t="inlineStr">
@@ -22704,215 +22704,255 @@
       </c>
       <c r="E317" s="742" t="n"/>
     </row>
-    <row r="318" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A318" s="754" t="n"/>
+    <row r="318" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A318" s="742" t="inlineStr">
+        <is>
+          <t>Разработка Плана мероприятий по улучшению условий и охраны труда на 2027 г.</t>
+        </is>
+      </c>
       <c r="B318" s="742" t="inlineStr">
         <is>
-          <t>Разработка и утверждение Плана мероприятий по улучшению условий и охраны труда на 2027 г.</t>
+          <t>Формирование мероприятий, согласование с руководителями подразделений, утверждение</t>
         </is>
       </c>
       <c r="C318" s="743" t="inlineStr">
         <is>
+          <t>Соблюдение законодательства, планирование бюджета 2027 г.</t>
+        </is>
+      </c>
+      <c r="D318" s="744" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.</t>
+        </is>
+      </c>
+      <c r="E318" s="742" t="n"/>
+    </row>
+    <row r="319" ht="56.2" customFormat="1" customHeight="1" s="372">
+      <c r="A319" s="742" t="inlineStr">
+        <is>
+          <t>Организация проведения инструктажей по охране труда</t>
+        </is>
+      </c>
+      <c r="B319" s="742" t="inlineStr">
+        <is>
+          <t>Приказ о проведении вводного, первичного и повторного инструктажей; утверждение программ инструктажей; передача журналов регистрации и памяток руководителям подразделений; запуск инструктажей на всех площадках</t>
+        </is>
+      </c>
+      <c r="C319" s="743" t="inlineStr">
+        <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D318" s="744" t="inlineStr">
+      <c r="D319" s="744" t="inlineStr">
         <is>
           <t>Айкешева А.К.</t>
         </is>
       </c>
-      <c r="E318" s="742" t="n"/>
-    </row>
-    <row r="319" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A319" s="754" t="n"/>
-      <c r="B319" s="742" t="inlineStr">
-        <is>
-          <t>Регламентация порядка проведения инструктажей по охране труда (вводного, первичного на рабочем месте, повторного)</t>
-        </is>
-      </c>
-      <c r="C319" s="743" t="inlineStr">
+      <c r="E319" s="742" t="n"/>
+    </row>
+    <row r="320" ht="83.80000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A320" s="742" t="inlineStr">
+        <is>
+          <t>Проведение СОУТ рабочих мест офисного персонала головного подразделения</t>
+        </is>
+      </c>
+      <c r="B320" s="742" t="inlineStr">
+        <is>
+          <t>Заключение договора с подрядчиком; приказ о комиссии, перечень рабочих мест, график; идентификация факторов и измерения; утверждение отчёта; ознакомление работников с картами СОУТ (не позднее 30 кал. дней); подача декларации в ГИТ (при наличии оснований); контроль передачи сведений во ФГИС СОУТ</t>
+        </is>
+      </c>
+      <c r="C320" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D319" s="744" t="inlineStr">
+      <c r="D320" s="744" t="inlineStr">
         <is>
           <t>Айкешева А.К.</t>
         </is>
       </c>
-      <c r="E319" s="742" t="n"/>
-    </row>
-    <row r="320" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A320" s="754" t="n"/>
-      <c r="B320" s="742" t="inlineStr">
-        <is>
-          <t>Разработка и утверждение программ вводного и первичного/повторного инструктажей по охране труда</t>
-        </is>
-      </c>
-      <c r="C320" s="743" t="inlineStr">
+      <c r="E320" s="742" t="n"/>
+    </row>
+    <row r="321" ht="28.6" customFormat="1" customHeight="1" s="372">
+      <c r="A321" s="742" t="inlineStr">
+        <is>
+          <t>Планирование СОУТ обособленных подразделений на 2027 г.</t>
+        </is>
+      </c>
+      <c r="B321" s="742" t="inlineStr">
+        <is>
+          <t>Формирование графика СОУТ: Воронеж, Казань, Жуковский, Ульяновск, Внуково, Машково, Руднево</t>
+        </is>
+      </c>
+      <c r="C321" s="743" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства, планирование бюджета 2027 г.</t>
+        </is>
+      </c>
+      <c r="D321" s="744" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.</t>
+        </is>
+      </c>
+      <c r="E321" s="742" t="n"/>
+    </row>
+    <row r="322" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A322" s="742" t="inlineStr">
+        <is>
+          <t>Организация обучения по охране труда</t>
+        </is>
+      </c>
+      <c r="B322" s="742" t="inlineStr">
+        <is>
+          <t>Обучение работников офиса г. Москва; обучение рабочих, не прошедших обязательное обучение (программы А, Б, В, применение СИЗ, оказание первой помощи)</t>
+        </is>
+      </c>
+      <c r="C322" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D320" s="744" t="inlineStr">
+      <c r="D322" s="744" t="inlineStr">
         <is>
           <t>Айкешева А.К.</t>
         </is>
       </c>
-      <c r="E320" s="742" t="n"/>
-    </row>
-    <row r="321" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A321" s="754" t="n"/>
-      <c r="B321" s="742" t="inlineStr">
-        <is>
-          <t>Обеспечение руководителей подразделений журналами регистрации инструктажей и памятками по их заполнению</t>
-        </is>
-      </c>
-      <c r="C321" s="743" t="inlineStr">
+      <c r="E322" s="742" t="n"/>
+    </row>
+    <row r="323" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A323" s="742" t="inlineStr">
+        <is>
+          <t>Выстраивание системы обучения по охране труда</t>
+        </is>
+      </c>
+      <c r="B323" s="742" t="inlineStr">
+        <is>
+          <t>Разработка Положения о порядке обучения по охране труда и проверки знания требований охраны труда; утверждение перечня работ повышенной опасности</t>
+        </is>
+      </c>
+      <c r="C323" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D321" s="744" t="inlineStr">
+      <c r="D323" s="744" t="inlineStr">
         <is>
           <t>Айкешева А.К.</t>
         </is>
       </c>
-      <c r="E321" s="742" t="n"/>
-    </row>
-    <row r="322" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A322" s="753" t="n"/>
-      <c r="B322" s="742" t="inlineStr">
-        <is>
-          <t>Организация проведения инструктажей по охране труда на всех площадках</t>
-        </is>
-      </c>
-      <c r="C322" s="743" t="inlineStr">
+      <c r="E323" s="742" t="n"/>
+    </row>
+    <row r="324" ht="28.6" customFormat="1" customHeight="1" s="372">
+      <c r="A324" s="742" t="inlineStr">
+        <is>
+          <t>Внедрение стажировки на рабочем месте</t>
+        </is>
+      </c>
+      <c r="B324" s="742" t="inlineStr">
+        <is>
+          <t>Разработка Положения о стажировке, перечня профессий (должностей), программ стажировки, формы стажировочного листа</t>
+        </is>
+      </c>
+      <c r="C324" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D322" s="744" t="inlineStr">
+      <c r="D324" s="744" t="inlineStr">
         <is>
           <t>Айкешева А.К.</t>
         </is>
       </c>
-      <c r="E322" s="742" t="n"/>
-    </row>
-    <row r="323" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A323" s="742" t="inlineStr">
-        <is>
-          <t>ОХРАНА ТРУДА. СОУТ</t>
-        </is>
-      </c>
-      <c r="B323" s="742" t="inlineStr">
-        <is>
-          <t>Заключение договора на проведение СОУТ с выбранным подрядчиком (согласование и загрузка в 1С:ДО)</t>
-        </is>
-      </c>
-      <c r="C323" s="743" t="inlineStr">
+      <c r="E324" s="742" t="n"/>
+    </row>
+    <row r="325" ht="56.2" customFormat="1" customHeight="1" s="372">
+      <c r="A325" s="742" t="inlineStr">
+        <is>
+          <t>Организация периодического медицинского осмотра</t>
+        </is>
+      </c>
+      <c r="B325" s="742" t="inlineStr">
+        <is>
+          <t>Заключение договора на медосмотры и психиатрические освидетельствования; приказ; поимённый список и календарный план; проведение осмотра в выездном формате; получение заключительного акта</t>
+        </is>
+      </c>
+      <c r="C325" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D323" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К., подрядчик</t>
-        </is>
-      </c>
-      <c r="E323" s="742" t="n"/>
-    </row>
-    <row r="324" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A324" s="754" t="n"/>
-      <c r="B324" s="742" t="inlineStr">
-        <is>
-          <t>Формирование комиссии по проведению СОУТ, утверждение перечня рабочих мест и графика проведения СОУТ</t>
-        </is>
-      </c>
-      <c r="C324" s="743" t="inlineStr">
+      <c r="D325" s="744" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.</t>
+        </is>
+      </c>
+      <c r="E325" s="742" t="n"/>
+    </row>
+    <row r="326" ht="28.6" customFormat="1" customHeight="1" s="372">
+      <c r="A326" s="742" t="inlineStr">
+        <is>
+          <t>Организация психиатрического освидетельствования</t>
+        </is>
+      </c>
+      <c r="B326" s="742" t="inlineStr">
+        <is>
+          <t>Определение перечня должностей, разработка Положения, выдача направлений</t>
+        </is>
+      </c>
+      <c r="C326" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D324" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К., подрядчик</t>
-        </is>
-      </c>
-      <c r="E324" s="742" t="n"/>
-    </row>
-    <row r="325" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
-      <c r="A325" s="754" t="n"/>
-      <c r="B325" s="742" t="inlineStr">
-        <is>
-          <t>Проведение СОУТ рабочих мест офисного персонала головного подразделения (идентификация вредных и (или) опасных производственных факторов, исследования и измерения)</t>
-        </is>
-      </c>
-      <c r="C325" s="743" t="inlineStr">
+      <c r="D326" s="744" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.</t>
+        </is>
+      </c>
+      <c r="E326" s="742" t="n"/>
+    </row>
+    <row r="327" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A327" s="742" t="inlineStr">
+        <is>
+          <t>Совершенствование порядка предварительных медицинских осмотров</t>
+        </is>
+      </c>
+      <c r="B327" s="742" t="inlineStr">
+        <is>
+          <t>Подбор альтернативных медицинских организаций в регионах; журнал выдачи направлений; приказ о допуске к работе и отстранении от работы по результатам медосмотров</t>
+        </is>
+      </c>
+      <c r="C327" s="743" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства, оптимизация процесса приёма на работу</t>
+        </is>
+      </c>
+      <c r="D327" s="744" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.</t>
+        </is>
+      </c>
+      <c r="E327" s="742" t="n"/>
+    </row>
+    <row r="328" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A328" s="742" t="inlineStr">
+        <is>
+          <t>Организация обеспечения работников СИЗ</t>
+        </is>
+      </c>
+      <c r="B328" s="742" t="inlineStr">
+        <is>
+          <t>Утверждение Норм бесплатной выдачи СИЗ и Порядка обеспечения СИЗ; назначение ответственных за выдачу; ведение личных карточек учёта выдачи СИЗ</t>
+        </is>
+      </c>
+      <c r="C328" s="743" t="inlineStr">
         <is>
           <t>Соблюдение законодательства</t>
         </is>
       </c>
-      <c r="D325" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К., подрядчик</t>
-        </is>
-      </c>
-      <c r="E325" s="742" t="n"/>
-    </row>
-    <row r="326" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
-      <c r="A326" s="754" t="n"/>
-      <c r="B326" s="742" t="inlineStr">
-        <is>
-          <t>Утверждение отчёта о проведении СОУТ и ознакомление работников с результатами (картами СОУТ) в срок не позднее 30 календарных дней</t>
-        </is>
-      </c>
-      <c r="C326" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D326" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К., подрядчик</t>
-        </is>
-      </c>
-      <c r="E326" s="742" t="n"/>
-    </row>
-    <row r="327" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A327" s="754" t="n"/>
-      <c r="B327" s="742" t="inlineStr">
-        <is>
-          <t>Подача декларации соответствия условий труда в ГИТ; контроль передачи сведений о результатах СОУТ во ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="C327" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D327" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К., подрядчик</t>
-        </is>
-      </c>
-      <c r="E327" s="742" t="n"/>
-    </row>
-    <row r="328" ht="42.40000000000001" customFormat="1" customHeight="1" s="372">
-      <c r="A328" s="753" t="n"/>
-      <c r="B328" s="742" t="inlineStr">
-        <is>
-          <t>Планирование СОУТ обособленных подразделений на 2027 г. (Воронеж, Казань, Жуковский, Ульяновск, Внуково, Машково, Руднево)</t>
-        </is>
-      </c>
-      <c r="C328" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
       <c r="D328" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К., подрядчик</t>
+          <t>Айкешева А.К.</t>
         </is>
       </c>
       <c r="E328" s="742" t="n"/>
@@ -22920,12 +22960,12 @@
     <row r="329" ht="28.6" customFormat="1" customHeight="1" s="38">
       <c r="A329" s="742" t="inlineStr">
         <is>
-          <t>ОХРАНА ТРУДА. Обучение</t>
+          <t>Организация обеспечения аптечками для оказания первой помощи</t>
         </is>
       </c>
       <c r="B329" s="742" t="inlineStr">
         <is>
-          <t>Организация обучения по охране труда работников офиса г. Москва</t>
+          <t>Приказ; назначение ответственных; журнал контроля укомплектованности; доукомплектование аптечек по площадкам</t>
         </is>
       </c>
       <c r="C329" s="743" t="inlineStr">
@@ -22941,10 +22981,14 @@
       <c r="E329" s="742" t="n"/>
     </row>
     <row r="330" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A330" s="753" t="n"/>
+      <c r="A330" s="742" t="inlineStr">
+        <is>
+          <t>Распределение ответственности за экологическую безопасность и обращение с отходами</t>
+        </is>
+      </c>
       <c r="B330" s="742" t="inlineStr">
         <is>
-          <t>Организация обучения рабочих, не прошедших обязательное обучение по охране труда (программы А, Б, В, применение СИЗ, оказание первой помощи)</t>
+          <t>Назначение ответственных в подразделениях (приказ)</t>
         </is>
       </c>
       <c r="C330" s="743" t="inlineStr">
@@ -22954,7 +22998,7 @@
       </c>
       <c r="D330" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E330" s="742" t="n"/>
@@ -22962,12 +23006,12 @@
     <row r="331" ht="42.40000000000001" customFormat="1" customHeight="1" s="511">
       <c r="A331" s="742" t="inlineStr">
         <is>
-          <t>ОХРАНА ТРУДА. Стажировка и РПО</t>
+          <t>Регламентация деятельности в области экологической безопасности и обращения с отходами</t>
         </is>
       </c>
       <c r="B331" s="742" t="inlineStr">
         <is>
-          <t>Выстраивание системы обучения по охране труда: разработка и утверждение Положения о порядке обучения по охране труда и проверки знания требований охраны труда</t>
+          <t>Утверждение приказа и инструкций; проведение инструктажа по экологической безопасности</t>
         </is>
       </c>
       <c r="C331" s="743" t="inlineStr">
@@ -22977,16 +23021,20 @@
       </c>
       <c r="D331" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E331" s="742" t="n"/>
     </row>
     <row r="332" ht="28.6" customFormat="1" customHeight="1" s="511">
-      <c r="A332" s="754" t="n"/>
+      <c r="A332" s="742" t="inlineStr">
+        <is>
+          <t>Проведение экологического аудита площадок</t>
+        </is>
+      </c>
       <c r="B332" s="742" t="inlineStr">
         <is>
-          <t>Определение и утверждение перечня работ повышенной опасности</t>
+          <t>Приказ о комиссии; аудит 8 площадок: технологические процессы, источники выбросов, отходы по ФККО, водопользование</t>
         </is>
       </c>
       <c r="C332" s="743" t="inlineStr">
@@ -22996,16 +23044,20 @@
       </c>
       <c r="D332" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E332" s="742" t="n"/>
     </row>
     <row r="333" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A333" s="754" t="n"/>
+      <c r="A333" s="742" t="inlineStr">
+        <is>
+          <t>Подготовка к постановке площадки Руднево на государственный учёт объектов НВОС</t>
+        </is>
+      </c>
       <c r="B333" s="742" t="inlineStr">
         <is>
-          <t>Внедрение стажировки на рабочем месте: разработка и утверждение Положения о стажировке и перечня профессий (должностей), подлежащих стажировке</t>
+          <t>Сбор и анализ проектной документации; подготовка ТЗ на разработку природоохранной документации (ОВОС/НДВ)</t>
         </is>
       </c>
       <c r="C333" s="743" t="inlineStr">
@@ -23015,16 +23067,20 @@
       </c>
       <c r="D333" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E333" s="742" t="n"/>
     </row>
     <row r="334" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A334" s="753" t="n"/>
+      <c r="A334" s="742" t="inlineStr">
+        <is>
+          <t>Организация обучения по обращению с отходами</t>
+        </is>
+      </c>
       <c r="B334" s="742" t="inlineStr">
         <is>
-          <t>Разработка программ стажировки и формы стажировочного листа</t>
+          <t>Обучение ответственных за обращение с отходами I–IV классов опасности (не менее 1 чел. на площадку)</t>
         </is>
       </c>
       <c r="C334" s="743" t="inlineStr">
@@ -23034,7 +23090,7 @@
       </c>
       <c r="D334" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E334" s="742" t="n"/>
@@ -23042,12 +23098,12 @@
     <row r="335" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
       <c r="A335" s="742" t="inlineStr">
         <is>
-          <t>ОХРАНА ТРУДА. Медицинские осмотры и психиатрические освидетельствования</t>
+          <t>Договорная работа по обращению с отходами</t>
         </is>
       </c>
       <c r="B335" s="742" t="inlineStr">
         <is>
-          <t>Заключение договора с медицинской организацией на проведение медицинских осмотров и психиатрических освидетельствований</t>
+          <t>Доп. соглашения по 3 видам отходов; договоры на вывоз оргтехники и отработанной СОЖ (Руднево); подбор лицензированных операторов в регионах; проверка договоров на вывоз ТКО</t>
         </is>
       </c>
       <c r="C335" s="743" t="inlineStr">
@@ -23057,16 +23113,20 @@
       </c>
       <c r="D335" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E335" s="742" t="n"/>
     </row>
     <row r="336" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A336" s="754" t="n"/>
+      <c r="A336" s="742" t="inlineStr">
+        <is>
+          <t>Организация мест накопления отходов</t>
+        </is>
+      </c>
       <c r="B336" s="742" t="inlineStr">
         <is>
-          <t>Организация периодического медосмотра: издание приказа, утверждение поимённого списка и календарного плана с медицинской организацией</t>
+          <t>Согласование служебной записки; запросы арендодателям; доп. соглашения к договорам аренды; обустройство мест накопления</t>
         </is>
       </c>
       <c r="C336" s="743" t="inlineStr">
@@ -23076,16 +23136,20 @@
       </c>
       <c r="D336" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E336" s="742" t="n"/>
     </row>
     <row r="337" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A337" s="754" t="n"/>
+      <c r="A337" s="742" t="inlineStr">
+        <is>
+          <t>Организация учёта движения отходов</t>
+        </is>
+      </c>
       <c r="B337" s="742" t="inlineStr">
         <is>
-          <t>Проведение периодического медосмотра в выездном формате; получение заключительного акта</t>
+          <t>Приказ; введение журналов движения отходов на всех площадках по форме приказа Минприроды России № 227 (с 01.09.2026)</t>
         </is>
       </c>
       <c r="C337" s="743" t="inlineStr">
@@ -23095,16 +23159,20 @@
       </c>
       <c r="D337" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E337" s="742" t="n"/>
     </row>
-    <row r="338" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A338" s="754" t="n"/>
+    <row r="338" ht="28.6" customFormat="1" customHeight="1" s="38">
+      <c r="A338" s="742" t="inlineStr">
+        <is>
+          <t>Разработка паспортов отходов I–IV классов опасности</t>
+        </is>
+      </c>
       <c r="B338" s="742" t="inlineStr">
         <is>
-          <t>Организация психиатрического освидетельствования: определение перечня должностей, разработка Положения, выдача направлений</t>
+          <t>По площадкам, по итогам экологического аудита</t>
         </is>
       </c>
       <c r="C338" s="743" t="inlineStr">
@@ -23114,16 +23182,20 @@
       </c>
       <c r="D338" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E338" s="742" t="n"/>
     </row>
-    <row r="339" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A339" s="754" t="n"/>
+    <row r="339" ht="56.2" customFormat="1" customHeight="1" s="38">
+      <c r="A339" s="742" t="inlineStr">
+        <is>
+          <t>Подготовка к сдаче экологической отчётности за 2026 г.</t>
+        </is>
+      </c>
       <c r="B339" s="742" t="inlineStr">
         <is>
-          <t>Подбор альтернативных медицинских организаций в регионах для прохождения предварительных медосмотров</t>
+          <t>Доступ в ЛК природопользователя Росприроднадзора (МЧД, УКЭП); данные для отчётности (янв.–март 2027): 2-ТП (воздух), 2-ТП (отходы), 4-ОС, декларация о плате за НВОС, отчёт по ПЭК</t>
         </is>
       </c>
       <c r="C339" s="743" t="inlineStr">
@@ -23133,16 +23205,20 @@
       </c>
       <c r="D339" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E339" s="742" t="n"/>
     </row>
     <row r="340" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A340" s="754" t="n"/>
+      <c r="A340" s="742" t="inlineStr">
+        <is>
+          <t>Организация внутреннего экологического контроля</t>
+        </is>
+      </c>
       <c r="B340" s="742" t="inlineStr">
         <is>
-          <t>Организация учёта направлений на медосмотры (введение журнала выдачи направлений)</t>
+          <t>Ежеквартальные проверки площадок Руднево и Машково; ведение реестра экологической документации компании</t>
         </is>
       </c>
       <c r="C340" s="743" t="inlineStr">
@@ -23152,701 +23228,46 @@
       </c>
       <c r="D340" s="744" t="inlineStr">
         <is>
-          <t>Айкешева А.К.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E340" s="742" t="n"/>
     </row>
-    <row r="341" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A341" s="753" t="n"/>
-      <c r="B341" s="742" t="inlineStr">
-        <is>
-          <t>Регламентация порядка допуска к работе и отстранения от работы по результатам медосмотров</t>
-        </is>
-      </c>
-      <c r="C341" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D341" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E341" s="742" t="n"/>
-    </row>
-    <row r="342" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A342" s="742" t="inlineStr">
-        <is>
-          <t>ОХРАНА ТРУДА. СИЗ</t>
-        </is>
-      </c>
-      <c r="B342" s="742" t="inlineStr">
-        <is>
-          <t>Утверждение Норм бесплатной выдачи СИЗ работникам по профессиям (должностям)</t>
-        </is>
-      </c>
-      <c r="C342" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D342" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E342" s="742" t="n"/>
-    </row>
-    <row r="343" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A343" s="754" t="n"/>
-      <c r="B343" s="742" t="inlineStr">
-        <is>
-          <t>Регламентация порядка обеспечения работников СИЗ (Порядок обеспечения СИЗ)</t>
-        </is>
-      </c>
-      <c r="C343" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D343" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E343" s="742" t="n"/>
-    </row>
-    <row r="344" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A344" s="754" t="n"/>
-      <c r="B344" s="742" t="inlineStr">
-        <is>
-          <t>Распределение ответственности за выдачу и учёт СИЗ в подразделениях</t>
-        </is>
-      </c>
-      <c r="C344" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D344" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E344" s="742" t="n"/>
-    </row>
-    <row r="345" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A345" s="753" t="n"/>
-      <c r="B345" s="742" t="inlineStr">
-        <is>
-          <t>Организация учёта выдачи СИЗ (введение личных карточек учёта выдачи СИЗ)</t>
-        </is>
-      </c>
-      <c r="C345" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D345" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E345" s="742" t="n"/>
-    </row>
-    <row r="346" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A346" s="742" t="inlineStr">
-        <is>
-          <t>ОХРАНА ТРУДА. Аптечки</t>
-        </is>
-      </c>
-      <c r="B346" s="742" t="inlineStr">
-        <is>
-          <t>Регламентация порядка обеспечения аптечками для оказания первой помощи</t>
-        </is>
-      </c>
-      <c r="C346" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D346" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E346" s="742" t="n"/>
-    </row>
-    <row r="347" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A347" s="754" t="n"/>
-      <c r="B347" s="742" t="inlineStr">
-        <is>
-          <t>Распределение ответственности за хранение и укомплектованность аптечек по площадкам</t>
-        </is>
-      </c>
-      <c r="C347" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D347" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E347" s="742" t="n"/>
-    </row>
-    <row r="348" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A348" s="754" t="n"/>
-      <c r="B348" s="742" t="inlineStr">
-        <is>
-          <t>Организация учёта и контроля укомплектованности аптечек (введение журнала)</t>
-        </is>
-      </c>
-      <c r="C348" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D348" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E348" s="742" t="n"/>
-    </row>
-    <row r="349" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A349" s="753" t="n"/>
-      <c r="B349" s="742" t="inlineStr">
-        <is>
-          <t>Доукомплектование аптечек для оказания первой помощи на площадках</t>
-        </is>
-      </c>
-      <c r="C349" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D349" s="744" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E349" s="742" t="n"/>
-    </row>
-    <row r="350" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A350" s="742" t="inlineStr">
-        <is>
-          <t>ЭКОЛОГИЯ. ЛНА</t>
-        </is>
-      </c>
-      <c r="B350" s="742" t="inlineStr">
-        <is>
-          <t>Распределение ответственности за обеспечение экологической безопасности и обращение с отходами в подразделениях</t>
-        </is>
-      </c>
-      <c r="C350" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D350" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E350" s="742" t="n"/>
-    </row>
-    <row r="351" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A351" s="754" t="n"/>
-      <c r="B351" s="742" t="inlineStr">
-        <is>
-          <t>Регламентация деятельности в области экологической безопасности и обращения с отходами (приказ, инструкции)</t>
-        </is>
-      </c>
-      <c r="C351" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D351" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E351" s="742" t="n"/>
-    </row>
-    <row r="352" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A352" s="754" t="n"/>
-      <c r="B352" s="742" t="inlineStr">
-        <is>
-          <t>Проведение инструктажа по экологической безопасности</t>
-        </is>
-      </c>
-      <c r="C352" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D352" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E352" s="742" t="n"/>
-    </row>
-    <row r="353" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A353" s="754" t="n"/>
-      <c r="B353" s="742" t="inlineStr">
-        <is>
-          <t>Формирование комиссии по проведению экологического аудита</t>
-        </is>
-      </c>
-      <c r="C353" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D353" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E353" s="742" t="n"/>
-    </row>
-    <row r="354" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A354" s="754" t="n"/>
-      <c r="B354" s="742" t="inlineStr">
-        <is>
-          <t>Проведение экологического аудита 8 площадок: процессы, источники выбросов, отходы по ФККО, водопользование</t>
-        </is>
-      </c>
-      <c r="C354" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D354" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E354" s="742" t="n"/>
-    </row>
-    <row r="355" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A355" s="754" t="n"/>
-      <c r="B355" s="742" t="inlineStr">
-        <is>
-          <t>Руднево: сбор и анализ проектной документации</t>
-        </is>
-      </c>
-      <c r="C355" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D355" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E355" s="742" t="n"/>
-    </row>
-    <row r="356" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A356" s="753" t="n"/>
-      <c r="B356" s="742" t="inlineStr">
-        <is>
-          <t>Руднево: подготовка ТЗ на разработку документации (ОВОС/НДВ) для постановки объекта на государственный учёт</t>
-        </is>
-      </c>
-      <c r="C356" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D356" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E356" s="742" t="n"/>
-    </row>
-    <row r="357" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A357" s="742" t="inlineStr">
-        <is>
-          <t>ЭКОЛОГИЯ. Обучение</t>
-        </is>
-      </c>
-      <c r="B357" s="742" t="inlineStr">
-        <is>
-          <t>Организация обучения ответственных за обращение с отходами (не менее 1 чел. на площадку)</t>
-        </is>
-      </c>
-      <c r="C357" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D357" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E357" s="742" t="n"/>
-    </row>
-    <row r="358" ht="27.6" customFormat="1" customHeight="1" s="408">
-      <c r="A358" s="742" t="inlineStr">
-        <is>
-          <t>ЭКОЛОГИЯ. Договоры, отходы, журналы</t>
-        </is>
-      </c>
-      <c r="B358" s="742" t="inlineStr">
-        <is>
-          <t>Заключение дополнительных соглашений по 3 видам отходов</t>
-        </is>
-      </c>
-      <c r="C358" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D358" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E358" s="742" t="n"/>
-    </row>
-    <row r="359" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A359" s="754" t="n"/>
-      <c r="B359" s="742" t="inlineStr">
-        <is>
-          <t>Организация вывоза списанной оргтехники (заключение договора)</t>
-        </is>
-      </c>
-      <c r="C359" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D359" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E359" s="742" t="n"/>
-    </row>
-    <row r="360" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A360" s="754" t="n"/>
-      <c r="B360" s="742" t="inlineStr">
-        <is>
-          <t>Организация вывоза отработанной СОЖ с площадки Руднево</t>
-        </is>
-      </c>
-      <c r="C360" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D360" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E360" s="742" t="n"/>
-    </row>
-    <row r="361" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A361" s="754" t="n"/>
-      <c r="B361" s="742" t="inlineStr">
-        <is>
-          <t>Подбор лицензированных операторов по обращению с отходами в регионах и заключение договоров</t>
-        </is>
-      </c>
-      <c r="C361" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D361" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E361" s="742" t="n"/>
-    </row>
-    <row r="362" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A362" s="754" t="n"/>
-      <c r="B362" s="742" t="inlineStr">
-        <is>
-          <t>Проверка договоров на вывоз ТКО по площадкам</t>
-        </is>
-      </c>
-      <c r="C362" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D362" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E362" s="742" t="n"/>
-    </row>
-    <row r="363" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A363" s="754" t="n"/>
-      <c r="B363" s="742" t="inlineStr">
-        <is>
-          <t>Согласование мест накопления отходов (СЗ)</t>
-        </is>
-      </c>
-      <c r="C363" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D363" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E363" s="742" t="n"/>
-    </row>
-    <row r="364" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A364" s="754" t="n"/>
-      <c r="B364" s="742" t="inlineStr">
-        <is>
-          <t>Урегулирование с арендодателями вопросов размещения мест накопления отходов: направление запросов, оформление ДС к договорам аренды</t>
-        </is>
-      </c>
-      <c r="C364" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D364" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E364" s="742" t="n"/>
-    </row>
-    <row r="365" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A365" s="754" t="n"/>
-      <c r="B365" s="742" t="inlineStr">
-        <is>
-          <t>Обустройство мест накопления отходов</t>
-        </is>
-      </c>
-      <c r="C365" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D365" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E365" s="742" t="n"/>
-    </row>
-    <row r="366" ht="42.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A366" s="754" t="n"/>
-      <c r="B366" s="742" t="inlineStr">
-        <is>
-          <t>Организация учёта движения отходов на всех площадках: издание приказа, введение журналов движения отходов (форма по приказу Минприроды № 227, с 01.09.2026)</t>
-        </is>
-      </c>
-      <c r="C366" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D366" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E366" s="742" t="n"/>
-    </row>
-    <row r="367" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A367" s="753" t="n"/>
-      <c r="B367" s="742" t="inlineStr">
-        <is>
-          <t>Разработка паспортов отходов I–IV классов опасности по площадкам (по итогам аудита)</t>
-        </is>
-      </c>
-      <c r="C367" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D367" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E367" s="742" t="n"/>
-    </row>
-    <row r="368" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A368" s="742" t="inlineStr">
-        <is>
-          <t>ЭКОЛОГИЯ. Отчётность</t>
-        </is>
-      </c>
-      <c r="B368" s="742" t="inlineStr">
-        <is>
-          <t>Получение доступа в личный кабинет природопользователя Росприроднадзора (оформление МЧД, УКЭП)</t>
-        </is>
-      </c>
-      <c r="C368" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D368" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E368" s="742" t="n"/>
-    </row>
-    <row r="369" ht="28.6" customFormat="1" customHeight="1" s="38">
-      <c r="A369" s="754" t="n"/>
-      <c r="B369" s="742" t="inlineStr">
-        <is>
-          <t>Подготовка данных для статистической отчётности за 2026 г. (янв.–март 2027): 2-ТП (воздух), 2-ТП (отходы), 4-ОС</t>
-        </is>
-      </c>
-      <c r="C369" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D369" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E369" s="742" t="n"/>
-    </row>
-    <row r="370" ht="27.6" customFormat="1" customHeight="1" s="372">
-      <c r="A370" s="754" t="n"/>
-      <c r="B370" s="742" t="inlineStr">
-        <is>
-          <t>Подготовка декларации о плате за НВОС за 2026 г.</t>
-        </is>
-      </c>
-      <c r="C370" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D370" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E370" s="742" t="n"/>
-    </row>
-    <row r="371" ht="28.6" customFormat="1" customHeight="1" s="372">
-      <c r="A371" s="753" t="n"/>
-      <c r="B371" s="742" t="inlineStr">
-        <is>
-          <t>Подготовка отчёта об организации и о результатах ПЭК за 2026 г.</t>
-        </is>
-      </c>
-      <c r="C371" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D371" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E371" s="742" t="n"/>
-    </row>
-    <row r="372" ht="28.6" customFormat="1" customHeight="1" s="408">
-      <c r="A372" s="742" t="inlineStr">
-        <is>
-          <t>ЭКОЛОГИЯ. Контроль</t>
-        </is>
-      </c>
-      <c r="B372" s="742" t="inlineStr">
-        <is>
-          <t>Организация внутреннего экологического контроля на площадках Руднево и Машково (ежеквартально)</t>
-        </is>
-      </c>
-      <c r="C372" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D372" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E372" s="742" t="n"/>
-    </row>
-    <row r="373" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A373" s="753" t="n"/>
-      <c r="B373" s="742" t="inlineStr">
-        <is>
-          <t>Формирование реестра экологической документации компании</t>
-        </is>
-      </c>
-      <c r="C373" s="743" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D373" s="744" t="inlineStr">
-        <is>
-          <t>Батушин  А.В.</t>
-        </is>
-      </c>
-      <c r="E373" s="742" t="n"/>
-    </row>
-    <row r="374" customFormat="1" s="38">
-      <c r="A374" s="830" t="inlineStr">
+    <row r="341" customFormat="1" s="38">
+      <c r="A341" s="830" t="inlineStr">
         <is>
           <t>Рекрутинг</t>
         </is>
       </c>
-      <c r="B374" s="760" t="n"/>
-      <c r="C374" s="760" t="n"/>
-      <c r="D374" s="760" t="n"/>
-      <c r="E374" s="760" t="n"/>
-    </row>
-    <row r="375" ht="100.8" customFormat="1" customHeight="1" s="38">
-      <c r="A375" s="404" t="inlineStr">
+      <c r="B341" s="760" t="n"/>
+      <c r="C341" s="760" t="n"/>
+      <c r="D341" s="760" t="n"/>
+      <c r="E341" s="760" t="n"/>
+    </row>
+    <row r="342" ht="100.8" customFormat="1" customHeight="1" s="38">
+      <c r="A342" s="404" t="inlineStr">
         <is>
           <t>Набор технологов в АИ СН</t>
         </is>
       </c>
-      <c r="B375" s="403" t="inlineStr">
+      <c r="B342" s="403" t="inlineStr">
         <is>
           <t>набор персонала на критичное направление</t>
         </is>
       </c>
-      <c r="C375" s="403" t="inlineStr">
+      <c r="C342" s="403" t="inlineStr">
         <is>
           <t>Укомплектование отдела</t>
         </is>
       </c>
-      <c r="D375" s="403" t="inlineStr">
+      <c r="D342" s="403" t="inlineStr">
         <is>
           <t>Осипова В.
    Блинова А.
    Новикова Ю.</t>
         </is>
       </c>
-      <c r="E375" s="444" t="inlineStr">
+      <c r="E342" s="444" t="inlineStr">
         <is>
           <t>Осипова В.Г.
    регулярыне статусы, актуализация и приоритезация по ставкам
@@ -23855,23 +23276,23 @@
         </is>
       </c>
     </row>
-    <row r="376" ht="86.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A376" s="512" t="inlineStr">
+    <row r="343" ht="86.40000000000001" customFormat="1" customHeight="1" s="372">
+      <c r="A343" s="512" t="inlineStr">
         <is>
           <t>Доработка концепции внешнего кадрового резерва</t>
         </is>
       </c>
-      <c r="B376" s="513" t="inlineStr">
+      <c r="B343" s="513" t="inlineStr">
         <is>
           <t>Кадровый резерв, который может потребоваться при  расширении производства (теплая база кандидатов)</t>
         </is>
       </c>
-      <c r="C376" s="514" t="inlineStr">
+      <c r="C343" s="514" t="inlineStr">
         <is>
           <t>Масштабирование производства</t>
         </is>
       </c>
-      <c r="D376" s="514" t="inlineStr">
+      <c r="D343" s="514" t="inlineStr">
         <is>
           <t>Пенский А. 
 Осипова В. 
@@ -23881,29 +23302,29 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E376" s="514" t="inlineStr">
+      <c r="E343" s="514" t="inlineStr">
         <is>
           <t xml:space="preserve"> Утверждение схемы добавления резюме в базу; добавление кандидатов в резерв в соответствующими пометками для легкого поиска в дальнейшем </t>
         </is>
       </c>
     </row>
-    <row r="377" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A377" s="508" t="inlineStr">
+    <row r="344" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A344" s="508" t="inlineStr">
         <is>
           <t>Актуализация плана подбора на квартал</t>
         </is>
       </c>
-      <c r="B377" s="509" t="inlineStr">
+      <c r="B344" s="509" t="inlineStr">
         <is>
           <t>Вычитка всех вакансий, актуализация плана с руководителями, корректировки в ХФ и на HH.ru</t>
         </is>
       </c>
-      <c r="C377" s="510" t="inlineStr">
+      <c r="C344" s="510" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D377" s="510" t="inlineStr">
+      <c r="D344" s="510" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.,
@@ -23913,84 +23334,84 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E377" s="510" t="inlineStr">
+      <c r="E344" s="510" t="inlineStr">
         <is>
           <t>План актуализирован</t>
         </is>
       </c>
     </row>
-    <row r="378" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A378" s="840" t="inlineStr">
+    <row r="345" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A345" s="840" t="inlineStr">
         <is>
           <t xml:space="preserve">Организация и контроль работы по проверке соискателей </t>
         </is>
       </c>
-      <c r="B378" s="195" t="inlineStr">
+      <c r="B345" s="195" t="inlineStr">
         <is>
           <t>Проверка кандидатов на различного вида задолженности и наличие ЮР лиц и ИП в системе Кронос</t>
         </is>
       </c>
-      <c r="C378" s="195" t="inlineStr">
+      <c r="C345" s="195" t="inlineStr">
         <is>
           <t>Проверка</t>
         </is>
       </c>
-      <c r="D378" s="195" t="inlineStr">
+      <c r="D345" s="195" t="inlineStr">
         <is>
           <t xml:space="preserve">Ковалева Е.
 Осипова В.
 </t>
         </is>
       </c>
-      <c r="E378" s="195" t="inlineStr">
+      <c r="E345" s="195" t="inlineStr">
         <is>
           <t>Проведено 75 проверок в системе Кронос</t>
         </is>
       </c>
     </row>
-    <row r="379" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A379" s="841" t="n"/>
-      <c r="B379" s="196" t="inlineStr">
+    <row r="346" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A346" s="841" t="n"/>
+      <c r="B346" s="196" t="inlineStr">
         <is>
           <t xml:space="preserve">Точечные консультации с внутренней СБ по спорным вопросам проверок у кандидатов </t>
         </is>
       </c>
-      <c r="C379" s="197" t="inlineStr">
+      <c r="C346" s="197" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D379" s="198" t="inlineStr">
+      <c r="D346" s="198" t="inlineStr">
         <is>
           <t xml:space="preserve">Шибалкова Ю. 
 Ковалева Е.
 </t>
         </is>
       </c>
-      <c r="E379" s="199" t="inlineStr">
+      <c r="E346" s="199" t="inlineStr">
         <is>
           <t>Шибалкова Ю.А.  сбор доп. сведений на 2 кандидатов
 Ковалева Е.С.: сбор доп сведений на 1 кандидата</t>
         </is>
       </c>
     </row>
-    <row r="380" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A380" s="690" t="inlineStr">
+    <row r="347" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A347" s="690" t="inlineStr">
         <is>
           <t>Предварительные мед.осмотры</t>
         </is>
       </c>
-      <c r="B380" s="65" t="inlineStr">
+      <c r="B347" s="65" t="inlineStr">
         <is>
           <t>Направление на предварительные мед. осмотры</t>
         </is>
       </c>
-      <c r="C380" s="185" t="inlineStr">
+      <c r="C347" s="185" t="inlineStr">
         <is>
           <t>Проверка перед трудоустройством</t>
         </is>
       </c>
-      <c r="D380" s="186" t="inlineStr">
+      <c r="D347" s="186" t="inlineStr">
         <is>
           <t>Ковалева Е.
 Блинова А. 
@@ -23998,7 +23419,7 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E380" s="182" t="inlineStr">
+      <c r="E347" s="182" t="inlineStr">
         <is>
           <t>Исматова В.: было сделано около 10 направлений на медосмотр Блинова: выдано 6 направлений на медосмотр
 Шибалкова Ю.А.: выдано 5 направлений на медосмотр
@@ -24006,29 +23427,29 @@
         </is>
       </c>
     </row>
-    <row r="381" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A381" s="71" t="inlineStr">
+    <row r="348" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A348" s="71" t="inlineStr">
         <is>
           <t>Сбор рекомендаций с прошлых мест работ кандидатов</t>
         </is>
       </c>
-      <c r="B381" s="184" t="inlineStr">
+      <c r="B348" s="184" t="inlineStr">
         <is>
           <t>Для руководящих и точечных должностей по запросу собираем рекомендации по кандидату перед выставлением оффера</t>
         </is>
       </c>
-      <c r="C381" s="186" t="inlineStr">
+      <c r="C348" s="186" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D381" s="182" t="inlineStr">
+      <c r="D348" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.                              Блинова А.И</t>
         </is>
       </c>
-      <c r="E381" s="186" t="inlineStr">
+      <c r="E348" s="186" t="inlineStr">
         <is>
           <t>Блинова А.И.Собраны рекомендации на 2-х кандидатов
 Шибалкова Ю.А.  сбор рекомендации на 4-х кандидатов
@@ -24036,23 +23457,23 @@
         </is>
       </c>
     </row>
-    <row r="382" ht="138" customFormat="1" customHeight="1" s="38">
-      <c r="A382" s="691" t="inlineStr">
+    <row r="349" ht="138" customFormat="1" customHeight="1" s="38">
+      <c r="A349" s="691" t="inlineStr">
         <is>
           <t>Мониторинг рынка труда</t>
         </is>
       </c>
-      <c r="B382" s="184" t="inlineStr">
+      <c r="B349" s="184" t="inlineStr">
         <is>
           <t>Сбор и отражение в табличной форме данных</t>
         </is>
       </c>
-      <c r="C382" s="182" t="inlineStr">
+      <c r="C349" s="182" t="inlineStr">
         <is>
           <t>Оценка ситуации на рынке труда для корректировки кадровой политики</t>
         </is>
       </c>
-      <c r="D382" s="181" t="inlineStr">
+      <c r="D349" s="181" t="inlineStr">
         <is>
           <t>Осипова В.
 Блинова А.
@@ -24061,7 +23482,7 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E382" s="182" t="inlineStr">
+      <c r="E349" s="182" t="inlineStr">
         <is>
           <t>Осипова В.Г. Сбор и сведение данных и выводов по зарплатной аналитике, предоствление руководству
 Блинова А.И.: мониторинг рынка труда по 2 должностям - столяр и сборщик стеклопластиковых изделий
@@ -24070,23 +23491,23 @@
         </is>
       </c>
     </row>
-    <row r="383" ht="124.2" customFormat="1" customHeight="1" s="38">
-      <c r="A383" s="691" t="inlineStr">
+    <row r="350" ht="124.2" customFormat="1" customHeight="1" s="38">
+      <c r="A350" s="691" t="inlineStr">
         <is>
           <t>Отчетность еженедельная/квартальная</t>
         </is>
       </c>
-      <c r="B383" s="191" t="inlineStr">
+      <c r="B350" s="191" t="inlineStr">
         <is>
           <t>Заполнение форм отчетности</t>
         </is>
       </c>
-      <c r="C383" s="193" t="inlineStr">
+      <c r="C350" s="193" t="inlineStr">
         <is>
           <t>Выполнение плана подбора</t>
         </is>
       </c>
-      <c r="D383" s="193" t="inlineStr">
+      <c r="D350" s="193" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.,
@@ -24097,7 +23518,7 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E383" s="193" t="inlineStr">
+      <c r="E350" s="193" t="inlineStr">
         <is>
           <t>Блинова А.И - заполнение отчета по рекрутингу каждую пятницу. Заполнение квартального отчета в конце квартала
 Шибалкова Ю. - заполнение отчета по рекрутингу каждую пятницу, еженедельный отчет по выходам новых сотрудников,  квартального отчета в конце квартала.
@@ -24106,23 +23527,23 @@
         </is>
       </c>
     </row>
-    <row r="384" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A384" s="200" t="inlineStr">
+    <row r="351" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A351" s="200" t="inlineStr">
         <is>
           <t>Реферальная программа</t>
         </is>
       </c>
-      <c r="B384" s="201" t="inlineStr">
+      <c r="B351" s="201" t="inlineStr">
         <is>
           <t>Отслеживание окончания ИС сотрудников по рекомендации</t>
         </is>
       </c>
-      <c r="C384" s="202" t="inlineStr">
+      <c r="C351" s="202" t="inlineStr">
         <is>
           <t>Увеличение воронки кандидатов, развитие HR бренда работодателя</t>
         </is>
       </c>
-      <c r="D384" s="202" t="inlineStr">
+      <c r="D351" s="202" t="inlineStr">
         <is>
           <t>Осипова В.,
 Шибалкова Ю. 
@@ -24131,36 +23552,36 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E384" s="202" t="inlineStr">
+      <c r="E351" s="202" t="inlineStr">
         <is>
           <t>Фиксация данных по рекомендателям, отслеживание результатов работы рекомендованных сотрудников</t>
         </is>
       </c>
     </row>
-    <row r="385" ht="124.2" customFormat="1" customHeight="1" s="38">
-      <c r="A385" s="45" t="inlineStr">
+    <row r="352" ht="124.2" customFormat="1" customHeight="1" s="38">
+      <c r="A352" s="45" t="inlineStr">
         <is>
           <t>Обучение по подбору персонала для руководителей</t>
         </is>
       </c>
-      <c r="B385" s="45" t="inlineStr">
+      <c r="B352" s="45" t="inlineStr">
         <is>
           <t>Разработка программы тренинга</t>
         </is>
       </c>
-      <c r="C385" s="46" t="inlineStr">
+      <c r="C352" s="46" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D385" s="46" t="inlineStr">
+      <c r="D352" s="46" t="inlineStr">
         <is>
           <t>Новикова Ю.
 Аншакова И.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E385" s="46" t="inlineStr">
+      <c r="E352" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">- Разработана презентация для обучения
 - Подобран материал для проведения практических заданий
@@ -24170,88 +23591,88 @@
         </is>
       </c>
     </row>
-    <row r="386" ht="33.6" customFormat="1" customHeight="1" s="38">
-      <c r="A386" s="45" t="inlineStr">
+    <row r="353" ht="33.6" customFormat="1" customHeight="1" s="38">
+      <c r="A353" s="45" t="inlineStr">
         <is>
           <t>Планирование подбора на 2027 год</t>
         </is>
       </c>
-      <c r="B386" s="45" t="inlineStr">
+      <c r="B353" s="45" t="inlineStr">
         <is>
           <t>Сбор данных по подразделениям</t>
         </is>
       </c>
-      <c r="C386" s="46" t="inlineStr">
+      <c r="C353" s="46" t="inlineStr">
         <is>
           <t>Планирование 2027 год</t>
         </is>
       </c>
-      <c r="D386" s="46" t="inlineStr">
+      <c r="D353" s="46" t="inlineStr">
         <is>
           <t>Осипова В.Г.</t>
         </is>
       </c>
-      <c r="E386" s="46" t="inlineStr">
+      <c r="E353" s="46" t="inlineStr">
         <is>
           <t>Собраны первичные данные для плана подбора 2027, сведение первой версии плана на момент 09.2026</t>
         </is>
       </c>
     </row>
-    <row r="387" customFormat="1" s="38">
-      <c r="A387" s="830" t="inlineStr">
+    <row r="354" customFormat="1" s="38">
+      <c r="A354" s="830" t="inlineStr">
         <is>
           <t>Адаптация</t>
         </is>
       </c>
-      <c r="B387" s="760" t="n"/>
-      <c r="C387" s="760" t="n"/>
-      <c r="D387" s="760" t="n"/>
-      <c r="E387" s="760" t="n"/>
-    </row>
-    <row r="388" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A388" s="417" t="inlineStr">
+      <c r="B354" s="760" t="n"/>
+      <c r="C354" s="760" t="n"/>
+      <c r="D354" s="760" t="n"/>
+      <c r="E354" s="760" t="n"/>
+    </row>
+    <row r="355" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A355" s="417" t="inlineStr">
         <is>
           <t>Переезд в Руднево</t>
         </is>
       </c>
-      <c r="B388" s="418" t="inlineStr">
+      <c r="B355" s="418" t="inlineStr">
         <is>
           <t>Организация доставки сотрудников на площадку, организация питания, предложения п обустройству офиса, бытовых условий.</t>
         </is>
       </c>
-      <c r="C388" s="371" t="inlineStr">
+      <c r="C355" s="371" t="inlineStr">
         <is>
           <t>Организация комфортных условий труда для сотрудников</t>
         </is>
       </c>
-      <c r="D388" s="373" t="inlineStr">
+      <c r="D355" s="373" t="inlineStr">
         <is>
           <t>Пенский А.</t>
         </is>
       </c>
-      <c r="E388" s="423" t="inlineStr">
+      <c r="E355" s="423" t="inlineStr">
         <is>
           <t>проработаны варианты по организации столовых, произведены расчеты плановой численности персонала</t>
         </is>
       </c>
     </row>
-    <row r="389" ht="96.59999999999999" customFormat="1" customHeight="1" s="38">
-      <c r="A389" s="842" t="inlineStr">
+    <row r="356" ht="96.59999999999999" customFormat="1" customHeight="1" s="38">
+      <c r="A356" s="842" t="inlineStr">
         <is>
           <t>Онбординг</t>
         </is>
       </c>
-      <c r="B389" s="727" t="inlineStr">
+      <c r="B356" s="727" t="inlineStr">
         <is>
           <t>Проведение краткой экскурсии для новых сотрудников и выдача Welcome Kit, знакомство с руководителем</t>
         </is>
       </c>
-      <c r="C389" s="178" t="inlineStr">
+      <c r="C356" s="178" t="inlineStr">
         <is>
           <t>Адаптация новичков, снижение времени на включение в работу, снижение текучести.</t>
         </is>
       </c>
-      <c r="D389" s="178" t="inlineStr">
+      <c r="D356" s="178" t="inlineStr">
         <is>
           <t>Осипова В.
 Шибалкова Ю. 
@@ -24261,7 +23682,7 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E389" s="181" t="inlineStr">
+      <c r="E356" s="181" t="inlineStr">
         <is>
           <t xml:space="preserve">Исматова В.: краткая экскурсия, выдача Welcome Kit в производственном цехе Машково/Руднево
 Шибалкова Ю. экскурсия, выдача Welcome Kit в офисе Мск
@@ -24271,25 +23692,25 @@
         </is>
       </c>
     </row>
-    <row r="390" customFormat="1" s="38"/>
-    <row r="391" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A391" s="691" t="inlineStr">
+    <row r="357" customFormat="1" s="38"/>
+    <row r="358" ht="69" customFormat="1" customHeight="1" s="408">
+      <c r="A358" s="691" t="inlineStr">
         <is>
           <t>Общение по результатам ИС</t>
         </is>
       </c>
-      <c r="B391" s="701" t="inlineStr">
+      <c r="B358" s="701" t="inlineStr">
         <is>
           <t>Встречи с сотрудниками на ИС и во время ИС
 Подготовка чек-листа для прошедших ИС и шаблона СЗ для изменений по результатам ИС</t>
         </is>
       </c>
-      <c r="C391" s="181" t="inlineStr">
+      <c r="C358" s="181" t="inlineStr">
         <is>
           <t>Мониторинг состояния новичков на ИС, снижение текучести персонала, обсуждение дальнейшего развития</t>
         </is>
       </c>
-      <c r="D391" s="181" t="inlineStr">
+      <c r="D358" s="181" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -24297,7 +23718,7 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E391" s="181" t="inlineStr">
+      <c r="E358" s="181" t="inlineStr">
         <is>
           <t>Исматова В.: проведено 9 встреч по результатам ИС                            Блинова А.И. - проведено 11 встреч по результатам ИС
 Шибалкова Ю.: роведено 5 встреч по результатам ИС
@@ -24306,30 +23727,30 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A392" s="440" t="inlineStr">
+    <row r="359" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A359" s="440" t="inlineStr">
         <is>
           <t>Общение по результатам ИС/работы - переговоры по увольнению сотрудника</t>
         </is>
       </c>
-      <c r="B392" s="441" t="inlineStr">
+      <c r="B359" s="441" t="inlineStr">
         <is>
           <t>Встреча с сотрудником на протяжении ИС, с проблемными зонами</t>
         </is>
       </c>
-      <c r="C392" s="442" t="inlineStr">
+      <c r="C359" s="442" t="inlineStr">
         <is>
           <t>Повышение эффективности команды, "отсев" сотрудников, которые не устраивают работодателя</t>
         </is>
       </c>
-      <c r="D392" s="442" t="inlineStr">
+      <c r="D359" s="442" t="inlineStr">
         <is>
           <t>Осипова В.
 Ковалева Е.
 Исматова В.</t>
         </is>
       </c>
-      <c r="E392" s="442" t="inlineStr">
+      <c r="E359" s="442" t="inlineStr">
         <is>
           <t>Исматова В.: проведена 1 встреча по увольнению 
 Ковалева Е.: проведено 3 встречи по увольнениюч
@@ -24337,67 +23758,67 @@
         </is>
       </c>
     </row>
-    <row r="393" customFormat="1" s="38">
-      <c r="A393" s="843" t="inlineStr">
+    <row r="360" customFormat="1" s="38">
+      <c r="A360" s="843" t="inlineStr">
         <is>
           <t>Материальная и не материальная мотивация</t>
         </is>
       </c>
-      <c r="B393" s="805" t="n"/>
-      <c r="C393" s="805" t="n"/>
-      <c r="D393" s="805" t="n"/>
-      <c r="E393" s="747" t="n"/>
-    </row>
-    <row r="394" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A394" s="410" t="inlineStr">
+      <c r="B360" s="805" t="n"/>
+      <c r="C360" s="805" t="n"/>
+      <c r="D360" s="805" t="n"/>
+      <c r="E360" s="747" t="n"/>
+    </row>
+    <row r="361" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A361" s="410" t="inlineStr">
         <is>
           <t>Питание сотрудников</t>
         </is>
       </c>
-      <c r="B394" s="410" t="inlineStr">
+      <c r="B361" s="410" t="inlineStr">
         <is>
           <t>Сопровождение процесса, решение проблем</t>
         </is>
       </c>
-      <c r="C394" s="443" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D394" s="443" t="inlineStr">
+      <c r="C361" s="443" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D361" s="443" t="inlineStr">
         <is>
           <t>Пенский А.К.</t>
         </is>
       </c>
-      <c r="E394" s="443" t="inlineStr">
+      <c r="E361" s="443" t="inlineStr">
         <is>
           <t>Отладка электронного документооборота с контрагентом. Работа по минимизации списания обедов. Разбор конфликтных ситуаций. Заведение и отслеживание заявок на оплату.</t>
         </is>
       </c>
     </row>
-    <row r="395" ht="151.8" customFormat="1" customHeight="1" s="38">
-      <c r="A395" s="727" t="inlineStr">
+    <row r="362" ht="151.8" customFormat="1" customHeight="1" s="38">
+      <c r="A362" s="727" t="inlineStr">
         <is>
           <t>ДМС</t>
         </is>
       </c>
-      <c r="B395" s="727" t="inlineStr">
+      <c r="B362" s="727" t="inlineStr">
         <is>
           <t>Подключение сотрудников со сроком работы от 6 месяцев</t>
         </is>
       </c>
-      <c r="C395" s="443" t="inlineStr">
+      <c r="C362" s="443" t="inlineStr">
         <is>
           <t>Нематериальная мотивация</t>
         </is>
       </c>
-      <c r="D395" s="443" t="inlineStr">
+      <c r="D362" s="443" t="inlineStr">
         <is>
           <t>Осипова В. 
 Блинова А.И.</t>
         </is>
       </c>
-      <c r="E395" s="443" t="inlineStr">
+      <c r="E362" s="443" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В. организация со стороны АИ СН встреч с представителями ДМС на площадках в Машково и Руднево; курирование ДМС в АИ СН, решение вопросов по программе, отслеживание проблем при перезаключении догвора с июля 2026
 Блинова А.И.: оперативное внесение изменений в списки на ДМС (отключение сотрудников)/формирование списков на включение к программе ДМС 1 раз в месяц. Консультация сотрудников по программе ДМС
@@ -24405,209 +23826,209 @@
         </is>
       </c>
     </row>
-    <row r="396" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A396" s="706" t="inlineStr">
+    <row r="363" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A363" s="706" t="inlineStr">
         <is>
           <t>Подписка на журнал Кадровое дело</t>
         </is>
       </c>
-      <c r="B396" s="701" t="inlineStr">
+      <c r="B363" s="701" t="inlineStr">
         <is>
           <t>Оформление подписки, рассылка ежемесечных выпусков</t>
         </is>
       </c>
-      <c r="C396" s="182" t="inlineStr">
+      <c r="C363" s="182" t="inlineStr">
         <is>
           <t>Рассылка коллегам из HR отдела и ОУП свежих выпусков журнала, актуальных статей</t>
         </is>
       </c>
-      <c r="D396" s="182" t="inlineStr">
+      <c r="D363" s="182" t="inlineStr">
         <is>
           <t xml:space="preserve">Шибалкова Ю. </t>
         </is>
       </c>
-      <c r="E396" s="182" t="inlineStr">
+      <c r="E363" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю.: Рассылка коллегам из HR отдела и ОУП свежих выпусков журнала, актуальных статей на регулярной основе  по мере получения новый публикаций</t>
         </is>
       </c>
     </row>
-    <row r="397" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A397" s="190" t="inlineStr">
+    <row r="364" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A364" s="190" t="inlineStr">
         <is>
           <t>Реализация плана обучения персонала</t>
         </is>
       </c>
-      <c r="B397" s="191" t="inlineStr">
+      <c r="B364" s="191" t="inlineStr">
         <is>
           <t>План обучения согласован - актуализация планов на квартал, организация курсов</t>
         </is>
       </c>
-      <c r="C397" s="193" t="inlineStr">
+      <c r="C364" s="193" t="inlineStr">
         <is>
           <t>Повышение компетенций сотрудников по профильным направлениям</t>
         </is>
       </c>
-      <c r="D397" s="193" t="inlineStr">
+      <c r="D364" s="193" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В. 
 Шибалкова Ю. </t>
         </is>
       </c>
-      <c r="E397" s="193" t="inlineStr">
+      <c r="E364" s="193" t="inlineStr">
         <is>
           <t>Корректировка и актуализация плана на обучение. Отслеживание прохождения текущих курсов. Сбор закрывающих документов. Организовно 6 обучениий
 Осипова В. Шибалкова Ю. - предложения по корректировке плана обучения в соответствии с сокращением бюджета</t>
         </is>
       </c>
     </row>
-    <row r="398" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A398" s="405" t="inlineStr">
+    <row r="365" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A365" s="405" t="inlineStr">
         <is>
           <t>Кадровый резерв</t>
         </is>
       </c>
-      <c r="B398" s="406" t="inlineStr">
+      <c r="B365" s="406" t="inlineStr">
         <is>
           <t>Концепция, начало проекта</t>
         </is>
       </c>
-      <c r="C398" s="407" t="inlineStr">
+      <c r="C365" s="407" t="inlineStr">
         <is>
           <t>Проработка дорожной карты проекта
 Старт проекта по созданию внутреннего кадрового резерва из разных блоков компании (ИТР, пр-во, АУП)</t>
         </is>
       </c>
-      <c r="D398" s="407" t="inlineStr">
+      <c r="D365" s="407" t="inlineStr">
         <is>
           <t>Осипова В.</t>
         </is>
       </c>
-      <c r="E398" s="193" t="inlineStr">
+      <c r="E365" s="193" t="inlineStr">
         <is>
           <t>с 21 сентября запуск, с 25 сентября сбор заявок на участие в программе</t>
         </is>
       </c>
     </row>
-    <row r="399" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A399" s="405" t="inlineStr">
+    <row r="366" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A366" s="405" t="inlineStr">
         <is>
           <t xml:space="preserve">Проработка изменений зарплатной сетки и штатного расписанияпо производству (Машково Руднево) </t>
         </is>
       </c>
-      <c r="B399" s="406" t="inlineStr">
+      <c r="B366" s="406" t="inlineStr">
         <is>
           <t>Совместно с ЗГД по произвоству работа по унификации зп сетки с АИ Казань в соответствии с рыночной зп</t>
         </is>
       </c>
-      <c r="C399" s="407" t="inlineStr">
+      <c r="C366" s="407" t="inlineStr">
         <is>
           <t>Приведение производственной зп сетки в соответствии с АИ Казань и рынком, повышение мотивации производственного персонала</t>
         </is>
       </c>
-      <c r="D399" s="407" t="inlineStr">
+      <c r="D366" s="407" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.Г.</t>
         </is>
       </c>
-      <c r="E399" s="193" t="inlineStr">
+      <c r="E366" s="193" t="inlineStr">
         <is>
           <t xml:space="preserve">Подготовка аналитических данных по рыночной зп для производственных должностей, совместно с ЗГД по произвоству работа по унификации зп сетки с АИ Казань в соответствии с рыночной зп. 
 Данные переданы в ОУП для изменений </t>
         </is>
       </c>
     </row>
-    <row r="400" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A400" s="405" t="inlineStr">
+    <row r="367" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A367" s="405" t="inlineStr">
         <is>
           <t>Договоры на практику (студенты по рекомендации наших сотрудников, закрытие учебной практики нашим сотрудникам)</t>
         </is>
       </c>
-      <c r="B400" s="406" t="inlineStr">
+      <c r="B367" s="406" t="inlineStr">
         <is>
           <t>Проведение практики</t>
         </is>
       </c>
-      <c r="C400" s="407" t="inlineStr">
+      <c r="C367" s="407" t="inlineStr">
         <is>
           <t>Предоставление практики студентам</t>
         </is>
       </c>
-      <c r="D400" s="407" t="inlineStr">
+      <c r="D367" s="407" t="inlineStr">
         <is>
           <t>Осипова В.</t>
         </is>
       </c>
-      <c r="E400" s="193" t="inlineStr">
+      <c r="E367" s="193" t="inlineStr">
         <is>
           <t>Согласовано и подписано 2 договора на практику</t>
         </is>
       </c>
     </row>
-    <row r="401" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A401" s="405" t="inlineStr">
+    <row r="368" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A368" s="405" t="inlineStr">
         <is>
           <t>Мероприятие для сотрудников 10+ лет</t>
         </is>
       </c>
-      <c r="B401" s="406" t="inlineStr">
+      <c r="B368" s="406" t="inlineStr">
         <is>
           <t>Помощь с сбором списка сотрудников на мероприятие</t>
         </is>
       </c>
-      <c r="C401" s="407" t="inlineStr">
+      <c r="C368" s="407" t="inlineStr">
         <is>
           <t>Повышение лояльности персонала</t>
         </is>
       </c>
-      <c r="D401" s="407" t="inlineStr">
+      <c r="D368" s="407" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.
 Шибалкова Ю.</t>
         </is>
       </c>
-      <c r="E401" s="193" t="inlineStr">
+      <c r="E368" s="193" t="inlineStr">
         <is>
           <t>Помощь с составлением списка сотрудников (с учетом стажа в ГК), обзвон сотрудников для подтверждения участия и просчета фин.количества</t>
         </is>
       </c>
     </row>
-    <row r="402" customFormat="1" s="38">
-      <c r="A402" s="825" t="inlineStr">
+    <row r="369" customFormat="1" s="38">
+      <c r="A369" s="825" t="inlineStr">
         <is>
           <t>Развитие  HR-бренда</t>
         </is>
       </c>
-      <c r="B402" s="805" t="n"/>
-      <c r="C402" s="805" t="n"/>
-      <c r="D402" s="805" t="n"/>
-      <c r="E402" s="747" t="n"/>
-    </row>
-    <row r="403" ht="96.59999999999999" customFormat="1" customHeight="1" s="38">
-      <c r="A403" s="405" t="inlineStr">
+      <c r="B369" s="805" t="n"/>
+      <c r="C369" s="805" t="n"/>
+      <c r="D369" s="805" t="n"/>
+      <c r="E369" s="747" t="n"/>
+    </row>
+    <row r="370" ht="96.59999999999999" customFormat="1" customHeight="1" s="372">
+      <c r="A370" s="405" t="inlineStr">
         <is>
           <t>Happy Job</t>
         </is>
       </c>
-      <c r="B403" s="406" t="inlineStr">
+      <c r="B370" s="406" t="inlineStr">
         <is>
           <t>Органиация,проведение встреч с руководителями/сотрудниками подразделений по результатам опроса вовлеченности персонала Happy Job</t>
         </is>
       </c>
-      <c r="C403" s="407" t="inlineStr">
+      <c r="C370" s="407" t="inlineStr">
         <is>
           <t>Повышение показателей вовлеченности и лояльности</t>
         </is>
       </c>
-      <c r="D403" s="409" t="inlineStr">
+      <c r="D370" s="409" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.Г.</t>
         </is>
       </c>
-      <c r="E403" s="407" t="inlineStr">
+      <c r="E370" s="407" t="inlineStr">
         <is>
           <t>Пенский А. - формирование загрузочного файла, работа с подразделениями, информирование руководителей, сопровождение информационной компании
 Осипова В.Г. - участи в проработке структуры опроса, логики исследования; 
@@ -24615,24 +24036,24 @@
         </is>
       </c>
     </row>
-    <row r="404" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A404" s="706" t="inlineStr">
+    <row r="371" ht="55.2" customFormat="1" customHeight="1" s="372">
+      <c r="A371" s="706" t="inlineStr">
         <is>
           <t>Встречи с сотрудниками по запросу от руководителей/размещенному резюме/exit-интервью</t>
         </is>
       </c>
-      <c r="B404" s="701" t="inlineStr">
+      <c r="B371" s="701" t="inlineStr">
         <is>
           <t xml:space="preserve">По запросу
 </t>
         </is>
       </c>
-      <c r="C404" s="181" t="inlineStr">
+      <c r="C371" s="181" t="inlineStr">
         <is>
           <t>Сбор информации о причинах увольнений и проблемах компании для проработки и устранения проблем</t>
         </is>
       </c>
-      <c r="D404" s="182" t="inlineStr">
+      <c r="D371" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -24640,7 +24061,7 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E404" s="182" t="inlineStr">
+      <c r="E371" s="182" t="inlineStr">
         <is>
           <t>Исматова В.: проведено 4 exit-интервью                                              Блинова А.И.: проведено 3 exit интервью
 Шибалкова Ю.: проведено 1 exit интервью
@@ -24648,101 +24069,101 @@
         </is>
       </c>
     </row>
-    <row r="405" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A405" s="833" t="inlineStr">
+    <row r="372" ht="55.2" customFormat="1" customHeight="1" s="408">
+      <c r="A372" s="833" t="inlineStr">
         <is>
           <t>Поздравления с ДР сотрудников</t>
         </is>
       </c>
-      <c r="B405" s="701" t="inlineStr">
+      <c r="B372" s="701" t="inlineStr">
         <is>
           <t xml:space="preserve">Актуализация списков именинников на будущий месяц, сбор фотографий для поздравлений. Сбор/отправка в филиалы подарков на ДР для сотрудников </t>
         </is>
       </c>
-      <c r="C405" s="834" t="inlineStr">
+      <c r="C372" s="834" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D405" s="181" t="inlineStr">
+      <c r="D372" s="181" t="inlineStr">
         <is>
           <t>Шибалкова Ю. Котов И.</t>
         </is>
       </c>
-      <c r="E405" s="181" t="inlineStr">
+      <c r="E372" s="181" t="inlineStr">
         <is>
           <t>Шибалкова Ю.: Актуализация и выгрузка списков именинников
 Котов И.: Обработка списков для составления рассылок и документации</t>
         </is>
       </c>
     </row>
-    <row r="406" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A406" s="753" t="n"/>
-      <c r="B406" s="701" t="inlineStr">
+    <row r="373" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A373" s="753" t="n"/>
+      <c r="B373" s="701" t="inlineStr">
         <is>
           <t>Составление, подписание приказов, списков, ведомостей, договоров дарения на подарки</t>
         </is>
       </c>
-      <c r="C406" s="753" t="n"/>
-      <c r="D406" s="181" t="inlineStr">
+      <c r="C373" s="753" t="n"/>
+      <c r="D373" s="181" t="inlineStr">
         <is>
           <t>Котов И.
 Исматова В.</t>
         </is>
       </c>
-      <c r="E406" s="181" t="inlineStr">
+      <c r="E373" s="181" t="inlineStr">
         <is>
           <t>Исматова В.: подписание договоров и ведомостей на площадке Машково
 Котов И.: Составление приказов и договоров дарения</t>
         </is>
       </c>
     </row>
-    <row r="407" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A407" s="405" t="inlineStr">
+    <row r="374" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A374" s="405" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
       </c>
-      <c r="B407" s="406" t="inlineStr">
+      <c r="B374" s="406" t="inlineStr">
         <is>
           <t>Повышение узнаваемости</t>
         </is>
       </c>
-      <c r="C407" s="406" t="inlineStr">
+      <c r="C374" s="406" t="inlineStr">
         <is>
           <t>Развитие бренда
 Контроль реализации исполнения ТЗ на брендирование корп.транспорта со стороны Отдела дизайна</t>
         </is>
       </c>
-      <c r="D407" s="407" t="inlineStr">
+      <c r="D374" s="407" t="inlineStr">
         <is>
           <t>ПенскийА.К.
 ОсиповаВ.Г.</t>
         </is>
       </c>
-      <c r="E407" s="445" t="inlineStr">
+      <c r="E374" s="445" t="inlineStr">
         <is>
           <t>задача была в прошлом квартале, почему она дублируется? Хзадача получилась переходящей: с нашей стороны все сделано, передано в отдел дизайна. Как они сделают - продолжим реализацию с заказом оклейки корпоративных автобусов ПЕРЕНЕСЕНА НА СЛЕДУЮЩИЙ ГОД</t>
         </is>
       </c>
     </row>
-    <row r="408" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A408" s="706" t="inlineStr">
+    <row r="375" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A375" s="706" t="inlineStr">
         <is>
           <t>Работа с СУЗами, ВУЗами, ярмарки вакансий</t>
         </is>
       </c>
-      <c r="B408" s="701" t="inlineStr">
+      <c r="B375" s="701" t="inlineStr">
         <is>
           <t>Актуализация информации по сотрудничеству, участие в ярмарках вакансий</t>
         </is>
       </c>
-      <c r="C408" s="181" t="inlineStr">
+      <c r="C375" s="181" t="inlineStr">
         <is>
           <t>Привлечь молодых специалистов на открытые вакансии , повышение узнаваемости бренда АИ СН</t>
         </is>
       </c>
-      <c r="D408" s="181" t="inlineStr">
+      <c r="D375" s="181" t="inlineStr">
         <is>
           <t>Осипова В.,
 Исматова В.
@@ -24750,67 +24171,67 @@
 Блинова А.</t>
         </is>
       </c>
-      <c r="E408" s="182" t="inlineStr">
+      <c r="E375" s="182" t="inlineStr">
         <is>
           <t>Исматова В.: внесено предложение о сотрудничестве с КАДР 26, тк есть действующие сотрудники из данного колледжа</t>
         </is>
       </c>
     </row>
-    <row r="409" customFormat="1" s="38">
-      <c r="A409" s="825" t="inlineStr">
+    <row r="376" customFormat="1" s="38">
+      <c r="A376" s="825" t="inlineStr">
         <is>
           <t>Автоматизация процессов и аналитика</t>
         </is>
       </c>
-      <c r="B409" s="805" t="n"/>
-      <c r="C409" s="805" t="n"/>
-      <c r="D409" s="805" t="n"/>
-      <c r="E409" s="747" t="n"/>
-    </row>
-    <row r="410" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A410" s="691" t="inlineStr">
+      <c r="B376" s="805" t="n"/>
+      <c r="C376" s="805" t="n"/>
+      <c r="D376" s="805" t="n"/>
+      <c r="E376" s="747" t="n"/>
+    </row>
+    <row r="377" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A377" s="691" t="inlineStr">
         <is>
           <t>Аудит Хантфлоу</t>
         </is>
       </c>
-      <c r="B410" s="691" t="inlineStr">
+      <c r="B377" s="691" t="inlineStr">
         <is>
           <t>Проведение аудит по качеству ведения базы согласно нашей инструкции, фиксация замечаний и дальнейшая отработка</t>
         </is>
       </c>
-      <c r="C410" s="691" t="inlineStr">
+      <c r="C377" s="691" t="inlineStr">
         <is>
           <t>Повышение качества подбора, снижение сроков</t>
         </is>
       </c>
-      <c r="D410" s="195" t="inlineStr">
+      <c r="D377" s="195" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В. </t>
         </is>
       </c>
-      <c r="E410" s="691" t="inlineStr">
+      <c r="E377" s="691" t="inlineStr">
         <is>
           <t>Проведение дежурств по аудиту базы, передача в отдел отработки замечаний по аудиту</t>
         </is>
       </c>
     </row>
-    <row r="411" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A411" s="691" t="inlineStr">
+    <row r="378" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A378" s="691" t="inlineStr">
         <is>
           <t xml:space="preserve"> Хантфлоу</t>
         </is>
       </c>
-      <c r="B411" s="701" t="inlineStr">
+      <c r="B378" s="701" t="inlineStr">
         <is>
           <t>Ведение базы кандидатов, отслеживание воронки подбора.</t>
         </is>
       </c>
-      <c r="C411" s="182" t="inlineStr">
+      <c r="C378" s="182" t="inlineStr">
         <is>
           <t>Повышение качества подбора, снижение сроков</t>
         </is>
       </c>
-      <c r="D411" s="182" t="inlineStr">
+      <c r="D378" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -24819,30 +24240,30 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E411" s="182" t="inlineStr">
+      <c r="E378" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю.: ведение базы ХФ, открытие/закрытие вакансий, отработка замечаний по Аудиту
 Ковалева Е.: ведение базы ХФ, добавление новых вакансий, закрытие неактуальных вакансий, аудит</t>
         </is>
       </c>
     </row>
-    <row r="412" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A412" s="691" t="inlineStr">
+    <row r="379" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A379" s="691" t="inlineStr">
         <is>
           <t>Аналитика резюме кандидатов. Работающих сотрудников, обновляющих резюме</t>
         </is>
       </c>
-      <c r="B412" s="184" t="inlineStr">
+      <c r="B379" s="184" t="inlineStr">
         <is>
           <t>Отслеживание баз резюме, аналитика</t>
         </is>
       </c>
-      <c r="C412" s="182" t="inlineStr">
+      <c r="C379" s="182" t="inlineStr">
         <is>
           <t>Удержание персонала</t>
         </is>
       </c>
-      <c r="D412" s="182" t="inlineStr">
+      <c r="D379" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -24850,115 +24271,115 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E412" s="182" t="inlineStr">
+      <c r="E379" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю.: периодический просмотр базы НН.ru на отслеживание сотрудников, обновляющих резюме
 Ковалева Е.: еженедельный отсмотр резюме действующих сотрудников, точечное информирование руководителей</t>
         </is>
       </c>
     </row>
-    <row r="413" ht="35.55" customFormat="1" customHeight="1" s="38">
-      <c r="A413" s="691" t="inlineStr">
+    <row r="380" ht="35.55" customFormat="1" customHeight="1" s="38">
+      <c r="A380" s="691" t="inlineStr">
         <is>
           <t>Бюджет 2027</t>
         </is>
       </c>
-      <c r="B413" s="184" t="inlineStr">
+      <c r="B380" s="184" t="inlineStr">
         <is>
           <t>Сбор информации</t>
         </is>
       </c>
-      <c r="C413" s="182" t="inlineStr">
+      <c r="C380" s="182" t="inlineStr">
         <is>
           <t>Планирование 2027, передача данных в финансовый блок</t>
         </is>
       </c>
-      <c r="D413" s="182" t="inlineStr">
+      <c r="D380" s="182" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E413" s="182" t="inlineStr">
+      <c r="E380" s="182" t="inlineStr">
         <is>
           <t>Составление бюджета с учетом всех планируемых затрат и стратегических задач на 2027 год</t>
         </is>
       </c>
     </row>
-    <row r="414" ht="18.45" customFormat="1" customHeight="1" s="38">
-      <c r="A414" s="825" t="inlineStr">
+    <row r="381" ht="18.45" customFormat="1" customHeight="1" s="38">
+      <c r="A381" s="825" t="inlineStr">
         <is>
           <t>Развитие и обучение</t>
         </is>
       </c>
-      <c r="B414" s="805" t="n"/>
-      <c r="C414" s="805" t="n"/>
-      <c r="D414" s="805" t="n"/>
-      <c r="E414" s="747" t="n"/>
-    </row>
-    <row r="415" ht="34.2" customFormat="1" customHeight="1" s="38">
-      <c r="A415" s="370" t="inlineStr">
+      <c r="B381" s="805" t="n"/>
+      <c r="C381" s="805" t="n"/>
+      <c r="D381" s="805" t="n"/>
+      <c r="E381" s="747" t="n"/>
+    </row>
+    <row r="382" ht="34.2" customFormat="1" customHeight="1" s="38">
+      <c r="A382" s="370" t="inlineStr">
         <is>
           <t>Актуализация процесса планирования обучения</t>
         </is>
       </c>
-      <c r="B415" s="370" t="inlineStr">
+      <c r="B382" s="370" t="inlineStr">
         <is>
           <t>подготовка к бюджетированию 2027</t>
         </is>
       </c>
-      <c r="C415" s="371" t="inlineStr">
+      <c r="C382" s="371" t="inlineStr">
         <is>
           <t xml:space="preserve">Развитие процессов </t>
         </is>
       </c>
-      <c r="D415" s="371" t="inlineStr">
+      <c r="D382" s="371" t="inlineStr">
         <is>
           <t>Пенский А., ОсиповаВ.</t>
         </is>
       </c>
-      <c r="E415" s="371" t="n"/>
-    </row>
-    <row r="416" ht="27" customFormat="1" customHeight="1" s="38">
-      <c r="A416" s="417" t="inlineStr">
+      <c r="E382" s="371" t="n"/>
+    </row>
+    <row r="383" ht="27" customFormat="1" customHeight="1" s="38">
+      <c r="A383" s="417" t="inlineStr">
         <is>
           <t>Разработка програаммы и Организация обучения кадрового резерва</t>
         </is>
       </c>
-      <c r="B416" s="417" t="inlineStr">
+      <c r="B383" s="417" t="inlineStr">
         <is>
           <t>повышение управленческих компетенций резервистов</t>
         </is>
       </c>
-      <c r="C416" s="418" t="inlineStr">
+      <c r="C383" s="418" t="inlineStr">
         <is>
           <t>развитие потенциала Компании</t>
         </is>
       </c>
-      <c r="D416" s="418" t="inlineStr">
+      <c r="D383" s="418" t="inlineStr">
         <is>
           <t>Пенский А., Осипова В.</t>
         </is>
       </c>
-      <c r="E416" s="418" t="n"/>
-    </row>
-    <row r="417" ht="111.3" customFormat="1" customHeight="1" s="38">
-      <c r="A417" s="727" t="inlineStr">
+      <c r="E383" s="418" t="n"/>
+    </row>
+    <row r="384" ht="111.3" customFormat="1" customHeight="1" s="38">
+      <c r="A384" s="727" t="inlineStr">
         <is>
           <t>Аттестация</t>
         </is>
       </c>
-      <c r="B417" s="515" t="inlineStr">
+      <c r="B384" s="515" t="inlineStr">
         <is>
           <t>Проведение аттестации действующих сотрудников для повышения категории/разряда и уровня заработной платы, в соответствии с ШР</t>
         </is>
       </c>
-      <c r="C417" s="193" t="inlineStr">
+      <c r="C384" s="193" t="inlineStr">
         <is>
           <t>Повышение категорий и разрядов действующих сотрудников</t>
         </is>
       </c>
-      <c r="D417" s="193" t="inlineStr">
+      <c r="D384" s="193" t="inlineStr">
         <is>
           <t>Осипова В.
 Шибалкова Ю.
@@ -24967,7 +24388,7 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E417" s="193" t="inlineStr">
+      <c r="E384" s="193" t="inlineStr">
         <is>
           <t>Осипова В.: сведение итогов аттестации для согласования с руководством, передача данных в ОУП для проведения изменений;
 Исматова В.: проведено 11 аттестаций
@@ -24977,125 +24398,125 @@
         </is>
       </c>
     </row>
-    <row r="418" customFormat="1" s="38">
-      <c r="A418" s="825" t="inlineStr">
+    <row r="385" customFormat="1" s="38">
+      <c r="A385" s="825" t="inlineStr">
         <is>
           <t>ЛНА и регламентация процессов</t>
         </is>
       </c>
-      <c r="B418" s="805" t="n"/>
-      <c r="C418" s="805" t="n"/>
-      <c r="D418" s="805" t="n"/>
-      <c r="E418" s="747" t="n"/>
-    </row>
-    <row r="419" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A419" s="691" t="inlineStr">
+      <c r="B385" s="805" t="n"/>
+      <c r="C385" s="805" t="n"/>
+      <c r="D385" s="805" t="n"/>
+      <c r="E385" s="747" t="n"/>
+    </row>
+    <row r="386" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A386" s="691" t="inlineStr">
         <is>
           <t>ЛНА</t>
         </is>
       </c>
-      <c r="B419" s="701" t="inlineStr">
+      <c r="B386" s="701" t="inlineStr">
         <is>
           <t>Внедрение Положений об адаптации и наставничестве</t>
         </is>
       </c>
-      <c r="C419" s="181" t="inlineStr">
+      <c r="C386" s="181" t="inlineStr">
         <is>
           <t>Систематизация процесса, инструктирование руководителей.</t>
         </is>
       </c>
-      <c r="D419" s="181" t="inlineStr">
+      <c r="D386" s="181" t="inlineStr">
         <is>
           <t>Осипова В.</t>
         </is>
       </c>
-      <c r="E419" s="419" t="inlineStr">
+      <c r="E386" s="419" t="inlineStr">
         <is>
           <t>Участие в проработке системы мотивации для наставников, для утверждения в Положении об оплате труда
 По итогам 2 итерация нового процесса соглсования ЛНА по ГК - отработаны все замечания, переданы на 3 круг согласования</t>
         </is>
       </c>
     </row>
-    <row r="420" ht="35.25" customFormat="1" customHeight="1" s="38">
-      <c r="A420" s="691" t="inlineStr">
+    <row r="387" ht="35.25" customFormat="1" customHeight="1" s="38">
+      <c r="A387" s="691" t="inlineStr">
         <is>
           <t>Комиссия по этике и служебному поведению работников</t>
         </is>
       </c>
-      <c r="B420" s="184" t="inlineStr">
+      <c r="B387" s="184" t="inlineStr">
         <is>
           <t>Соблюдение норм и правил Кодекса</t>
         </is>
       </c>
-      <c r="C420" s="182" t="inlineStr">
+      <c r="C387" s="182" t="inlineStr">
         <is>
           <t>Систематизация процесса</t>
         </is>
       </c>
-      <c r="D420" s="182" t="inlineStr">
+      <c r="D387" s="182" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E420" s="182" t="inlineStr">
+      <c r="E387" s="182" t="inlineStr">
         <is>
           <t>Первое заседание комисси по этике и служебному поведению работников по 2 инцидентам (драка в Машково и оскорбления в эл.почте).
 Издание приказа о созыве комиссии, сбор письменных показаний, проведение заседания.</t>
         </is>
       </c>
     </row>
-    <row r="421" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A421" s="691" t="inlineStr">
+    <row r="388" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A388" s="691" t="inlineStr">
         <is>
           <t>Аудит ОС Кволити+ (по ГОСТ Р 58876)</t>
         </is>
       </c>
-      <c r="B421" s="184" t="inlineStr">
+      <c r="B388" s="184" t="inlineStr">
         <is>
           <t>Устранение замечаний по итогам вненего аудита</t>
         </is>
       </c>
-      <c r="C421" s="182" t="inlineStr">
+      <c r="C388" s="182" t="inlineStr">
         <is>
           <t>СМК</t>
         </is>
       </c>
-      <c r="D421" s="182" t="inlineStr">
+      <c r="D388" s="182" t="inlineStr">
         <is>
           <t>Осипова В.
 Ковалева Е.</t>
         </is>
       </c>
-      <c r="E421" s="182" t="inlineStr">
+      <c r="E388" s="182" t="inlineStr">
         <is>
           <t>Устранений замечаний в части процедуры аттестации персонала - Положение об аттестации переработано и внесены соответствующие изменения, отвечающие требованиям аудиторов.</t>
         </is>
       </c>
     </row>
-    <row r="422" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A422" s="691" t="inlineStr">
+    <row r="389" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A389" s="691" t="inlineStr">
         <is>
           <t xml:space="preserve">Прохождение внутреннего аудита СМК отдела подбора и развития персонала </t>
         </is>
       </c>
-      <c r="B422" s="184" t="inlineStr">
+      <c r="B389" s="184" t="inlineStr">
         <is>
           <t>Подведение итогов по результатам аудита и корректирующим действиям 2025 года; прохождение планового аудита 2026</t>
         </is>
       </c>
-      <c r="C422" s="182" t="inlineStr">
+      <c r="C389" s="182" t="inlineStr">
         <is>
           <t>Плановый аудит СМК</t>
         </is>
       </c>
-      <c r="D422" s="182" t="inlineStr">
+      <c r="D389" s="182" t="inlineStr">
         <is>
           <t>Осипова В.
 Ковалева Е.</t>
         </is>
       </c>
-      <c r="E422" s="182" t="inlineStr">
+      <c r="E389" s="182" t="inlineStr">
         <is>
           <t>Подготовка у аудиту - сбор необходимых документов и систематизация; 
 В сентябре успешно пройден внутренний аудит СМК и приняты итоги по плану 2025-2026 года;
@@ -25103,95 +24524,95 @@
         </is>
       </c>
     </row>
-    <row r="423" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A423" s="691" t="inlineStr">
+    <row r="390" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A390" s="691" t="inlineStr">
         <is>
           <t>План мероприятий по достижению целей в области качества дирекции о персоналу на 2026г.</t>
         </is>
       </c>
-      <c r="B423" s="184" t="inlineStr">
+      <c r="B390" s="184" t="inlineStr">
         <is>
           <t>СМК</t>
         </is>
       </c>
-      <c r="C423" s="182" t="inlineStr">
+      <c r="C390" s="182" t="inlineStr">
         <is>
           <t>СМК</t>
         </is>
       </c>
-      <c r="D423" s="182" t="inlineStr">
+      <c r="D390" s="182" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E423" s="182" t="inlineStr">
+      <c r="E390" s="182" t="inlineStr">
         <is>
           <t>С отделом СМК согласован план мероприятий для закрытия целей в области качества в части дирекции по персоналу (вопросы по обучению и наставничеству)</t>
         </is>
       </c>
     </row>
-    <row r="424" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A424" s="691" t="inlineStr">
+    <row r="391" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A391" s="691" t="inlineStr">
         <is>
           <t>Аудит Росавиации по ФАП-145</t>
         </is>
       </c>
-      <c r="B424" s="184" t="inlineStr">
+      <c r="B391" s="184" t="inlineStr">
         <is>
           <t>СМК</t>
         </is>
       </c>
-      <c r="C424" s="182" t="inlineStr">
+      <c r="C391" s="182" t="inlineStr">
         <is>
           <t>СМК</t>
         </is>
       </c>
-      <c r="D424" s="182" t="inlineStr">
+      <c r="D391" s="182" t="inlineStr">
         <is>
           <t>Осипова В.Г.</t>
         </is>
       </c>
-      <c r="E424" s="182" t="inlineStr">
+      <c r="E391" s="182" t="inlineStr">
         <is>
           <t>По запросу СМК участие в совещании по внешнему аудиту Росавиации, подготовка по возможным вопросам в части персонала. Аудит пройден успешно.</t>
         </is>
       </c>
     </row>
-    <row r="425" customFormat="1" s="38">
-      <c r="A425" s="844" t="inlineStr">
+    <row r="392" customFormat="1" s="38">
+      <c r="A392" s="844" t="inlineStr">
         <is>
           <t>Корпоративные коммуникации</t>
         </is>
       </c>
-      <c r="B425" s="832" t="n"/>
-      <c r="C425" s="832" t="n"/>
-      <c r="D425" s="832" t="n"/>
-      <c r="E425" s="749" t="n"/>
-    </row>
-    <row r="426" ht="273.6" customFormat="1" customHeight="1" s="38">
-      <c r="A426" s="390" t="inlineStr">
+      <c r="B392" s="832" t="n"/>
+      <c r="C392" s="832" t="n"/>
+      <c r="D392" s="832" t="n"/>
+      <c r="E392" s="749" t="n"/>
+    </row>
+    <row r="393" ht="273.6" customFormat="1" customHeight="1" s="38">
+      <c r="A393" s="390" t="inlineStr">
         <is>
           <t>Развитие каналов коммуникаций в компании</t>
         </is>
       </c>
-      <c r="B426" s="391" t="inlineStr">
+      <c r="B393" s="391" t="inlineStr">
         <is>
           <t>Использование текущих каналов и продвижение, предложения по развитию (почтовые рассылки, инфодоски, чаты)</t>
         </is>
       </c>
-      <c r="C426" s="392" t="inlineStr">
+      <c r="C393" s="392" t="inlineStr">
         <is>
           <t>Повышение качества коммуникаций и обмен новостями в компании</t>
         </is>
       </c>
-      <c r="D426" s="393" t="inlineStr">
+      <c r="D393" s="393" t="inlineStr">
         <is>
           <t>Котов И.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E426" s="392" t="inlineStr">
+      <c r="E393" s="392" t="inlineStr">
         <is>
           <t xml:space="preserve">   Котов, Осипова: 1.Закуплены дополнительные инфодоски для подразделения в Руднево, а также ТВ в ПП №6 (Воронеж).
 Котов И.:
@@ -25203,28 +24624,28 @@
         </is>
       </c>
     </row>
-    <row r="427" ht="86.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A427" s="374" t="inlineStr">
+    <row r="394" ht="86.40000000000001" customFormat="1" customHeight="1" s="38">
+      <c r="A394" s="374" t="inlineStr">
         <is>
           <t>Корпоративные рассылки и ТВ</t>
         </is>
       </c>
-      <c r="B427" s="394" t="inlineStr">
+      <c r="B394" s="394" t="inlineStr">
         <is>
           <t>Плановые и внеплановые коммуникации: дни рождения, выходы новых сотрудников, реферальная программа и другие инфоповоды</t>
         </is>
       </c>
-      <c r="C427" s="374" t="inlineStr">
+      <c r="C394" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D427" s="376" t="inlineStr">
+      <c r="D394" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E427" s="392" t="inlineStr">
+      <c r="E394" s="392" t="inlineStr">
         <is>
           <t xml:space="preserve">1.Реализована 321 коммуникация по группе компаний, 255 из которых подготовлены лично.
    2.Всего реализовано: 233 рассылки, 250 новостей в чаты, 113 новостей на портал, 33 новости на корпоративное ТВ.
@@ -25232,29 +24653,29 @@
         </is>
       </c>
     </row>
-    <row r="428" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A428" s="374" t="inlineStr">
+    <row r="395" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A395" s="374" t="inlineStr">
         <is>
           <t>Настольный теннис ЛЧБ</t>
         </is>
       </c>
-      <c r="B428" s="395" t="inlineStr">
+      <c r="B395" s="395" t="inlineStr">
         <is>
           <t>Организация участия сотрудников в турнирах по настольному теннису, ведение информационной кампании</t>
         </is>
       </c>
-      <c r="C428" s="374" t="inlineStr">
+      <c r="C395" s="374" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D428" s="292" t="inlineStr">
+      <c r="D395" s="292" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.</t>
         </is>
       </c>
-      <c r="E428" s="397" t="inlineStr">
+      <c r="E395" s="397" t="inlineStr">
         <is>
           <t>1.Проведено освещение корпоративного тенниса и будущей Лиги чемпионов бизнеса среди АИ СН и ЦТП.
    2.Команда пополнилась на 2 игроков.
@@ -25262,28 +24683,28 @@
         </is>
       </c>
     </row>
-    <row r="429" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A429" s="374" t="inlineStr">
+    <row r="396" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A396" s="374" t="inlineStr">
         <is>
           <t>Волейбол</t>
         </is>
       </c>
-      <c r="B429" s="389" t="inlineStr">
+      <c r="B396" s="389" t="inlineStr">
         <is>
           <t>Создание команды, информационная кампания по набору, сопровождение тренировок</t>
         </is>
       </c>
-      <c r="C429" s="374" t="inlineStr">
+      <c r="C396" s="374" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D429" s="376" t="inlineStr">
+      <c r="D396" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E429" s="390" t="inlineStr">
+      <c r="E396" s="390" t="inlineStr">
         <is>
           <t>1.Оказана помощь в создании команды по волейболу.
    2.Проведена информационная кампания по набору в команду.
@@ -25291,28 +24712,28 @@
         </is>
       </c>
     </row>
-    <row r="430" ht="288" customFormat="1" customHeight="1" s="38">
-      <c r="A430" s="374" t="inlineStr">
+    <row r="397" ht="288" customFormat="1" customHeight="1" s="38">
+      <c r="A397" s="374" t="inlineStr">
         <is>
           <t>Видео-контент</t>
         </is>
       </c>
-      <c r="B430" s="395" t="inlineStr">
+      <c r="B397" s="395" t="inlineStr">
         <is>
           <t>Съёмка, монтаж и озвучка корпоративных роликов: фильмы, интервью, ОТ, мероприятия</t>
         </is>
       </c>
-      <c r="C430" s="374" t="inlineStr">
+      <c r="C397" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D430" s="376" t="inlineStr">
+      <c r="D397" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E430" s="390" t="inlineStr">
+      <c r="E397" s="390" t="inlineStr">
         <is>
           <t>1.Разработан сценарий совместно с А. Прошкиным по второму фильму «Культурный код».
    2.Снят второй корпоративный фильм в Воронеже и Москве.
@@ -25324,23 +24745,23 @@
         </is>
       </c>
     </row>
-    <row r="431" ht="273.6" customFormat="1" customHeight="1" s="38">
-      <c r="A431" s="374" t="inlineStr">
+    <row r="398" ht="273.6" customFormat="1" customHeight="1" s="38">
+      <c r="A398" s="374" t="inlineStr">
         <is>
           <t>Летнее мероприятие</t>
         </is>
       </c>
-      <c r="B431" s="395" t="inlineStr">
+      <c r="B398" s="395" t="inlineStr">
         <is>
           <t>Разработка концепции, работа с подрядчиком, проведение мероприятия, сопровождение</t>
         </is>
       </c>
-      <c r="C431" s="374" t="inlineStr">
+      <c r="C398" s="374" t="inlineStr">
         <is>
           <t>Нематериальная мотивация, поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D431" s="376" t="inlineStr">
+      <c r="D398" s="376" t="inlineStr">
         <is>
           <t>Пенский А.
 Котов И.
@@ -25351,7 +24772,7 @@
 Шибалкова Ю.</t>
         </is>
       </c>
-      <c r="E431" s="390" t="inlineStr">
+      <c r="E398" s="390" t="inlineStr">
         <is>
           <t>Пенский А.:
 1. Проработана и обеспечена безопасность на мероприятии, курирование внешней службы охраны
@@ -25368,23 +24789,23 @@
         </is>
       </c>
     </row>
-    <row r="432" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A432" s="290" t="inlineStr">
+    <row r="399" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A399" s="290" t="inlineStr">
         <is>
           <t>Горящие вакансии</t>
         </is>
       </c>
-      <c r="B432" s="290" t="inlineStr">
+      <c r="B399" s="290" t="inlineStr">
         <is>
           <t>Ежемесячная информационная кампания</t>
         </is>
       </c>
-      <c r="C432" s="290" t="inlineStr">
+      <c r="C399" s="290" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций, распространение активных вакансий</t>
         </is>
       </c>
-      <c r="D432" s="292" t="inlineStr">
+      <c r="D399" s="292" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В.
    Котов И.
@@ -25392,36 +24813,36 @@
 </t>
         </is>
       </c>
-      <c r="E432" s="290" t="inlineStr">
+      <c r="E399" s="290" t="inlineStr">
         <is>
           <t>Котов И.: Сбор информации по ГК и освещение горящих вакансий по почте, на корп. ТВ и портале, а также в чатах Макс.
 Исматова В.: размещение объявлений на информ досках на площадках Машково и Руднево</t>
         </is>
       </c>
     </row>
-    <row r="433" ht="172.8" customFormat="1" customHeight="1" s="38">
-      <c r="A433" s="374" t="inlineStr">
+    <row r="400" ht="172.8" customFormat="1" customHeight="1" s="38">
+      <c r="A400" s="374" t="inlineStr">
         <is>
           <t>Happy Job</t>
         </is>
       </c>
-      <c r="B433" s="395" t="inlineStr">
+      <c r="B400" s="395" t="inlineStr">
         <is>
           <t>Информационная кампания по освещению ежегодного опроса вовлечённости</t>
         </is>
       </c>
-      <c r="C433" s="374" t="inlineStr">
+      <c r="C400" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций, распространение активных вакансий</t>
         </is>
       </c>
-      <c r="D433" s="376" t="inlineStr">
+      <c r="D400" s="376" t="inlineStr">
         <is>
           <t>Пенский А.
 Котов И.</t>
         </is>
       </c>
-      <c r="E433" s="390" t="inlineStr">
+      <c r="E400" s="390" t="inlineStr">
         <is>
           <t>Пенский А.:
 1. Контроль реализации информационной кампании по АИ СН
@@ -25433,28 +24854,28 @@
         </is>
       </c>
     </row>
-    <row r="434" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A434" s="374" t="inlineStr">
+    <row r="401" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A401" s="374" t="inlineStr">
         <is>
           <t>Замещение руководителя</t>
         </is>
       </c>
-      <c r="B434" s="395" t="inlineStr">
+      <c r="B401" s="395" t="inlineStr">
         <is>
           <t>Контроль и реализация всех внутренних коммуникаций на период отпуска руководителя</t>
         </is>
       </c>
-      <c r="C434" s="374" t="inlineStr">
+      <c r="C401" s="374" t="inlineStr">
         <is>
           <t>Нематериальная мотивация, поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D434" s="376" t="inlineStr">
+      <c r="D401" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E434" s="390" t="inlineStr">
+      <c r="E401" s="390" t="inlineStr">
         <is>
           <t>1.Замещение А. Прошкина на период отпуска.
 2.Контроль и реализация всех внутренних коммуникаций.
@@ -25462,176 +24883,176 @@
         </is>
       </c>
     </row>
-    <row r="435" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A435" s="845" t="inlineStr">
+    <row r="402" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A402" s="845" t="inlineStr">
         <is>
           <t>Поздравления с ДР сотрудников</t>
         </is>
       </c>
-      <c r="B435" s="290" t="inlineStr">
+      <c r="B402" s="290" t="inlineStr">
         <is>
           <t xml:space="preserve">Актуализация списков именинников на будущий месяц, сбор фотографий для поздравлений. Сбор/отправка в филиалы подарков на ДР для сотрудников </t>
         </is>
       </c>
-      <c r="C435" s="290" t="inlineStr">
+      <c r="C402" s="290" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D435" s="292" t="inlineStr">
+      <c r="D402" s="292" t="inlineStr">
         <is>
           <t xml:space="preserve">Котов И.
 </t>
         </is>
       </c>
-      <c r="E435" s="290" t="inlineStr">
+      <c r="E402" s="290" t="inlineStr">
         <is>
           <t>1. Сбор информации об именинниках, ежедневная отправка рассылок по почте и в чатах, загрузка фотографий сотрудников на портале</t>
         </is>
       </c>
     </row>
-    <row r="436" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A436" s="754" t="n"/>
-      <c r="B436" s="290" t="inlineStr">
+    <row r="403" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A403" s="754" t="n"/>
+      <c r="B403" s="290" t="inlineStr">
         <is>
           <t>Составление, подписание приказов, списков, ведомостей, договоров дарения на подарки</t>
         </is>
       </c>
-      <c r="C436" s="290" t="inlineStr">
+      <c r="C403" s="290" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D436" s="292" t="n"/>
-      <c r="E436" s="290" t="inlineStr">
+      <c r="D403" s="292" t="n"/>
+      <c r="E403" s="290" t="inlineStr">
         <is>
           <t>1. Выдача подарков сотрудникам по подразделениям (ежемесячно)
 2. Оказана помощь коллегам из отдела дизайна в проверке заключительной партии ракеток для АИ Казань (выявление брака)</t>
         </is>
       </c>
     </row>
-    <row r="437" customFormat="1" s="38">
-      <c r="A437" s="753" t="n"/>
-      <c r="B437" s="387" t="inlineStr">
+    <row r="404" customFormat="1" s="38">
+      <c r="A404" s="753" t="n"/>
+      <c r="B404" s="387" t="inlineStr">
         <is>
           <t>Выдача подарков сотрудникам</t>
         </is>
       </c>
-      <c r="C437" s="387" t="n"/>
-      <c r="D437" s="388" t="inlineStr">
+      <c r="C404" s="387" t="n"/>
+      <c r="D404" s="388" t="inlineStr">
         <is>
           <t>Исматова В.</t>
         </is>
       </c>
-      <c r="E437" s="387" t="n"/>
-    </row>
-    <row r="438" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A438" s="374" t="inlineStr">
+      <c r="E404" s="387" t="n"/>
+    </row>
+    <row r="405" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A405" s="374" t="inlineStr">
         <is>
           <t>Кубок «Химграда 2026»</t>
         </is>
       </c>
-      <c r="B438" s="395" t="inlineStr">
+      <c r="B405" s="395" t="inlineStr">
         <is>
           <t>Информационное освещение результатов коллег на летнем турнире в Казани</t>
         </is>
       </c>
-      <c r="C438" s="374" t="inlineStr">
+      <c r="C405" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D438" s="376" t="inlineStr">
+      <c r="D405" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E438" s="390" t="inlineStr">
+      <c r="E405" s="390" t="inlineStr">
         <is>
           <t>1.Реализована информационная кампания по освещению результатов коллег, участвовавших в летнем турнире в Казани.
    2.Подготовлены новостные рассылки и публикации на портале.</t>
         </is>
       </c>
     </row>
-    <row r="439" ht="57.6" customFormat="1" customHeight="1" s="38">
-      <c r="A439" s="374" t="inlineStr">
+    <row r="406" ht="57.6" customFormat="1" customHeight="1" s="38">
+      <c r="A406" s="374" t="inlineStr">
         <is>
           <t>Кадровый резерв</t>
         </is>
       </c>
-      <c r="B439" s="395" t="inlineStr">
+      <c r="B406" s="395" t="inlineStr">
         <is>
           <t>Разработка плана коммуникаций и освещение программы на портале и в чатах</t>
         </is>
       </c>
-      <c r="C439" s="374" t="inlineStr">
+      <c r="C406" s="374" t="inlineStr">
         <is>
           <t>Развитие корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D439" s="376" t="inlineStr">
+      <c r="D406" s="376" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.</t>
         </is>
       </c>
-      <c r="E439" s="390" t="inlineStr">
+      <c r="E406" s="390" t="inlineStr">
         <is>
           <t>1.Помощь в разработке плана коммуникаций по освещению программы на корпоративном портале.
    2.Проведено освещение программы среди коллег компании.</t>
         </is>
       </c>
     </row>
-    <row r="440" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A440" s="374" t="inlineStr">
+    <row r="407" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A407" s="374" t="inlineStr">
         <is>
           <t>ДМС</t>
         </is>
       </c>
-      <c r="B440" s="395" t="inlineStr">
+      <c r="B407" s="395" t="inlineStr">
         <is>
           <t>Информационная кампания по освещению корпоративной страховки, серия рассылок</t>
         </is>
       </c>
-      <c r="C440" s="374" t="inlineStr">
+      <c r="C407" s="374" t="inlineStr">
         <is>
           <t>Поддержание корп.культуры</t>
         </is>
       </c>
-      <c r="D440" s="376" t="inlineStr">
+      <c r="D407" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E440" s="390" t="inlineStr">
+      <c r="E407" s="390" t="inlineStr">
         <is>
           <t>1.Проведена информационная кампания среди коллег группы компаний по освещению корпоративной страховки.
    2.Создана серия рассылок о программе страхования и её возможностях.</t>
         </is>
       </c>
     </row>
-    <row r="441" ht="100.8" customFormat="1" customHeight="1" s="38">
-      <c r="A441" s="374" t="inlineStr">
+    <row r="408" ht="100.8" customFormat="1" customHeight="1" s="38">
+      <c r="A408" s="374" t="inlineStr">
         <is>
           <t>КЭДО</t>
         </is>
       </c>
-      <c r="B441" s="395" t="inlineStr">
+      <c r="B408" s="395" t="inlineStr">
         <is>
           <t>Освещение КЭДО для сотрудников, унификация инструкций и загрузка на портал</t>
         </is>
       </c>
-      <c r="C441" s="374" t="inlineStr">
+      <c r="C408" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D441" s="376" t="inlineStr">
+      <c r="D408" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E441" s="390" t="inlineStr">
+      <c r="E408" s="390" t="inlineStr">
         <is>
           <t>1.Проведена информационная кампания по освещению КЭДО для сотрудников «Авиационных интерьеров».
    2.Унифицированы инструкции и загружены на корпоративный портал.
@@ -25639,28 +25060,28 @@
         </is>
       </c>
     </row>
-    <row r="442" ht="86.40000000000001" customFormat="1" customHeight="1" s="38">
-      <c r="A442" s="396" t="inlineStr">
+    <row r="409" ht="86.40000000000001" customFormat="1" customHeight="1" s="38">
+      <c r="A409" s="396" t="inlineStr">
         <is>
           <t>Обращение Р. В. Торопова и инструкция по командировкам</t>
         </is>
       </c>
-      <c r="B442" s="396" t="inlineStr">
+      <c r="B409" s="396" t="inlineStr">
         <is>
           <t>Доработка инструкции и освещение процесса через обращение руководителя</t>
         </is>
       </c>
-      <c r="C442" s="374" t="inlineStr">
+      <c r="C409" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D442" s="376" t="inlineStr">
+      <c r="D409" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E442" s="398" t="inlineStr">
+      <c r="E409" s="398" t="inlineStr">
         <is>
           <t>1.Доработана инструкция по командировкам для сотрудников компании.
    2.Проведено освещение процесса через обращение Р. В. Топорова.
@@ -25668,85 +25089,85 @@
         </is>
       </c>
     </row>
-    <row r="443" ht="57.6" customFormat="1" customHeight="1" s="38">
-      <c r="A443" s="396" t="inlineStr">
+    <row r="410" ht="57.6" customFormat="1" customHeight="1" s="38">
+      <c r="A410" s="396" t="inlineStr">
         <is>
           <t>Подарки к 1 сентября</t>
         </is>
       </c>
-      <c r="B443" s="396" t="inlineStr">
+      <c r="B410" s="396" t="inlineStr">
         <is>
           <t>Сбор и вручение подарков сотрудникам — родителям первоклассников</t>
         </is>
       </c>
-      <c r="C443" s="374" t="inlineStr">
+      <c r="C410" s="374" t="inlineStr">
         <is>
           <t>Поддержание корп.культуры</t>
         </is>
       </c>
-      <c r="D443" s="376" t="inlineStr">
+      <c r="D410" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E443" s="398" t="inlineStr">
+      <c r="E410" s="398" t="inlineStr">
         <is>
           <t>1.Собраны и вручены подарки сотрудникам — родителям первоклассников.
    2.Оказана помощь в отправке подарков для сотрудников АИ Казань через СДЭК.</t>
         </is>
       </c>
     </row>
-    <row r="444" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A444" s="290" t="inlineStr">
+    <row r="411" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A411" s="290" t="inlineStr">
         <is>
           <t>Видео-экскурсия по ГК</t>
         </is>
       </c>
-      <c r="B444" s="290" t="inlineStr">
+      <c r="B411" s="290" t="inlineStr">
         <is>
           <t>планирование нового элемента адаптации сотрудников</t>
         </is>
       </c>
-      <c r="C444" s="290" t="inlineStr">
+      <c r="C411" s="290" t="inlineStr">
         <is>
           <t>Развитие корп. Культуры</t>
         </is>
       </c>
-      <c r="D444" s="292" t="inlineStr">
+      <c r="D411" s="292" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.</t>
         </is>
       </c>
-      <c r="E444" s="290" t="inlineStr">
+      <c r="E411" s="290" t="inlineStr">
         <is>
           <t>1. Составлен концепт ознакомительного видео для новых сотрудников ГК
 2. Запланирована съемка видео после монтажа серии роликов по ОТ, а также внеплановых видео (Мос. марафон, видеогид)</t>
         </is>
       </c>
     </row>
-    <row r="445" ht="110.4" customFormat="1" customHeight="1" s="38">
-      <c r="A445" s="290" t="inlineStr">
+    <row r="412" ht="110.4" customFormat="1" customHeight="1" s="38">
+      <c r="A412" s="290" t="inlineStr">
         <is>
           <t>Корпоративный помощник</t>
         </is>
       </c>
-      <c r="B445" s="290" t="inlineStr">
+      <c r="B412" s="290" t="inlineStr">
         <is>
           <t>проект по внедрению ИИ</t>
         </is>
       </c>
-      <c r="C445" s="290" t="inlineStr">
+      <c r="C412" s="290" t="inlineStr">
         <is>
           <t>развитие ИИ в ГК</t>
         </is>
       </c>
-      <c r="D445" s="292" t="inlineStr">
+      <c r="D412" s="292" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E445" s="290" t="inlineStr">
+      <c r="E412" s="290" t="inlineStr">
         <is>
           <t>1.Создан веб-интерфейс (сайт) для бота — как для пользователей, так и для администраторов.
 2.Создано 3 группы тестировщиков для корпоративного чат-бота, разработаны инструкции по тестированию.
@@ -25755,11 +25176,703 @@
         </is>
       </c>
     </row>
-    <row r="446" customFormat="1" s="38"/>
-    <row r="447" ht="18" customFormat="1" customHeight="1" s="38">
-      <c r="A447" s="837" t="inlineStr">
+    <row r="413" customFormat="1" s="38"/>
+    <row r="414" ht="18" customFormat="1" customHeight="1" s="38">
+      <c r="A414" s="837" t="inlineStr">
         <is>
           <t>ПЛАН 4 квартал 2026</t>
+        </is>
+      </c>
+      <c r="B414" s="805" t="n"/>
+      <c r="C414" s="805" t="n"/>
+      <c r="D414" s="805" t="n"/>
+      <c r="E414" s="747" t="n"/>
+    </row>
+    <row r="415" ht="15.6" customFormat="1" customHeight="1" s="38">
+      <c r="A415" s="838" t="inlineStr">
+        <is>
+          <t>Кадровое делопроизводство</t>
+        </is>
+      </c>
+      <c r="B415" s="805" t="n"/>
+      <c r="C415" s="805" t="n"/>
+      <c r="D415" s="805" t="n"/>
+      <c r="E415" s="747" t="n"/>
+    </row>
+    <row r="416" ht="15.6" customFormat="1" customHeight="1" s="38">
+      <c r="A416" s="804" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Текущая деятельность </t>
+        </is>
+      </c>
+      <c r="B416" s="805" t="n"/>
+      <c r="C416" s="805" t="n"/>
+      <c r="D416" s="805" t="n"/>
+      <c r="E416" s="747" t="n"/>
+    </row>
+    <row r="417" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A417" s="290" t="inlineStr">
+        <is>
+          <t>Приказы о премировании</t>
+        </is>
+      </c>
+      <c r="B417" s="184" t="inlineStr">
+        <is>
+          <t>Сбор данных, проверка и оформление приказов. Передача в бухгалтерию копий приказов.</t>
+        </is>
+      </c>
+      <c r="C417" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D417" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E417" s="184" t="n"/>
+    </row>
+    <row r="418" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A418" s="290" t="inlineStr">
+        <is>
+          <t>Отчетность по премированию</t>
+        </is>
+      </c>
+      <c r="B418" s="184" t="inlineStr">
+        <is>
+          <t>Сбор данных ежемесячно, составление свода за месяц/квартал, подготовка данных для анализа квартального премирования</t>
+        </is>
+      </c>
+      <c r="C418" s="701" t="inlineStr">
+        <is>
+          <t>Обоснование расходов для отчета руководству (Торопов Р., Шигаев В., Кисловская И.)</t>
+        </is>
+      </c>
+      <c r="D418" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E418" s="184" t="n"/>
+    </row>
+    <row r="419" customFormat="1" s="38">
+      <c r="A419" s="290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обоснование премирования </t>
+        </is>
+      </c>
+      <c r="B419" s="184" t="inlineStr">
+        <is>
+          <t>Оформление служебных записок</t>
+        </is>
+      </c>
+      <c r="C419" s="701" t="inlineStr">
+        <is>
+          <t>Обоснование расходов работодателя</t>
+        </is>
+      </c>
+      <c r="D419" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E419" s="184" t="n"/>
+    </row>
+    <row r="420" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A420" s="290" t="inlineStr">
+        <is>
+          <t>Приказы о материальной помощи</t>
+        </is>
+      </c>
+      <c r="B420" s="184" t="inlineStr">
+        <is>
+          <t>Оформляется по заявлению работника, согласовывается с ГД.</t>
+        </is>
+      </c>
+      <c r="C420" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D420" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E420" s="184" t="n"/>
+    </row>
+    <row r="421" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A421" s="290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прием на работу </t>
+        </is>
+      </c>
+      <c r="B421" s="184" t="inlineStr">
+        <is>
+          <t>Оформление документов при приеме на работу: ТД, приказ, Соглашение о неразглашении конфиденциальной информации, документы по персональным данным, заявления, справки и т.д., внесение данных в базу 1С, подписание с работником</t>
+        </is>
+      </c>
+      <c r="C421" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D421" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Резенова Н.А.
+   Руцкая В.В.</t>
+        </is>
+      </c>
+      <c r="E421" s="184" t="n"/>
+    </row>
+    <row r="422" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A422" s="738" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Увольнение </t>
+        </is>
+      </c>
+      <c r="B422" s="184" t="inlineStr">
+        <is>
+          <t>Оформление увольнения  по инициативе работника, по инициативе работодателя. Оформляются приказ, соглашение об увольнении, табель учета, вносится запись в тр. книжку или справка СТД-Р, ознакомление работника с документами</t>
+        </is>
+      </c>
+      <c r="C422" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D422" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Резенова Н.А.</t>
+        </is>
+      </c>
+      <c r="E422" s="184" t="n"/>
+    </row>
+    <row r="423" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A423" s="753" t="n"/>
+      <c r="B423" s="184" t="inlineStr">
+        <is>
+          <t>Решение сложных вопросов по увольнению работников</t>
+        </is>
+      </c>
+      <c r="C423" s="701" t="n"/>
+      <c r="D423" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.
+   Козлова Ю.В.</t>
+        </is>
+      </c>
+      <c r="E423" s="184" t="n"/>
+    </row>
+    <row r="424" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A424" s="691" t="inlineStr">
+        <is>
+          <t>Переводы (изменение должностей, подразделений)</t>
+        </is>
+      </c>
+      <c r="B424" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Переводы оформляются по соглашению сторон (возможно в связи с  изменением шатного расписания, на основании результатлов аттестации персонала), готовится: приказ, доп. соглашение к ТД, вносятся данные в программу 1С, ознакомление работника </t>
+        </is>
+      </c>
+      <c r="C424" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D424" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Резенова Н.А.
+   Павленко Н.С.</t>
+        </is>
+      </c>
+      <c r="E424" s="184" t="n"/>
+    </row>
+    <row r="425" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A425" s="691" t="inlineStr">
+        <is>
+          <t>Отпуска, все виды (ежегодные, без сохранений з/п, учебные, по БИР, по уходу за ребенком, донорские, пр.)</t>
+        </is>
+      </c>
+      <c r="B425" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">На основании графика отпусков или по заявлению работника оформляется приказ на отпуск с приложением необходимых подтверждающих документов </t>
+        </is>
+      </c>
+      <c r="C425" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D425" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Руцкая В.В.
+   Резенова Н.А.
+   Казначеева А.Н.</t>
+        </is>
+      </c>
+      <c r="E425" s="184" t="n"/>
+    </row>
+    <row r="426" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A426" s="691" t="inlineStr">
+        <is>
+          <t>Оформление сверхурочной работы</t>
+        </is>
+      </c>
+      <c r="B426" s="184" t="inlineStr">
+        <is>
+          <t>На основании СЗ от руководителя и согласия работников оформляется Приказ (с офомлением повышенной оплаты или предоставлением днем отдыха)</t>
+        </is>
+      </c>
+      <c r="C426" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D426" s="182" t="inlineStr">
+        <is>
+          <t>Павленко Н.С.
+Руцкая В.В.</t>
+        </is>
+      </c>
+      <c r="E426" s="184" t="n"/>
+    </row>
+    <row r="427" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A427" s="691" t="inlineStr">
+        <is>
+          <t>Оформление работы в выходной день</t>
+        </is>
+      </c>
+      <c r="B427" s="184" t="inlineStr">
+        <is>
+          <t>На основании СЗ от руководителя и согласия работников оформляется Приказ (с офомлением повышенной оплаты или предоставлением днем отдыха)</t>
+        </is>
+      </c>
+      <c r="C427" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D427" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В. - командировки
+   Павленко Н.С. - все остальные</t>
+        </is>
+      </c>
+      <c r="E427" s="184" t="n"/>
+    </row>
+    <row r="428" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A428" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Командировки </t>
+        </is>
+      </c>
+      <c r="B428" s="184" t="inlineStr">
+        <is>
+          <t>Оформление приказов о командировании , изменении сроков командирования  и контроль оформления  Служебных заданий на командировки</t>
+        </is>
+      </c>
+      <c r="C428" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D428" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Руцкая В.В.
+   Резенова Н.А.</t>
+        </is>
+      </c>
+      <c r="E428" s="184" t="n"/>
+    </row>
+    <row r="429" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A429" s="691" t="inlineStr">
+        <is>
+          <t>Аудит кадровых документов</t>
+        </is>
+      </c>
+      <c r="B429" s="184" t="inlineStr">
+        <is>
+          <t>Проверка раличия и восстановление отсутствующих приказов за 2025 и при необходимости за 2024 кадровых приказов</t>
+        </is>
+      </c>
+      <c r="C429" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D429" s="182" t="inlineStr">
+        <is>
+          <t>Козлова Ю.В.
+   Афонина Ю.В.
+   Резенова Н.А.
+   Павленко Н.С.</t>
+        </is>
+      </c>
+      <c r="E429" s="184" t="n"/>
+    </row>
+    <row r="430" customFormat="1" s="38">
+      <c r="A430" s="829" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Согласование, утверждение  Положений и должностных инструкций по новому ШР в полном объеме </t>
+        </is>
+      </c>
+      <c r="B430" s="805" t="n"/>
+      <c r="C430" s="805" t="n"/>
+      <c r="D430" s="805" t="n"/>
+      <c r="E430" s="747" t="n"/>
+    </row>
+    <row r="431" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A431" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Согласование ДИ по новой форме по всем должностям согласно ШР, подписание, передача на утверждение ГД </t>
+        </is>
+      </c>
+      <c r="B431" s="184" t="inlineStr">
+        <is>
+          <t>Наличие базы ДИ и ПП по организации в полном объеме</t>
+        </is>
+      </c>
+      <c r="C431" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D431" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.
+Козлова Ю.В.</t>
+        </is>
+      </c>
+      <c r="E431" s="184" t="n"/>
+    </row>
+    <row r="432" customFormat="1" s="38">
+      <c r="A432" s="829" t="inlineStr">
+        <is>
+          <t>Формирование  отчётности</t>
+        </is>
+      </c>
+      <c r="B432" s="805" t="n"/>
+      <c r="C432" s="805" t="n"/>
+      <c r="D432" s="805" t="n"/>
+      <c r="E432" s="747" t="n"/>
+    </row>
+    <row r="433" customFormat="1" s="38">
+      <c r="A433" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отчет по статистике </t>
+        </is>
+      </c>
+      <c r="B433" s="184" t="inlineStr">
+        <is>
+          <t>П4 НЗ, ежеквартальный, за 3-й квартал 2026</t>
+        </is>
+      </c>
+      <c r="C433" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D433" s="182" t="inlineStr">
+        <is>
+          <t>Козлова Ю.В</t>
+        </is>
+      </c>
+      <c r="E433" s="184" t="n"/>
+    </row>
+    <row r="434" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A434" s="691" t="inlineStr">
+        <is>
+          <t>Отчёты в СФР штатные работники (прием/увольнение)</t>
+        </is>
+      </c>
+      <c r="B434" s="184" t="inlineStr">
+        <is>
+          <t>Отчёт в СФР  (по форме ЕФС-1 разд. 1.1.)  оформляется не позднее одного рабочего дня после даты издания приказов о  приеме, увольнении работников.</t>
+        </is>
+      </c>
+      <c r="C434" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D434" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Резенова Н.А.
+   Козлова Ю.В.
+   Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E434" s="184" t="n"/>
+    </row>
+    <row r="435" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A435" s="691" t="inlineStr">
+        <is>
+          <t>Отчёты в СФР  штатные работники (переводы)</t>
+        </is>
+      </c>
+      <c r="B435" s="184" t="inlineStr">
+        <is>
+          <t>Отчёт в СФР  (по форме ЕФС-1 разд. 1.1.)  оформляется не позднее 25 числа месяца, следующего за отчетным месяцем издания приказов о  переводе работников. А так же иным мероприятиям предусмотренным законодательствам РФ.</t>
+        </is>
+      </c>
+      <c r="C435" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D435" s="182" t="inlineStr">
+        <is>
+          <t>Афонина Ю.В.
+   Резенова Н.А.
+   Козлова Ю.В.
+   Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E435" s="184" t="n"/>
+    </row>
+    <row r="436" customFormat="1" s="38">
+      <c r="A436" s="691" t="inlineStr">
+        <is>
+          <t>Отчет по инвалидам</t>
+        </is>
+      </c>
+      <c r="B436" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ежеквартальный </t>
+        </is>
+      </c>
+      <c r="C436" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ</t>
+        </is>
+      </c>
+      <c r="D436" s="182" t="inlineStr">
+        <is>
+          <t>Козлова Ю.В.</t>
+        </is>
+      </c>
+      <c r="E436" s="184" t="n"/>
+    </row>
+    <row r="437" customFormat="1" s="38">
+      <c r="A437" s="829" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разработка (актуализация)  ЛНА, развитие процессов, создание  Базы знаний по кадрам </t>
+        </is>
+      </c>
+      <c r="B437" s="805" t="n"/>
+      <c r="C437" s="805" t="n"/>
+      <c r="D437" s="805" t="n"/>
+      <c r="E437" s="747" t="n"/>
+    </row>
+    <row r="438" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A438" s="691" t="inlineStr">
+        <is>
+          <t>Внесение изменений в БП Командировки ГК</t>
+        </is>
+      </c>
+      <c r="B438" s="184" t="inlineStr">
+        <is>
+          <t>Дополнить размеры суточных по загранице суточными для поездок в Китай</t>
+        </is>
+      </c>
+      <c r="C438" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства РФ, оптимизация БП</t>
+        </is>
+      </c>
+      <c r="D438" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E438" s="184" t="n"/>
+    </row>
+    <row r="439" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A439" s="691" t="inlineStr">
+        <is>
+          <t>Автоматизация печатных форм приказов и договоров в 1С</t>
+        </is>
+      </c>
+      <c r="B439" s="184" t="inlineStr">
+        <is>
+          <t>В рамках подготовки к внедрению КЭДО</t>
+        </is>
+      </c>
+      <c r="C439" s="701" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D439" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.
+   Козлова Ю.В.</t>
+        </is>
+      </c>
+      <c r="E439" s="184" t="n"/>
+    </row>
+    <row r="440" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A440" s="691" t="inlineStr">
+        <is>
+          <t>Изменение процессов взаимодействия между подразделениями</t>
+        </is>
+      </c>
+      <c r="B440" s="184" t="inlineStr">
+        <is>
+          <t>Оптимизация взаимодействия между кадрами и бухгалтерией, разработка документооборота между кадрами и другими подразделениями</t>
+        </is>
+      </c>
+      <c r="C440" s="701" t="inlineStr">
+        <is>
+          <t>Оптимизация взаимодействия работников  подразделений и ОУП</t>
+        </is>
+      </c>
+      <c r="D440" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E440" s="184" t="n"/>
+    </row>
+    <row r="441" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A441" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подготовка методических материалов по кадрам </t>
+        </is>
+      </c>
+      <c r="B441" s="184" t="inlineStr">
+        <is>
+          <t>Формирование Базы знаний по кадровым  направлениям (Прием, перевод, увольнение , пр.) . Подготовка Памяток для работников, шаблонов  СЗ, Заявлений, размещение в Базе - по основным мероприятиям</t>
+        </is>
+      </c>
+      <c r="C441" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оптимизация взаимодействия работников  подразделений и ОУП.  Повышение уровня сервиса для персонала  </t>
+        </is>
+      </c>
+      <c r="D441" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E441" s="184" t="n"/>
+    </row>
+    <row r="442" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A442" s="412" t="inlineStr">
+        <is>
+          <t>Оптимизация работы отделов Дирекции по персоналу</t>
+        </is>
+      </c>
+      <c r="B442" s="413" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C442" s="414" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D442" s="415" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E442" s="413" t="n"/>
+    </row>
+    <row r="443" customFormat="1" s="38">
+      <c r="A443" s="829" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Работа с суммированным учетом РВ (в рамках Положения о СУРВ),  Графики работы подразделений с СУРВ, Табели подразделений </t>
+        </is>
+      </c>
+      <c r="B443" s="805" t="n"/>
+      <c r="C443" s="805" t="n"/>
+      <c r="D443" s="805" t="n"/>
+      <c r="E443" s="747" t="n"/>
+    </row>
+    <row r="444" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A444" s="410" t="inlineStr">
+        <is>
+          <t>Организация работы подразделений по графикам смен.  Анализ и актуализация графиков работы (смен)  работников. Подготовка приказов Приведение в соответствие ТД  работников</t>
+        </is>
+      </c>
+      <c r="B444" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Соблюдение графиков производства. Разработка графиком для Отдела режима </t>
+        </is>
+      </c>
+      <c r="C444" s="727" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация деятельности подразделений, соблюдение требований ТК РФ </t>
+        </is>
+      </c>
+      <c r="D444" s="182" t="inlineStr">
+        <is>
+          <t>Павленко Н.С.</t>
+        </is>
+      </c>
+      <c r="E444" s="184" t="n"/>
+    </row>
+    <row r="445" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A445" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация работы с табелями </t>
+        </is>
+      </c>
+      <c r="B445" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контроль, сопровождение оформления табелей </t>
+        </is>
+      </c>
+      <c r="C445" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация деятельности подразделений, соблюдение требований ТК РФ </t>
+        </is>
+      </c>
+      <c r="D445" s="182" t="inlineStr">
+        <is>
+          <t>Руцкая В.В.
+   Павленко Н.С.</t>
+        </is>
+      </c>
+      <c r="E445" s="184" t="n"/>
+    </row>
+    <row r="446" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A446" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация работы с табелями </t>
+        </is>
+      </c>
+      <c r="B446" s="184" t="inlineStr">
+        <is>
+          <t>Назначение ответственных за ведение табелей Вемина по подразделениям</t>
+        </is>
+      </c>
+      <c r="C446" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация деятельности подразделений, соблюдение требований ТК РФ </t>
+        </is>
+      </c>
+      <c r="D446" s="182" t="inlineStr">
+        <is>
+          <t>Павленко Н.С.</t>
+        </is>
+      </c>
+      <c r="E446" s="184" t="n"/>
+    </row>
+    <row r="447" customFormat="1" s="38">
+      <c r="A447" s="829" t="inlineStr">
+        <is>
+          <t>Новая организационная структура, штатное расписание компании</t>
         </is>
       </c>
       <c r="B447" s="805" t="n"/>
@@ -25767,42 +25880,66 @@
       <c r="D447" s="805" t="n"/>
       <c r="E447" s="747" t="n"/>
     </row>
-    <row r="448" ht="15.6" customFormat="1" customHeight="1" s="38">
-      <c r="A448" s="838" t="inlineStr">
-        <is>
-          <t>Кадровое делопроизводство</t>
-        </is>
-      </c>
-      <c r="B448" s="805" t="n"/>
-      <c r="C448" s="805" t="n"/>
-      <c r="D448" s="805" t="n"/>
-      <c r="E448" s="747" t="n"/>
-    </row>
-    <row r="449" ht="15.6" customFormat="1" customHeight="1" s="38">
-      <c r="A449" s="804" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Текущая деятельность </t>
-        </is>
-      </c>
-      <c r="B449" s="805" t="n"/>
-      <c r="C449" s="805" t="n"/>
-      <c r="D449" s="805" t="n"/>
-      <c r="E449" s="747" t="n"/>
-    </row>
-    <row r="450" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A450" s="290" t="inlineStr">
-        <is>
-          <t>Приказы о премировании</t>
+    <row r="448" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A448" s="691" t="inlineStr">
+        <is>
+          <t>Соблюдение нового штатного расписания и  ФОТ</t>
+        </is>
+      </c>
+      <c r="B448" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контроль исполнения ФОТ/ШР.  Предоставление данных для приема на работу, переводов руководителям и в отдел подбора </t>
+        </is>
+      </c>
+      <c r="C448" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация деятельности  компании </t>
+        </is>
+      </c>
+      <c r="D448" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E448" s="184" t="n"/>
+    </row>
+    <row r="449" customFormat="1" s="38">
+      <c r="A449" s="691" t="inlineStr">
+        <is>
+          <t>Внесение изменений в 1С по новому  ШР</t>
+        </is>
+      </c>
+      <c r="B449" s="184" t="inlineStr">
+        <is>
+          <t>Согласование, внесение изменений в 1С</t>
+        </is>
+      </c>
+      <c r="C449" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация деятельности  компании </t>
+        </is>
+      </c>
+      <c r="D449" s="182" t="inlineStr">
+        <is>
+          <t>Еремина О.А.</t>
+        </is>
+      </c>
+      <c r="E449" s="184" t="n"/>
+    </row>
+    <row r="450" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A450" s="691" t="inlineStr">
+        <is>
+          <t>Проработка возможности реализации в 1С:ЗУП управленческой структуры и отчетности</t>
         </is>
       </c>
       <c r="B450" s="184" t="inlineStr">
         <is>
-          <t>Сбор данных, проверка и оформление приказов. Передача в бухгалтерию копий приказов.</t>
+          <t xml:space="preserve">Реализация упарвленческой структцуры и отчетности в целях учета функциональной принадлежности позиций штатного расписания и работников. </t>
         </is>
       </c>
       <c r="C450" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Организация деятельности  компании </t>
         </is>
       </c>
       <c r="D450" s="182" t="inlineStr">
@@ -25812,235 +25949,204 @@
       </c>
       <c r="E450" s="184" t="n"/>
     </row>
-    <row r="451" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A451" s="290" t="inlineStr">
-        <is>
-          <t>Отчетность по премированию</t>
-        </is>
-      </c>
-      <c r="B451" s="184" t="inlineStr">
-        <is>
-          <t>Сбор данных ежемесячно, составление свода за месяц/квартал, подготовка данных для анализа квартального премирования</t>
-        </is>
-      </c>
-      <c r="C451" s="701" t="inlineStr">
-        <is>
-          <t>Обоснование расходов для отчета руководству (Торопов Р., Шигаев В., Кисловская И.)</t>
-        </is>
-      </c>
-      <c r="D451" s="182" t="inlineStr">
-        <is>
-          <t>Еремина О.А.</t>
-        </is>
-      </c>
-      <c r="E451" s="184" t="n"/>
+    <row r="451" customFormat="1" s="38">
+      <c r="A451" s="829" t="inlineStr">
+        <is>
+          <t>Ведение воинского учёта и бронирования</t>
+        </is>
+      </c>
+      <c r="B451" s="805" t="n"/>
+      <c r="C451" s="805" t="n"/>
+      <c r="D451" s="805" t="n"/>
+      <c r="E451" s="747" t="n"/>
     </row>
     <row r="452" customFormat="1" s="38">
-      <c r="A452" s="290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Обоснование премирования </t>
+      <c r="A452" s="691" t="inlineStr">
+        <is>
+          <t>Разъяснение правил воинского учета</t>
         </is>
       </c>
       <c r="B452" s="184" t="inlineStr">
         <is>
-          <t>Оформление служебных записок</t>
+          <t>При приеме на работу. Ведение журнала.</t>
         </is>
       </c>
       <c r="C452" s="701" t="inlineStr">
         <is>
-          <t>Обоснование расходов работодателя</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D452" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E452" s="184" t="n"/>
     </row>
     <row r="453" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A453" s="290" t="inlineStr">
-        <is>
-          <t>Приказы о материальной помощи</t>
+      <c r="A453" s="691" t="inlineStr">
+        <is>
+          <t>Ведение карточек ф.10</t>
         </is>
       </c>
       <c r="B453" s="184" t="inlineStr">
         <is>
-          <t>Оформляется по заявлению работника, согласовывается с ГД.</t>
+          <t>При приеме, переводе, изменении данных, увольнении</t>
         </is>
       </c>
       <c r="C453" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t>Соблюдение законожательства РФ.</t>
         </is>
       </c>
       <c r="D453" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E453" s="184" t="n"/>
     </row>
-    <row r="454" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A454" s="290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Прием на работу </t>
+    <row r="454" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A454" s="691" t="inlineStr">
+        <is>
+          <t>Сведения при приеме/увольнении/переводе/  изменении др. (Приложение № 2 к Положению о ВУ)</t>
         </is>
       </c>
       <c r="B454" s="184" t="inlineStr">
         <is>
-          <t>Оформление документов при приеме на работу: ТД, приказ, Соглашение о неразглашении конфиденциальной информации, документы по персональным данным, заявления, справки и т.д., внесение данных в базу 1С, подписание с работником</t>
+          <t>Направление в военный комиссариат по месту жительства работника</t>
         </is>
       </c>
       <c r="C454" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D454" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В.
-   Резенова Н.А.
-   Руцкая В.В.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E454" s="184" t="n"/>
     </row>
-    <row r="455" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A455" s="738" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Увольнение </t>
+    <row r="455" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A455" s="691" t="inlineStr">
+        <is>
+          <t>Отчетность</t>
         </is>
       </c>
       <c r="B455" s="184" t="inlineStr">
         <is>
-          <t>Оформление увольнения  по инициативе работника, по инициативе работодателя. Оформляются приказ, соглашение об увольнении, табель учета, вносится запись в тр. книжку или справка СТД-Р, ознакомление работника с документами</t>
+          <t>Продление справки (с предоставлением карточки организации ф.18; ф.6 и ф.19) в районной комиссии по бронированию. Передача справки в военный комиссариат</t>
         </is>
       </c>
       <c r="C455" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D455" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В.
-   Резенова Н.А.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E455" s="184" t="n"/>
     </row>
     <row r="456" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A456" s="753" t="n"/>
+      <c r="A456" s="839" t="inlineStr">
+        <is>
+          <t>Ведение документации по бронированию</t>
+        </is>
+      </c>
       <c r="B456" s="184" t="inlineStr">
         <is>
-          <t>Решение сложных вопросов по увольнению работников</t>
-        </is>
-      </c>
-      <c r="C456" s="701" t="n"/>
+          <t>Подготовка  приказов о бронировании сотрудников</t>
+        </is>
+      </c>
+      <c r="C456" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
+        </is>
+      </c>
       <c r="D456" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.
-   Козлова Ю.В.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E456" s="184" t="n"/>
     </row>
-    <row r="457" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A457" s="691" t="inlineStr">
-        <is>
-          <t>Переводы (изменение должностей, подразделений)</t>
-        </is>
-      </c>
+    <row r="457" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A457" s="754" t="n"/>
       <c r="B457" s="184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Переводы оформляются по соглашению сторон (возможно в связи с  изменением шатного расписания, на основании результатлов аттестации персонала), готовится: приказ, доп. соглашение к ТД, вносятся данные в программу 1С, ознакомление работника </t>
+          <t>Подготовка Выписок из приказа о бронировании сотрудников</t>
         </is>
       </c>
       <c r="C457" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D457" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В.
-   Резенова Н.А.
-   Павленко Н.С.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E457" s="184" t="n"/>
     </row>
-    <row r="458" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A458" s="691" t="inlineStr">
-        <is>
-          <t>Отпуска, все виды (ежегодные, без сохранений з/п, учебные, по БИР, по уходу за ребенком, донорские, пр.)</t>
-        </is>
-      </c>
+    <row r="458" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A458" s="754" t="n"/>
       <c r="B458" s="184" t="inlineStr">
         <is>
-          <t xml:space="preserve">На основании графика отпусков или по заявлению работника оформляется приказ на отпуск с приложением необходимых подтверждающих документов </t>
+          <t>Оформление приказа о прекращении бронирования</t>
         </is>
       </c>
       <c r="C458" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D458" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В.
-   Руцкая В.В.
-   Резенова Н.А.
-   Казначеева А.Н.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E458" s="184" t="n"/>
     </row>
-    <row r="459" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A459" s="691" t="inlineStr">
-        <is>
-          <t>Оформление сверхурочной работы</t>
-        </is>
-      </c>
+    <row r="459" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A459" s="754" t="n"/>
       <c r="B459" s="184" t="inlineStr">
         <is>
-          <t>На основании СЗ от руководителя и согласия работников оформляется Приказ (с офомлением повышенной оплаты или предоставлением днем отдыха)</t>
+          <t>Оформление выписок из проекта приказа о прекращении бронировании</t>
         </is>
       </c>
       <c r="C459" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D459" s="182" t="inlineStr">
         <is>
-          <t>Павленко Н.С.
-Руцкая В.В.</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E459" s="184" t="n"/>
     </row>
-    <row r="460" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A460" s="691" t="inlineStr">
-        <is>
-          <t>Оформление работы в выходной день</t>
-        </is>
-      </c>
+    <row r="460" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A460" s="753" t="n"/>
       <c r="B460" s="184" t="inlineStr">
         <is>
-          <t>На основании СЗ от руководителя и согласия работников оформляется Приказ (с офомлением повышенной оплаты или предоставлением днем отдыха)</t>
+          <t>Оформление сопроводительных писем к выпискам из приказов</t>
         </is>
       </c>
       <c r="C460" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
         </is>
       </c>
       <c r="D460" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В. - командировки
-   Павленко Н.С. - все остальные</t>
+          <t>Кавыза О.Г.</t>
         </is>
       </c>
       <c r="E460" s="184" t="n"/>
@@ -26048,171 +26154,171 @@
     <row r="461" ht="55.2" customFormat="1" customHeight="1" s="38">
       <c r="A461" s="691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Командировки </t>
+          <t>Подготовка листков сообщений</t>
         </is>
       </c>
       <c r="B461" s="184" t="inlineStr">
         <is>
-          <t>Оформление приказов о командировании , изменении сроков командирования  и контроль оформления  Служебных заданий на командировки</t>
+          <t>Документ выдается на руки сотрудники с целью посещения военкомата в связи с ихменением места жительства, состава семьи, образования и т.д.</t>
         </is>
       </c>
       <c r="C461" s="701" t="inlineStr">
         <is>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
+        </is>
+      </c>
+      <c r="D461" s="182" t="inlineStr">
+        <is>
+          <t>Кавыза О.Г.</t>
+        </is>
+      </c>
+      <c r="E461" s="184" t="n"/>
+    </row>
+    <row r="462" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A462" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подготовка направления для постановки на ВУ </t>
+        </is>
+      </c>
+      <c r="B462" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Документ выдается на руки сотрудники с целью посещения военкомата для постановки на ВУ </t>
+        </is>
+      </c>
+      <c r="C462" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
+        </is>
+      </c>
+      <c r="D462" s="182" t="inlineStr">
+        <is>
+          <t>Кавыза О.Г.</t>
+        </is>
+      </c>
+      <c r="E462" s="184" t="n"/>
+    </row>
+    <row r="463" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A463" s="691" t="inlineStr">
+        <is>
+          <t>Ведение журналов</t>
+        </is>
+      </c>
+      <c r="B463" s="184" t="inlineStr">
+        <is>
+          <t>Журналы по работе, связанной с воинским учетом и бронированием.</t>
+        </is>
+      </c>
+      <c r="C463" s="701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
+        </is>
+      </c>
+      <c r="D463" s="182" t="inlineStr">
+        <is>
+          <t>Кавыза О.Г.</t>
+        </is>
+      </c>
+      <c r="E463" s="184" t="n"/>
+    </row>
+    <row r="464" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A464" s="691" t="inlineStr">
+        <is>
+          <t>Автоматизация в 1С ведения данных по ВУ и бронированию</t>
+        </is>
+      </c>
+      <c r="B464" s="184" t="inlineStr">
+        <is>
+          <t>Внесение данных по бронированию в 1С: приказов, справок пр. документов</t>
+        </is>
+      </c>
+      <c r="C464" s="701" t="inlineStr">
+        <is>
+          <t>Организация деятельности подразделения</t>
+        </is>
+      </c>
+      <c r="D464" s="182" t="inlineStr">
+        <is>
+          <t>Кавыза О.Г.</t>
+        </is>
+      </c>
+      <c r="E464" s="184" t="n"/>
+    </row>
+    <row r="465" customFormat="1" s="38">
+      <c r="A465" s="691" t="inlineStr">
+        <is>
+          <t>Подключение к ЛК Реестр повесток.рф</t>
+        </is>
+      </c>
+      <c r="B465" s="184" t="inlineStr">
+        <is>
+          <t>Подача установленных форм в электронном виде</t>
+        </is>
+      </c>
+      <c r="C465" s="701" t="inlineStr">
+        <is>
           <t>Соблюдение законодательства РФ</t>
         </is>
       </c>
-      <c r="D461" s="182" t="inlineStr">
-        <is>
-          <t>Афонина Ю.В.
-   Руцкая В.В.
-   Резенова Н.А.</t>
-        </is>
-      </c>
-      <c r="E461" s="184" t="n"/>
-    </row>
-    <row r="462" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A462" s="691" t="inlineStr">
-        <is>
-          <t>Аудит кадровых документов</t>
-        </is>
-      </c>
-      <c r="B462" s="184" t="inlineStr">
-        <is>
-          <t>Проверка раличия и восстановление отсутствующих приказов за 2025 и при необходимости за 2024 кадровых приказов</t>
-        </is>
-      </c>
-      <c r="C462" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства РФ</t>
-        </is>
-      </c>
-      <c r="D462" s="182" t="inlineStr">
-        <is>
-          <t>Козлова Ю.В.
-   Афонина Ю.В.
-   Резенова Н.А.
-   Павленко Н.С.</t>
-        </is>
-      </c>
-      <c r="E462" s="184" t="n"/>
-    </row>
-    <row r="463" customFormat="1" s="38">
-      <c r="A463" s="829" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Согласование, утверждение  Положений и должностных инструкций по новому ШР в полном объеме </t>
-        </is>
-      </c>
-      <c r="B463" s="805" t="n"/>
-      <c r="C463" s="805" t="n"/>
-      <c r="D463" s="805" t="n"/>
-      <c r="E463" s="747" t="n"/>
-    </row>
-    <row r="464" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A464" s="691" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Согласование ДИ по новой форме по всем должностям согласно ШР, подписание, передача на утверждение ГД </t>
-        </is>
-      </c>
-      <c r="B464" s="184" t="inlineStr">
-        <is>
-          <t>Наличие базы ДИ и ПП по организации в полном объеме</t>
-        </is>
-      </c>
-      <c r="C464" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства РФ</t>
-        </is>
-      </c>
-      <c r="D464" s="182" t="inlineStr">
-        <is>
-          <t>Еремина О.А.
-Козлова Ю.В.</t>
-        </is>
-      </c>
-      <c r="E464" s="184" t="n"/>
-    </row>
-    <row r="465" customFormat="1" s="38">
-      <c r="A465" s="829" t="inlineStr">
-        <is>
-          <t>Формирование  отчётности</t>
-        </is>
-      </c>
-      <c r="B465" s="805" t="n"/>
-      <c r="C465" s="805" t="n"/>
-      <c r="D465" s="805" t="n"/>
-      <c r="E465" s="747" t="n"/>
+      <c r="D465" s="182" t="inlineStr">
+        <is>
+          <t>Кавыза О.Г.</t>
+        </is>
+      </c>
+      <c r="E465" s="184" t="n"/>
     </row>
     <row r="466" customFormat="1" s="38">
-      <c r="A466" s="691" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отчет по статистике </t>
-        </is>
-      </c>
-      <c r="B466" s="184" t="inlineStr">
-        <is>
-          <t>П4 НЗ, ежеквартальный, за 3-й квартал 2026</t>
-        </is>
-      </c>
-      <c r="C466" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства РФ</t>
-        </is>
-      </c>
-      <c r="D466" s="182" t="inlineStr">
-        <is>
-          <t>Козлова Ю.В</t>
-        </is>
-      </c>
-      <c r="E466" s="184" t="n"/>
-    </row>
-    <row r="467" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A466" s="819" t="inlineStr">
+        <is>
+          <t>ОТ и ТБ</t>
+        </is>
+      </c>
+      <c r="B466" s="760" t="n"/>
+      <c r="C466" s="760" t="n"/>
+      <c r="D466" s="760" t="n"/>
+      <c r="E466" s="761" t="n"/>
+    </row>
+    <row r="467" ht="27.6" customFormat="1" customHeight="1" s="38">
       <c r="A467" s="691" t="inlineStr">
         <is>
-          <t>Отчёты в СФР штатные работники (прием/увольнение)</t>
+          <t>Создание отдела ОТ, ТБ, экологической безопасности</t>
         </is>
       </c>
       <c r="B467" s="184" t="inlineStr">
         <is>
-          <t>Отчёт в СФР  (по форме ЕФС-1 разд. 1.1.)  оформляется не позднее одного рабочего дня после даты издания приказов о  приеме, увольнении работников.</t>
+          <t>Комплектование штата, содание перечня работ до конца 2026г.</t>
         </is>
       </c>
       <c r="C467" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t> </t>
         </is>
       </c>
       <c r="D467" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В.
-   Резенова Н.А.
-   Козлова Ю.В.
-   Еремина О.А.</t>
+          <t>Пенский А.</t>
         </is>
       </c>
       <c r="E467" s="184" t="n"/>
     </row>
-    <row r="468" ht="82.8" customFormat="1" customHeight="1" s="38">
+    <row r="468" ht="27.6" customFormat="1" customHeight="1" s="38">
       <c r="A468" s="691" t="inlineStr">
         <is>
-          <t>Отчёты в СФР  штатные работники (переводы)</t>
+          <t>Создание плана работы отдела, показателей оценки результата</t>
         </is>
       </c>
       <c r="B468" s="184" t="inlineStr">
         <is>
-          <t>Отчёт в СФР  (по форме ЕФС-1 разд. 1.1.)  оформляется не позднее 25 числа месяца, следующего за отчетным месяцем издания приказов о  переводе работников. А так же иным мероприятиям предусмотренным законодательствам РФ.</t>
+          <t> </t>
         </is>
       </c>
       <c r="C468" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t> </t>
         </is>
       </c>
       <c r="D468" s="182" t="inlineStr">
         <is>
-          <t>Афонина Ю.В.
-   Резенова Н.А.
-   Козлова Ю.В.
-   Еремина О.А.</t>
+          <t>Пенский А.</t>
         </is>
       </c>
       <c r="E468" s="184" t="n"/>
@@ -26220,183 +26326,206 @@
     <row r="469" customFormat="1" s="38">
       <c r="A469" s="691" t="inlineStr">
         <is>
-          <t>Отчет по инвалидам</t>
+          <t>СОУТ</t>
         </is>
       </c>
       <c r="B469" s="184" t="inlineStr">
         <is>
-          <t xml:space="preserve">ежеквартальный </t>
+          <t> </t>
         </is>
       </c>
       <c r="C469" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ</t>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D469" s="182" t="inlineStr">
         <is>
-          <t>Козлова Ю.В.</t>
+          <t>Пенский А.</t>
         </is>
       </c>
       <c r="E469" s="184" t="n"/>
     </row>
     <row r="470" customFormat="1" s="38">
-      <c r="A470" s="829" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разработка (актуализация)  ЛНА, развитие процессов, создание  Базы знаний по кадрам </t>
-        </is>
-      </c>
-      <c r="B470" s="805" t="n"/>
-      <c r="C470" s="805" t="n"/>
-      <c r="D470" s="805" t="n"/>
-      <c r="E470" s="747" t="n"/>
-    </row>
-    <row r="471" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A470" s="691" t="inlineStr">
+        <is>
+          <t>ОПР</t>
+        </is>
+      </c>
+      <c r="B470" s="184" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C470" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства</t>
+        </is>
+      </c>
+      <c r="D470" s="182" t="inlineStr">
+        <is>
+          <t>Пенский А.</t>
+        </is>
+      </c>
+      <c r="E470" s="184" t="n"/>
+    </row>
+    <row r="471" customFormat="1" s="38">
       <c r="A471" s="691" t="inlineStr">
         <is>
-          <t>Внесение изменений в БП Командировки ГК</t>
+          <t>Автоматизация процессов</t>
         </is>
       </c>
       <c r="B471" s="184" t="inlineStr">
         <is>
-          <t>Дополнить размеры суточных по загранице суточными для поездок в Китай</t>
+          <t>Участие в проработке решений и их внедрение</t>
         </is>
       </c>
       <c r="C471" s="701" t="inlineStr">
         <is>
-          <t>Соблюдение законодательства РФ, оптимизация БП</t>
+          <t xml:space="preserve">Развитие процессов </t>
         </is>
       </c>
       <c r="D471" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Пенский А.</t>
         </is>
       </c>
       <c r="E471" s="184" t="n"/>
     </row>
-    <row r="472" ht="27.6" customFormat="1" customHeight="1" s="38">
+    <row r="472" ht="41.4" customFormat="1" customHeight="1" s="38">
       <c r="A472" s="691" t="inlineStr">
         <is>
-          <t>Автоматизация печатных форм приказов и договоров в 1С</t>
+          <t>Организация обучения по охране труда (программа А, Б, СИЗ, первая помощь) для работников рабочих профессий</t>
         </is>
       </c>
       <c r="B472" s="184" t="inlineStr">
         <is>
-          <t>В рамках подготовки к внедрению КЭДО</t>
+          <t> </t>
         </is>
       </c>
       <c r="C472" s="701" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D472" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.
-   Козлова Ю.В.</t>
+          <t>Айкешева А.К.</t>
         </is>
       </c>
       <c r="E472" s="184" t="n"/>
     </row>
-    <row r="473" ht="41.4" customFormat="1" customHeight="1" s="408">
+    <row r="473" ht="27.6" customFormat="1" customHeight="1" s="408">
       <c r="A473" s="691" t="inlineStr">
         <is>
-          <t>Изменение процессов взаимодействия между подразделениями</t>
+          <t>Разработка локальных нормативных актов по охране труда и экологии</t>
         </is>
       </c>
       <c r="B473" s="184" t="inlineStr">
         <is>
-          <t>Оптимизация взаимодействия между кадрами и бухгалтерией, разработка документооборота между кадрами и другими подразделениями</t>
+          <t>Приказы, ЛНД и т.д.</t>
         </is>
       </c>
       <c r="C473" s="701" t="inlineStr">
         <is>
-          <t>Оптимизация взаимодействия работников  подразделений и ОУП</t>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D473" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Айкешева А.К.</t>
         </is>
       </c>
       <c r="E473" s="184" t="n"/>
     </row>
-    <row r="474" ht="69" customFormat="1" customHeight="1" s="38">
+    <row r="474" ht="27.6" customFormat="1" customHeight="1" s="38">
       <c r="A474" s="691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подготовка методических материалов по кадрам </t>
+          <t>Разработка таблицы по нормам СИЗ (спец. одежды) по подразделениям и профессиям</t>
         </is>
       </c>
       <c r="B474" s="184" t="inlineStr">
         <is>
-          <t>Формирование Базы знаний по кадровым  направлениям (Прием, перевод, увольнение , пр.) . Подготовка Памяток для работников, шаблонов  СЗ, Заявлений, размещение в Базе - по основным мероприятиям</t>
+          <t> </t>
         </is>
       </c>
       <c r="C474" s="701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оптимизация взаимодействия работников  подразделений и ОУП.  Повышение уровня сервиса для персонала  </t>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D474" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Айкешева А.К.</t>
         </is>
       </c>
       <c r="E474" s="184" t="n"/>
     </row>
-    <row r="475" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A475" s="412" t="inlineStr">
-        <is>
-          <t>Оптимизация работы отделов Дирекции по персоналу</t>
-        </is>
-      </c>
-      <c r="B475" s="413" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C475" s="414" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D475" s="415" t="inlineStr">
-        <is>
-          <t>Еремина О.А.</t>
-        </is>
-      </c>
-      <c r="E475" s="413" t="n"/>
-    </row>
-    <row r="476" customFormat="1" s="38">
-      <c r="A476" s="829" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Работа с суммированным учетом РВ (в рамках Положения о СУРВ),  Графики работы подразделений с СУРВ, Табели подразделений </t>
-        </is>
-      </c>
-      <c r="B476" s="805" t="n"/>
-      <c r="C476" s="805" t="n"/>
-      <c r="D476" s="805" t="n"/>
-      <c r="E476" s="747" t="n"/>
-    </row>
-    <row r="477" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A477" s="410" t="inlineStr">
-        <is>
-          <t>Организация работы подразделений по графикам смен.  Анализ и актуализация графиков работы (смен)  работников. Подготовка приказов Приведение в соответствие ТД  работников</t>
-        </is>
-      </c>
-      <c r="B477" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение графиков производства. Разработка графиком для Отдела режима </t>
-        </is>
-      </c>
-      <c r="C477" s="727" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Организация деятельности подразделений, соблюдение требований ТК РФ </t>
+    <row r="475" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A475" s="691" t="inlineStr">
+        <is>
+          <t>Формирование комплектов документов по охране труда для обособленных подразделений</t>
+        </is>
+      </c>
+      <c r="B475" s="184" t="inlineStr">
+        <is>
+          <t>Инструкции ОТ, программы инструктажа, журналы инструктажа</t>
+        </is>
+      </c>
+      <c r="C475" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства</t>
+        </is>
+      </c>
+      <c r="D475" s="182" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.</t>
+        </is>
+      </c>
+      <c r="E475" s="184" t="n"/>
+    </row>
+    <row r="476" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A476" s="691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обучение работников по экологической безопасности </t>
+        </is>
+      </c>
+      <c r="B476" s="184" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C476" s="701" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D476" s="182" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E476" s="184" t="n"/>
+    </row>
+    <row r="477" customFormat="1" s="38">
+      <c r="A477" s="691" t="inlineStr">
+        <is>
+          <t>Инвентаризация отходов</t>
+        </is>
+      </c>
+      <c r="B477" s="184" t="inlineStr">
+        <is>
+          <t>Ведение договора, сбор данных</t>
+        </is>
+      </c>
+      <c r="C477" s="701" t="inlineStr">
+        <is>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D477" s="182" t="inlineStr">
         <is>
-          <t>Павленко Н.С.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E477" s="184" t="n"/>
@@ -26404,23 +26533,22 @@
     <row r="478" ht="27.6" customFormat="1" customHeight="1" s="38">
       <c r="A478" s="691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация работы с табелями </t>
+          <t>Подготовка и контроль по вывозу отходов в подразделениях</t>
         </is>
       </c>
       <c r="B478" s="184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Контроль, сопровождение оформления табелей </t>
+          <t>Сбор информации, учёт в журнале движения отходов</t>
         </is>
       </c>
       <c r="C478" s="701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация деятельности подразделений, соблюдение требований ТК РФ </t>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D478" s="182" t="inlineStr">
         <is>
-          <t>Руцкая В.В.
-   Павленко Н.С.</t>
+          <t>Батушин А.В.</t>
         </is>
       </c>
       <c r="E478" s="184" t="n"/>
@@ -26428,56 +26556,70 @@
     <row r="479" ht="27.6" customFormat="1" customHeight="1" s="38">
       <c r="A479" s="691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация работы с табелями </t>
+          <t>Контроль за соблюдением охраны труда и экологии в подразделениях</t>
         </is>
       </c>
       <c r="B479" s="184" t="inlineStr">
         <is>
-          <t>Назначение ответственных за ведение табелей Вемина по подразделениям</t>
+          <t> </t>
         </is>
       </c>
       <c r="C479" s="701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация деятельности подразделений, соблюдение требований ТК РФ </t>
+          <t>Соблюдение законодательства</t>
         </is>
       </c>
       <c r="D479" s="182" t="inlineStr">
         <is>
-          <t>Павленко Н.С.</t>
+          <t>Айкешева А.К.
+   Батушин А.В.</t>
         </is>
       </c>
       <c r="E479" s="184" t="n"/>
     </row>
-    <row r="480" customFormat="1" s="38">
-      <c r="A480" s="829" t="inlineStr">
-        <is>
-          <t>Новая организационная структура, штатное расписание компании</t>
-        </is>
-      </c>
-      <c r="B480" s="805" t="n"/>
-      <c r="C480" s="805" t="n"/>
-      <c r="D480" s="805" t="n"/>
-      <c r="E480" s="747" t="n"/>
-    </row>
-    <row r="481" ht="41.4" customFormat="1" customHeight="1" s="38">
+    <row r="480" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A480" s="691" t="inlineStr">
+        <is>
+          <t>Оплата и контроль счётов по охране труда и экологии</t>
+        </is>
+      </c>
+      <c r="B480" s="184" t="inlineStr">
+        <is>
+          <t>Договорная работы (Медкомиссия, вывоз отходов)</t>
+        </is>
+      </c>
+      <c r="C480" s="701" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D480" s="182" t="inlineStr">
+        <is>
+          <t>Айкешева А.К.
+   Батушин А.В.</t>
+        </is>
+      </c>
+      <c r="E480" s="184" t="n"/>
+    </row>
+    <row r="481" customFormat="1" s="38">
       <c r="A481" s="691" t="inlineStr">
         <is>
-          <t>Соблюдение нового штатного расписания и  ФОТ</t>
+          <t>Бюджетирование</t>
         </is>
       </c>
       <c r="B481" s="184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Контроль исполнения ФОТ/ШР.  Предоставление данных для приема на работу, переводов руководителям и в отдел подбора </t>
+          <t> </t>
         </is>
       </c>
       <c r="C481" s="701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация деятельности  компании </t>
+          <t> </t>
         </is>
       </c>
       <c r="D481" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Айкешева А.К.</t>
         </is>
       </c>
       <c r="E481" s="184" t="n"/>
@@ -26485,800 +26627,79 @@
     <row r="482" customFormat="1" s="38">
       <c r="A482" s="691" t="inlineStr">
         <is>
-          <t>Внесение изменений в 1С по новому  ШР</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="B482" s="184" t="inlineStr">
         <is>
-          <t>Согласование, внесение изменений в 1С</t>
+          <t> </t>
         </is>
       </c>
       <c r="C482" s="701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация деятельности  компании </t>
+          <t> </t>
         </is>
       </c>
       <c r="D482" s="182" t="inlineStr">
         <is>
-          <t>Еремина О.А.</t>
+          <t>Айкешева А.К.</t>
         </is>
       </c>
       <c r="E482" s="184" t="n"/>
     </row>
-    <row r="483" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A483" s="691" t="inlineStr">
-        <is>
-          <t>Проработка возможности реализации в 1С:ЗУП управленческой структуры и отчетности</t>
-        </is>
-      </c>
-      <c r="B483" s="184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Реализация упарвленческой структцуры и отчетности в целях учета функциональной принадлежности позиций штатного расписания и работников. </t>
-        </is>
-      </c>
-      <c r="C483" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Организация деятельности  компании </t>
-        </is>
-      </c>
-      <c r="D483" s="182" t="inlineStr">
-        <is>
-          <t>Еремина О.А.</t>
-        </is>
-      </c>
-      <c r="E483" s="184" t="n"/>
+    <row r="483" customFormat="1" s="38">
+      <c r="A483" s="830" t="inlineStr">
+        <is>
+          <t>Рекрутинг</t>
+        </is>
+      </c>
+      <c r="B483" s="760" t="n"/>
+      <c r="C483" s="760" t="n"/>
+      <c r="D483" s="760" t="n"/>
+      <c r="E483" s="760" t="n"/>
     </row>
     <row r="484" customFormat="1" s="38">
-      <c r="A484" s="829" t="inlineStr">
-        <is>
-          <t>Ведение воинского учёта и бронирования</t>
-        </is>
-      </c>
-      <c r="B484" s="805" t="n"/>
-      <c r="C484" s="805" t="n"/>
-      <c r="D484" s="805" t="n"/>
-      <c r="E484" s="747" t="n"/>
-    </row>
-    <row r="485" customFormat="1" s="38">
-      <c r="A485" s="691" t="inlineStr">
-        <is>
-          <t>Разъяснение правил воинского учета</t>
-        </is>
-      </c>
-      <c r="B485" s="184" t="inlineStr">
-        <is>
-          <t>При приеме на работу. Ведение журнала.</t>
-        </is>
-      </c>
-      <c r="C485" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D485" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E485" s="184" t="n"/>
-    </row>
-    <row r="486" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A486" s="691" t="inlineStr">
-        <is>
-          <t>Ведение карточек ф.10</t>
-        </is>
-      </c>
-      <c r="B486" s="184" t="inlineStr">
-        <is>
-          <t>При приеме, переводе, изменении данных, увольнении</t>
-        </is>
-      </c>
-      <c r="C486" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законожательства РФ.</t>
-        </is>
-      </c>
-      <c r="D486" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E486" s="184" t="n"/>
-    </row>
-    <row r="487" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A487" s="691" t="inlineStr">
-        <is>
-          <t>Сведения при приеме/увольнении/переводе/  изменении др. (Приложение № 2 к Положению о ВУ)</t>
-        </is>
-      </c>
-      <c r="B487" s="184" t="inlineStr">
-        <is>
-          <t>Направление в военный комиссариат по месту жительства работника</t>
-        </is>
-      </c>
-      <c r="C487" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D487" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E487" s="184" t="n"/>
-    </row>
-    <row r="488" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A488" s="691" t="inlineStr">
-        <is>
-          <t>Отчетность</t>
-        </is>
-      </c>
-      <c r="B488" s="184" t="inlineStr">
-        <is>
-          <t>Продление справки (с предоставлением карточки организации ф.18; ф.6 и ф.19) в районной комиссии по бронированию. Передача справки в военный комиссариат</t>
-        </is>
-      </c>
-      <c r="C488" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D488" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E488" s="184" t="n"/>
-    </row>
-    <row r="489" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A489" s="839" t="inlineStr">
-        <is>
-          <t>Ведение документации по бронированию</t>
-        </is>
-      </c>
-      <c r="B489" s="184" t="inlineStr">
-        <is>
-          <t>Подготовка  приказов о бронировании сотрудников</t>
-        </is>
-      </c>
-      <c r="C489" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D489" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E489" s="184" t="n"/>
-    </row>
-    <row r="490" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A490" s="754" t="n"/>
-      <c r="B490" s="184" t="inlineStr">
-        <is>
-          <t>Подготовка Выписок из приказа о бронировании сотрудников</t>
-        </is>
-      </c>
-      <c r="C490" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D490" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E490" s="184" t="n"/>
-    </row>
-    <row r="491" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A491" s="754" t="n"/>
-      <c r="B491" s="184" t="inlineStr">
-        <is>
-          <t>Оформление приказа о прекращении бронирования</t>
-        </is>
-      </c>
-      <c r="C491" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D491" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E491" s="184" t="n"/>
-    </row>
-    <row r="492" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A492" s="754" t="n"/>
-      <c r="B492" s="184" t="inlineStr">
-        <is>
-          <t>Оформление выписок из проекта приказа о прекращении бронировании</t>
-        </is>
-      </c>
-      <c r="C492" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D492" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E492" s="184" t="n"/>
-    </row>
-    <row r="493" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A493" s="753" t="n"/>
-      <c r="B493" s="184" t="inlineStr">
-        <is>
-          <t>Оформление сопроводительных писем к выпискам из приказов</t>
-        </is>
-      </c>
-      <c r="C493" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D493" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E493" s="184" t="n"/>
-    </row>
-    <row r="494" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A494" s="691" t="inlineStr">
-        <is>
-          <t>Подготовка листков сообщений</t>
-        </is>
-      </c>
-      <c r="B494" s="184" t="inlineStr">
-        <is>
-          <t>Документ выдается на руки сотрудники с целью посещения военкомата в связи с ихменением места жительства, состава семьи, образования и т.д.</t>
-        </is>
-      </c>
-      <c r="C494" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D494" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E494" s="184" t="n"/>
-    </row>
-    <row r="495" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A495" s="691" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подготовка направления для постановки на ВУ </t>
-        </is>
-      </c>
-      <c r="B495" s="184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Документ выдается на руки сотрудники с целью посещения военкомата для постановки на ВУ </t>
-        </is>
-      </c>
-      <c r="C495" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D495" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E495" s="184" t="n"/>
-    </row>
-    <row r="496" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A496" s="691" t="inlineStr">
-        <is>
-          <t>Ведение журналов</t>
-        </is>
-      </c>
-      <c r="B496" s="184" t="inlineStr">
-        <is>
-          <t>Журналы по работе, связанной с воинским учетом и бронированием.</t>
-        </is>
-      </c>
-      <c r="C496" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Соблюдение законодательства РФ. </t>
-        </is>
-      </c>
-      <c r="D496" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E496" s="184" t="n"/>
-    </row>
-    <row r="497" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A497" s="691" t="inlineStr">
-        <is>
-          <t>Автоматизация в 1С ведения данных по ВУ и бронированию</t>
-        </is>
-      </c>
-      <c r="B497" s="184" t="inlineStr">
-        <is>
-          <t>Внесение данных по бронированию в 1С: приказов, справок пр. документов</t>
-        </is>
-      </c>
-      <c r="C497" s="701" t="inlineStr">
-        <is>
-          <t>Организация деятельности подразделения</t>
-        </is>
-      </c>
-      <c r="D497" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E497" s="184" t="n"/>
-    </row>
-    <row r="498" customFormat="1" s="38">
-      <c r="A498" s="691" t="inlineStr">
-        <is>
-          <t>Подключение к ЛК Реестр повесток.рф</t>
-        </is>
-      </c>
-      <c r="B498" s="184" t="inlineStr">
-        <is>
-          <t>Подача установленных форм в электронном виде</t>
-        </is>
-      </c>
-      <c r="C498" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства РФ</t>
-        </is>
-      </c>
-      <c r="D498" s="182" t="inlineStr">
-        <is>
-          <t>Кавыза О.Г.</t>
-        </is>
-      </c>
-      <c r="E498" s="184" t="n"/>
-    </row>
-    <row r="499" customFormat="1" s="38">
-      <c r="A499" s="819" t="inlineStr">
-        <is>
-          <t>ОТ и ТБ</t>
-        </is>
-      </c>
-      <c r="B499" s="760" t="n"/>
-      <c r="C499" s="760" t="n"/>
-      <c r="D499" s="760" t="n"/>
-      <c r="E499" s="761" t="n"/>
-    </row>
-    <row r="500" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A500" s="691" t="inlineStr">
-        <is>
-          <t>Создание отдела ОТ, ТБ, экологической безопасности</t>
-        </is>
-      </c>
-      <c r="B500" s="184" t="inlineStr">
-        <is>
-          <t>Комплектование штата, содание перечня работ до конца 2026г.</t>
-        </is>
-      </c>
-      <c r="C500" s="701" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D500" s="182" t="inlineStr">
-        <is>
-          <t>Пенский А.</t>
-        </is>
-      </c>
-      <c r="E500" s="184" t="n"/>
-    </row>
-    <row r="501" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A501" s="691" t="inlineStr">
-        <is>
-          <t>Создание плана работы отдела, показателей оценки результата</t>
-        </is>
-      </c>
-      <c r="B501" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C501" s="701" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D501" s="182" t="inlineStr">
-        <is>
-          <t>Пенский А.</t>
-        </is>
-      </c>
-      <c r="E501" s="184" t="n"/>
-    </row>
-    <row r="502" customFormat="1" s="38">
-      <c r="A502" s="691" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="B502" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C502" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D502" s="182" t="inlineStr">
-        <is>
-          <t>Пенский А.</t>
-        </is>
-      </c>
-      <c r="E502" s="184" t="n"/>
-    </row>
-    <row r="503" customFormat="1" s="38">
-      <c r="A503" s="691" t="inlineStr">
-        <is>
-          <t>ОПР</t>
-        </is>
-      </c>
-      <c r="B503" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C503" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D503" s="182" t="inlineStr">
-        <is>
-          <t>Пенский А.</t>
-        </is>
-      </c>
-      <c r="E503" s="184" t="n"/>
-    </row>
-    <row r="504" customFormat="1" s="511">
-      <c r="A504" s="691" t="inlineStr">
-        <is>
-          <t>Автоматизация процессов</t>
-        </is>
-      </c>
-      <c r="B504" s="184" t="inlineStr">
-        <is>
-          <t>Участие в проработке решений и их внедрение</t>
-        </is>
-      </c>
-      <c r="C504" s="701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Развитие процессов </t>
-        </is>
-      </c>
-      <c r="D504" s="182" t="inlineStr">
-        <is>
-          <t>Пенский А.</t>
-        </is>
-      </c>
-      <c r="E504" s="184" t="n"/>
-    </row>
-    <row r="505" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A505" s="691" t="inlineStr">
-        <is>
-          <t>Организация обучения по охране труда (программа А, Б, СИЗ, первая помощь) для работников рабочих профессий</t>
-        </is>
-      </c>
-      <c r="B505" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C505" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D505" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E505" s="184" t="n"/>
-    </row>
-    <row r="506" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A506" s="691" t="inlineStr">
-        <is>
-          <t>Разработка локальных нормативных актов по охране труда и экологии</t>
-        </is>
-      </c>
-      <c r="B506" s="184" t="inlineStr">
-        <is>
-          <t>Приказы, ЛНД и т.д.</t>
-        </is>
-      </c>
-      <c r="C506" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D506" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E506" s="184" t="n"/>
-    </row>
-    <row r="507" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A507" s="691" t="inlineStr">
-        <is>
-          <t>Разработка таблицы по нормам СИЗ (спец. одежды) по подразделениям и профессиям</t>
-        </is>
-      </c>
-      <c r="B507" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C507" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D507" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E507" s="184" t="n"/>
-    </row>
-    <row r="508" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A508" s="691" t="inlineStr">
-        <is>
-          <t>Формирование комплектов документов по охране труда для обособленных подразделений</t>
-        </is>
-      </c>
-      <c r="B508" s="184" t="inlineStr">
-        <is>
-          <t>Инструкции ОТ, программы инструктажа, журналы инструктажа</t>
-        </is>
-      </c>
-      <c r="C508" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D508" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E508" s="184" t="n"/>
-    </row>
-    <row r="509" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A509" s="691" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Обучение работников по экологической безопасности </t>
-        </is>
-      </c>
-      <c r="B509" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C509" s="701" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D509" s="182" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E509" s="184" t="n"/>
-    </row>
-    <row r="510" customFormat="1" s="38">
-      <c r="A510" s="691" t="inlineStr">
-        <is>
-          <t>Инвентаризация отходов</t>
-        </is>
-      </c>
-      <c r="B510" s="184" t="inlineStr">
-        <is>
-          <t>Ведение договора, сбор данных</t>
-        </is>
-      </c>
-      <c r="C510" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D510" s="182" t="inlineStr">
-        <is>
-          <t>Батушин А.В.</t>
-        </is>
-      </c>
-      <c r="E510" s="184" t="n"/>
-    </row>
-    <row r="511" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A511" s="691" t="inlineStr">
-        <is>
-          <t>Подготовка и контроль по вывозу отходов в подразделениях</t>
-        </is>
-      </c>
-      <c r="B511" s="184" t="inlineStr">
-        <is>
-          <t>Сбор информации, учёт в журнале движения отходов</t>
-        </is>
-      </c>
-      <c r="C511" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D511" s="182" t="inlineStr">
-        <is>
-          <t>Батушин А.В.</t>
-        </is>
-      </c>
-      <c r="E511" s="184" t="n"/>
-    </row>
-    <row r="512" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A512" s="691" t="inlineStr">
-        <is>
-          <t>Контроль за соблюдением охраны труда и экологии в подразделениях</t>
-        </is>
-      </c>
-      <c r="B512" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C512" s="701" t="inlineStr">
-        <is>
-          <t>Соблюдение законодательства</t>
-        </is>
-      </c>
-      <c r="D512" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.
-   Батушин А.В.</t>
-        </is>
-      </c>
-      <c r="E512" s="184" t="n"/>
-    </row>
-    <row r="513" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A513" s="691" t="inlineStr">
-        <is>
-          <t>Оплата и контроль счётов по охране труда и экологии</t>
-        </is>
-      </c>
-      <c r="B513" s="184" t="inlineStr">
-        <is>
-          <t>Договорная работы (Медкомиссия, вывоз отходов)</t>
-        </is>
-      </c>
-      <c r="C513" s="701" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D513" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.
-   Батушин А.В.</t>
-        </is>
-      </c>
-      <c r="E513" s="184" t="n"/>
-    </row>
-    <row r="514" customFormat="1" s="38">
-      <c r="A514" s="691" t="inlineStr">
-        <is>
-          <t>Бюджетирование</t>
-        </is>
-      </c>
-      <c r="B514" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C514" s="701" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D514" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E514" s="184" t="n"/>
-    </row>
-    <row r="515" customFormat="1" s="38">
-      <c r="A515" s="691" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="B515" s="184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C515" s="701" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D515" s="182" t="inlineStr">
-        <is>
-          <t>Айкешева А.К.</t>
-        </is>
-      </c>
-      <c r="E515" s="184" t="n"/>
-    </row>
-    <row r="516" customFormat="1" s="38">
-      <c r="A516" s="830" t="inlineStr">
-        <is>
-          <t>Рекрутинг</t>
-        </is>
-      </c>
-      <c r="B516" s="760" t="n"/>
-      <c r="C516" s="760" t="n"/>
-      <c r="D516" s="760" t="n"/>
-      <c r="E516" s="760" t="n"/>
-    </row>
-    <row r="517" customFormat="1" s="38">
-      <c r="A517" s="404" t="inlineStr">
+      <c r="A484" s="404" t="inlineStr">
         <is>
           <t>Набор технологов в АИ СН</t>
         </is>
       </c>
-      <c r="B517" s="403" t="inlineStr">
+      <c r="B484" s="403" t="inlineStr">
         <is>
           <t>набор персонала на критичное направление</t>
         </is>
       </c>
-      <c r="C517" s="403" t="inlineStr">
+      <c r="C484" s="403" t="inlineStr">
         <is>
           <t>Укомплектование отдела</t>
         </is>
       </c>
-      <c r="D517" s="403" t="inlineStr">
+      <c r="D484" s="403" t="inlineStr">
         <is>
           <t>Осипова В.
    Блинова А.
    Новикова Ю.</t>
         </is>
       </c>
-      <c r="E517" s="444" t="n"/>
-    </row>
-    <row r="518" ht="72" customFormat="1" customHeight="1" s="38">
-      <c r="A518" s="447" t="inlineStr">
+      <c r="E484" s="444" t="n"/>
+    </row>
+    <row r="485" ht="72" customFormat="1" customHeight="1" s="38">
+      <c r="A485" s="447" t="inlineStr">
         <is>
           <t>Внешний кадроый резерв</t>
         </is>
       </c>
-      <c r="B518" s="448" t="inlineStr">
+      <c r="B485" s="448" t="inlineStr">
         <is>
           <t>Кадровый резерв, который может потребоваться при  расширении производства (теплая база кандидатов)</t>
         </is>
       </c>
-      <c r="C518" s="449" t="inlineStr">
+      <c r="C485" s="449" t="inlineStr">
         <is>
           <t>Масштабирование производства</t>
         </is>
       </c>
-      <c r="D518" s="449" t="inlineStr">
+      <c r="D485" s="449" t="inlineStr">
         <is>
           <t>Осипова В.
 Шибалкова Ю.
@@ -27287,95 +26708,95 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E518" s="449" t="n"/>
-    </row>
-    <row r="519" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A519" s="706" t="inlineStr">
+      <c r="E485" s="449" t="n"/>
+    </row>
+    <row r="486" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A486" s="706" t="inlineStr">
         <is>
           <t>Актуализация плана подбора на квартал</t>
         </is>
       </c>
-      <c r="B519" s="184" t="inlineStr">
+      <c r="B486" s="184" t="inlineStr">
         <is>
           <t>Вычитка всех вакансий, актуализация плана с руководителями, корректировки в ХФ и на HH.ru</t>
         </is>
       </c>
-      <c r="C519" s="182" t="inlineStr">
+      <c r="C486" s="182" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D519" s="182" t="inlineStr">
+      <c r="D486" s="182" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.,</t>
         </is>
       </c>
-      <c r="E519" s="181" t="n"/>
-    </row>
-    <row r="520" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A520" s="840" t="inlineStr">
+      <c r="E486" s="181" t="n"/>
+    </row>
+    <row r="487" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A487" s="840" t="inlineStr">
         <is>
           <t xml:space="preserve">Организация и контроль работы по проверке соискателей </t>
         </is>
       </c>
-      <c r="B520" s="195" t="inlineStr">
+      <c r="B487" s="195" t="inlineStr">
         <is>
           <t>Проверка кандидатов на различного вида задолженности и наличие ЮР лиц и ИП в системе Кронос</t>
         </is>
       </c>
-      <c r="C520" s="195" t="inlineStr">
+      <c r="C487" s="195" t="inlineStr">
         <is>
           <t>Проверка</t>
         </is>
       </c>
-      <c r="D520" s="195" t="inlineStr">
+      <c r="D487" s="195" t="inlineStr">
         <is>
           <t xml:space="preserve">Ковалева Е.
 Осипова В.
 </t>
         </is>
       </c>
-      <c r="E520" s="195" t="n"/>
-    </row>
-    <row r="521" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A521" s="841" t="n"/>
-      <c r="B521" s="196" t="inlineStr">
+      <c r="E487" s="195" t="n"/>
+    </row>
+    <row r="488" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A488" s="841" t="n"/>
+      <c r="B488" s="196" t="inlineStr">
         <is>
           <t xml:space="preserve">Точечные консультации с внутренней СБ по спорным вопросам проверок у кандидатов </t>
         </is>
       </c>
-      <c r="C521" s="197" t="inlineStr">
+      <c r="C488" s="197" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D521" s="198" t="inlineStr">
+      <c r="D488" s="198" t="inlineStr">
         <is>
           <t xml:space="preserve">Шибалкова Ю. 
 Ковалева Е.
 </t>
         </is>
       </c>
-      <c r="E521" s="199" t="n"/>
-    </row>
-    <row r="522" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A522" s="690" t="inlineStr">
+      <c r="E488" s="199" t="n"/>
+    </row>
+    <row r="489" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A489" s="690" t="inlineStr">
         <is>
           <t>Предварительные мед.осмотры</t>
         </is>
       </c>
-      <c r="B522" s="65" t="inlineStr">
+      <c r="B489" s="65" t="inlineStr">
         <is>
           <t>Направление на предварительные мед. осмотры</t>
         </is>
       </c>
-      <c r="C522" s="185" t="inlineStr">
+      <c r="C489" s="185" t="inlineStr">
         <is>
           <t>Проверка перед трудоустройством</t>
         </is>
       </c>
-      <c r="D522" s="186" t="inlineStr">
+      <c r="D489" s="186" t="inlineStr">
         <is>
           <t>Ковалева Е.
 Блинова А. 
@@ -27383,49 +26804,49 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E522" s="182" t="n"/>
-    </row>
-    <row r="523" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A523" s="71" t="inlineStr">
+      <c r="E489" s="182" t="n"/>
+    </row>
+    <row r="490" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A490" s="71" t="inlineStr">
         <is>
           <t>Сбор рекомендаций с прошлых мест работ кандидатов</t>
         </is>
       </c>
-      <c r="B523" s="184" t="inlineStr">
+      <c r="B490" s="184" t="inlineStr">
         <is>
           <t>Для руководящих и точечных должностей по запросу собираем рекомендации по кандидату перед выставлением оффера</t>
         </is>
       </c>
-      <c r="C523" s="186" t="inlineStr">
+      <c r="C490" s="186" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D523" s="182" t="inlineStr">
+      <c r="D490" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.                              Блинова А.И</t>
         </is>
       </c>
-      <c r="E523" s="186" t="n"/>
-    </row>
-    <row r="524" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A524" s="691" t="inlineStr">
+      <c r="E490" s="186" t="n"/>
+    </row>
+    <row r="491" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A491" s="691" t="inlineStr">
         <is>
           <t>Мониторинг рынка труда</t>
         </is>
       </c>
-      <c r="B524" s="184" t="inlineStr">
+      <c r="B491" s="184" t="inlineStr">
         <is>
           <t>Сбор и отражение в табличной форме данных</t>
         </is>
       </c>
-      <c r="C524" s="182" t="inlineStr">
+      <c r="C491" s="182" t="inlineStr">
         <is>
           <t>Оценка ситуации на рынке труда для корректировки кадровой политики</t>
         </is>
       </c>
-      <c r="D524" s="181" t="inlineStr">
+      <c r="D491" s="181" t="inlineStr">
         <is>
           <t>Осипова В.
 Блинова А.
@@ -27434,25 +26855,25 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E524" s="182" t="n"/>
-    </row>
-    <row r="525" ht="96.59999999999999" customFormat="1" customHeight="1" s="38">
-      <c r="A525" s="691" t="inlineStr">
+      <c r="E491" s="182" t="n"/>
+    </row>
+    <row r="492" ht="96.59999999999999" customFormat="1" customHeight="1" s="38">
+      <c r="A492" s="691" t="inlineStr">
         <is>
           <t>Отчетность еженедельная/квартальная</t>
         </is>
       </c>
-      <c r="B525" s="191" t="inlineStr">
+      <c r="B492" s="191" t="inlineStr">
         <is>
           <t>Заполнение форм отчетности</t>
         </is>
       </c>
-      <c r="C525" s="193" t="inlineStr">
+      <c r="C492" s="193" t="inlineStr">
         <is>
           <t>Выполнение плана подбора</t>
         </is>
       </c>
-      <c r="D525" s="193" t="inlineStr">
+      <c r="D492" s="193" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.,
@@ -27463,25 +26884,25 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E525" s="193" t="n"/>
-    </row>
-    <row r="526" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A526" s="200" t="inlineStr">
+      <c r="E492" s="193" t="n"/>
+    </row>
+    <row r="493" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A493" s="200" t="inlineStr">
         <is>
           <t>Реферальная программа</t>
         </is>
       </c>
-      <c r="B526" s="201" t="inlineStr">
+      <c r="B493" s="201" t="inlineStr">
         <is>
           <t>Отслеживание окончания ИС сотрудников по рекомендации</t>
         </is>
       </c>
-      <c r="C526" s="202" t="inlineStr">
+      <c r="C493" s="202" t="inlineStr">
         <is>
           <t>Увеличение воронки кандидатов, развитие HR бренда работодателя</t>
         </is>
       </c>
-      <c r="D526" s="202" t="inlineStr">
+      <c r="D493" s="202" t="inlineStr">
         <is>
           <t>Осипова В.,
 Шибалкова Ю. 
@@ -27490,107 +26911,107 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E526" s="202" t="n"/>
-    </row>
-    <row r="527" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A527" s="45" t="inlineStr">
+      <c r="E493" s="202" t="n"/>
+    </row>
+    <row r="494" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A494" s="45" t="inlineStr">
         <is>
           <t>Обучение по подбору персонала для руководителей</t>
         </is>
       </c>
-      <c r="B527" s="45" t="inlineStr">
+      <c r="B494" s="45" t="inlineStr">
         <is>
           <t>Проведение обучение</t>
         </is>
       </c>
-      <c r="C527" s="46" t="inlineStr">
+      <c r="C494" s="46" t="inlineStr">
         <is>
           <t>Повышение качества подбора персонала</t>
         </is>
       </c>
-      <c r="D527" s="46" t="inlineStr">
+      <c r="D494" s="46" t="inlineStr">
         <is>
           <t>Новикова Ю.
 Аншакова И.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E527" s="46" t="n"/>
-    </row>
-    <row r="528" customFormat="1" s="38">
-      <c r="A528" s="45" t="inlineStr">
+      <c r="E494" s="46" t="n"/>
+    </row>
+    <row r="495" customFormat="1" s="38">
+      <c r="A495" s="45" t="inlineStr">
         <is>
           <t>Планирование подбора на 2027 год</t>
         </is>
       </c>
-      <c r="B528" s="45" t="inlineStr">
+      <c r="B495" s="45" t="inlineStr">
         <is>
           <t>Сбор данных по подразделениям</t>
         </is>
       </c>
-      <c r="C528" s="46" t="inlineStr">
+      <c r="C495" s="46" t="inlineStr">
         <is>
           <t>Планирование 2027 год</t>
         </is>
       </c>
-      <c r="D528" s="46" t="inlineStr">
+      <c r="D495" s="46" t="inlineStr">
         <is>
           <t>Осипова В.Г.</t>
         </is>
       </c>
-      <c r="E528" s="46" t="n"/>
-    </row>
-    <row r="529" customFormat="1" s="38">
-      <c r="A529" s="830" t="inlineStr">
+      <c r="E495" s="46" t="n"/>
+    </row>
+    <row r="496" customFormat="1" s="38">
+      <c r="A496" s="830" t="inlineStr">
         <is>
           <t>Адаптация</t>
         </is>
       </c>
-      <c r="B529" s="760" t="n"/>
-      <c r="C529" s="760" t="n"/>
-      <c r="D529" s="760" t="n"/>
-      <c r="E529" s="760" t="n"/>
-    </row>
-    <row r="530" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A530" s="370" t="inlineStr">
+      <c r="B496" s="760" t="n"/>
+      <c r="C496" s="760" t="n"/>
+      <c r="D496" s="760" t="n"/>
+      <c r="E496" s="760" t="n"/>
+    </row>
+    <row r="497" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A497" s="370" t="inlineStr">
         <is>
           <t>Переезд в Руднево</t>
         </is>
       </c>
-      <c r="B530" s="371" t="inlineStr">
+      <c r="B497" s="371" t="inlineStr">
         <is>
           <t>Организация доставки сотрудников на площадку, организация питания, предложения п обустройству офиса, бытовых условий.</t>
         </is>
       </c>
-      <c r="C530" s="371" t="inlineStr">
+      <c r="C497" s="371" t="inlineStr">
         <is>
           <t>Организация комфортных условий труда для сотрудников</t>
         </is>
       </c>
-      <c r="D530" s="373" t="inlineStr">
+      <c r="D497" s="373" t="inlineStr">
         <is>
           <t>Пенский А.</t>
         </is>
       </c>
-      <c r="E530" s="423" t="n"/>
-    </row>
-    <row r="531" ht="82.8" customFormat="1" customHeight="1" s="38">
-      <c r="A531" s="740" t="inlineStr">
+      <c r="E497" s="423" t="n"/>
+    </row>
+    <row r="498" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A498" s="740" t="inlineStr">
         <is>
           <t>Онбординг</t>
         </is>
       </c>
-      <c r="B531" s="706" t="inlineStr">
+      <c r="B498" s="706" t="inlineStr">
         <is>
           <t>Проведение краткой экскурсии для новых сотрудников и выдача Welcome Kit, знакомство с руководителем</t>
         </is>
       </c>
-      <c r="C531" s="178" t="inlineStr">
+      <c r="C498" s="178" t="inlineStr">
         <is>
           <t>Адаптация новичков, снижение времени на включение в работу, снижение текучести.</t>
         </is>
       </c>
-      <c r="D531" s="178" t="inlineStr">
+      <c r="D498" s="178" t="inlineStr">
         <is>
           <t>Осипова В.
 Шибалкова Ю. 
@@ -27600,45 +27021,45 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E531" s="181" t="n"/>
-    </row>
-    <row r="532" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A532" s="761" t="n"/>
-      <c r="B532" s="191" t="inlineStr">
+      <c r="E498" s="181" t="n"/>
+    </row>
+    <row r="499" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A499" s="761" t="n"/>
+      <c r="B499" s="191" t="inlineStr">
         <is>
           <t>Создание приветственной страницы для новых сотрудников, аналогично ЦТП</t>
         </is>
       </c>
-      <c r="C532" s="193" t="inlineStr">
+      <c r="C499" s="193" t="inlineStr">
         <is>
           <t>Адаптация новичков, снижение времени на включение в работу, снижение текучести.</t>
         </is>
       </c>
-      <c r="D532" s="193" t="inlineStr">
+      <c r="D499" s="193" t="inlineStr">
         <is>
           <t>Осипова В.
 Котов И.</t>
         </is>
       </c>
-      <c r="E532" s="193" t="n"/>
-    </row>
-    <row r="533" ht="69" customFormat="1" customHeight="1" s="38">
-      <c r="A533" s="701" t="inlineStr">
+      <c r="E499" s="193" t="n"/>
+    </row>
+    <row r="500" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A500" s="701" t="inlineStr">
         <is>
           <t>Аттестация</t>
         </is>
       </c>
-      <c r="B533" s="191" t="inlineStr">
+      <c r="B500" s="191" t="inlineStr">
         <is>
           <t>Проведение аттестации действующих сотрудников для повышения категории/разряда и уровня заработной платы, в соответствии с ШР</t>
         </is>
       </c>
-      <c r="C533" s="193" t="inlineStr">
+      <c r="C500" s="193" t="inlineStr">
         <is>
           <t>Повышение категорий и разрядов действующих сотрудников</t>
         </is>
       </c>
-      <c r="D533" s="193" t="inlineStr">
+      <c r="D500" s="193" t="inlineStr">
         <is>
           <t>Осипова В.
 Шибалкова Ю.
@@ -27647,26 +27068,26 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E533" s="193" t="n"/>
-    </row>
-    <row r="534" ht="55.2" customFormat="1" customHeight="1" s="38">
-      <c r="A534" s="691" t="inlineStr">
+      <c r="E500" s="193" t="n"/>
+    </row>
+    <row r="501" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A501" s="691" t="inlineStr">
         <is>
           <t>Общение по результатам ИС</t>
         </is>
       </c>
-      <c r="B534" s="701" t="inlineStr">
+      <c r="B501" s="701" t="inlineStr">
         <is>
           <t>Встречи с сотрудниками на ИС и во время ИС
 Подготовка чек-листа для прошедших ИС и шаблона СЗ для изменений по результатам ИС</t>
         </is>
       </c>
-      <c r="C534" s="181" t="inlineStr">
+      <c r="C501" s="181" t="inlineStr">
         <is>
           <t>Мониторинг состояния новичков на ИС, снижение текучести персонала, обсуждение дальнейшего развития</t>
         </is>
       </c>
-      <c r="D534" s="181" t="inlineStr">
+      <c r="D501" s="181" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -27674,259 +27095,259 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E534" s="181" t="n"/>
-    </row>
-    <row r="535" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A535" s="440" t="inlineStr">
+      <c r="E501" s="181" t="n"/>
+    </row>
+    <row r="502" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A502" s="440" t="inlineStr">
         <is>
           <t>Общение по результатам ИС/работы - переговоры по увольнению сотрудника</t>
         </is>
       </c>
-      <c r="B535" s="441" t="inlineStr">
+      <c r="B502" s="441" t="inlineStr">
         <is>
           <t>Встреча с сотрудником на протяжении ИС, с проблемными зонами</t>
         </is>
       </c>
-      <c r="C535" s="442" t="inlineStr">
+      <c r="C502" s="442" t="inlineStr">
         <is>
           <t>Повышение эффективности команды, "отсев" сотрудников, которые не устраивают работодателя</t>
         </is>
       </c>
-      <c r="D535" s="442" t="inlineStr">
+      <c r="D502" s="442" t="inlineStr">
         <is>
           <t>Осипова В.
 Ковалева Е.
 Исматова В.</t>
         </is>
       </c>
-      <c r="E535" s="442" t="n"/>
-    </row>
-    <row r="536" customFormat="1" s="38">
-      <c r="A536" s="843" t="inlineStr">
+      <c r="E502" s="442" t="n"/>
+    </row>
+    <row r="503" customFormat="1" s="38">
+      <c r="A503" s="843" t="inlineStr">
         <is>
           <t>Материальная и не материальная мотивация</t>
         </is>
       </c>
-      <c r="B536" s="805" t="n"/>
-      <c r="C536" s="805" t="n"/>
-      <c r="D536" s="805" t="n"/>
-      <c r="E536" s="747" t="n"/>
-    </row>
-    <row r="537" customFormat="1" s="38">
-      <c r="A537" s="410" t="inlineStr">
+      <c r="B503" s="805" t="n"/>
+      <c r="C503" s="805" t="n"/>
+      <c r="D503" s="805" t="n"/>
+      <c r="E503" s="747" t="n"/>
+    </row>
+    <row r="504" customFormat="1" s="511">
+      <c r="A504" s="410" t="inlineStr">
         <is>
           <t>Питание сотрудников</t>
         </is>
       </c>
-      <c r="B537" s="410" t="inlineStr">
+      <c r="B504" s="410" t="inlineStr">
         <is>
           <t>Сопровождение процесса, решение проблем</t>
         </is>
       </c>
-      <c r="C537" s="443" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D537" s="443" t="inlineStr">
+      <c r="C504" s="443" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D504" s="443" t="inlineStr">
         <is>
           <t>Пенский А.К.</t>
         </is>
       </c>
-      <c r="E537" s="443" t="n"/>
-    </row>
-    <row r="538" ht="27.6" customFormat="1" customHeight="1" s="38">
-      <c r="A538" s="727" t="inlineStr">
+      <c r="E504" s="443" t="n"/>
+    </row>
+    <row r="505" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A505" s="727" t="inlineStr">
         <is>
           <t>ДМС</t>
         </is>
       </c>
-      <c r="B538" s="727" t="inlineStr">
+      <c r="B505" s="727" t="inlineStr">
         <is>
           <t>Подключение сотрудников со сроком работы от 6 месяцев</t>
         </is>
       </c>
-      <c r="C538" s="443" t="inlineStr">
+      <c r="C505" s="443" t="inlineStr">
         <is>
           <t>Нематериальная мотивация</t>
         </is>
       </c>
-      <c r="D538" s="443" t="inlineStr">
+      <c r="D505" s="443" t="inlineStr">
         <is>
           <t>Осипова В. 
 Блинова А.И.</t>
         </is>
       </c>
-      <c r="E538" s="443" t="n"/>
-    </row>
-    <row r="539" ht="41.4" customFormat="1" customHeight="1" s="38">
-      <c r="A539" s="706" t="inlineStr">
+      <c r="E505" s="443" t="n"/>
+    </row>
+    <row r="506" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A506" s="706" t="inlineStr">
         <is>
           <t>Подписка на журнал Кадровое дело</t>
         </is>
       </c>
-      <c r="B539" s="701" t="inlineStr">
+      <c r="B506" s="701" t="inlineStr">
         <is>
           <t>Оформление подписки, рассылка ежемесечных выпусков</t>
         </is>
       </c>
-      <c r="C539" s="182" t="inlineStr">
+      <c r="C506" s="182" t="inlineStr">
         <is>
           <t>Рассылка коллегам из HR отдела и ОУП свежих выпусков журнала, актуальных статей</t>
         </is>
       </c>
-      <c r="D539" s="182" t="inlineStr">
+      <c r="D506" s="182" t="inlineStr">
         <is>
           <t xml:space="preserve">Шибалкова Ю. </t>
         </is>
       </c>
-      <c r="E539" s="182" t="n"/>
-    </row>
-    <row r="540" ht="27.6" customHeight="1">
-      <c r="A540" s="190" t="inlineStr">
+      <c r="E506" s="182" t="n"/>
+    </row>
+    <row r="507" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A507" s="190" t="inlineStr">
         <is>
           <t>Реализация плана обучения персонала</t>
         </is>
       </c>
-      <c r="B540" s="191" t="inlineStr">
+      <c r="B507" s="191" t="inlineStr">
         <is>
           <t>План обучения согласован - актуализация планов на квартал, организация курсов</t>
         </is>
       </c>
-      <c r="C540" s="193" t="inlineStr">
+      <c r="C507" s="193" t="inlineStr">
         <is>
           <t>Повышение компетенций сотрудников по профильным направлениям</t>
         </is>
       </c>
-      <c r="D540" s="193" t="inlineStr">
+      <c r="D507" s="193" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В. 
 Шибалкова Ю. </t>
         </is>
       </c>
-      <c r="E540" s="193" t="n"/>
-    </row>
-    <row r="541" ht="55.2" customHeight="1">
-      <c r="A541" s="405" t="inlineStr">
+      <c r="E507" s="193" t="n"/>
+    </row>
+    <row r="508" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A508" s="405" t="inlineStr">
         <is>
           <t>Кадровый резерв</t>
         </is>
       </c>
-      <c r="B541" s="406" t="inlineStr">
+      <c r="B508" s="406" t="inlineStr">
         <is>
           <t>Концепция, начало проекта</t>
         </is>
       </c>
-      <c r="C541" s="407" t="inlineStr">
+      <c r="C508" s="407" t="inlineStr">
         <is>
           <t>Проработка дорожной карты проекта
 Старт проекта по созданию внутреннего кадрового резерва из разных блоков компании (ИТР, пр-во, АУП)</t>
         </is>
       </c>
-      <c r="D541" s="407" t="inlineStr">
+      <c r="D508" s="407" t="inlineStr">
         <is>
           <t>Осипова В.</t>
         </is>
       </c>
-      <c r="E541" s="193" t="n"/>
-    </row>
-    <row r="542" ht="55.2" customHeight="1">
-      <c r="A542" s="405" t="inlineStr">
+      <c r="E508" s="193" t="n"/>
+    </row>
+    <row r="509" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A509" s="405" t="inlineStr">
         <is>
           <t>Договоры на практику (студенты по рекомендации наших сотрудников, закрытие учебной практики нашим сотрудникам)</t>
         </is>
       </c>
-      <c r="B542" s="406" t="inlineStr">
+      <c r="B509" s="406" t="inlineStr">
         <is>
           <t>Проведение практики</t>
         </is>
       </c>
-      <c r="C542" s="407" t="inlineStr">
+      <c r="C509" s="407" t="inlineStr">
         <is>
           <t>Предоставление практики студентам</t>
         </is>
       </c>
-      <c r="D542" s="407" t="inlineStr">
+      <c r="D509" s="407" t="inlineStr">
         <is>
           <t>Осипова В.</t>
         </is>
       </c>
-      <c r="E542" s="193" t="n"/>
-    </row>
-    <row r="543" ht="41.4" customHeight="1">
-      <c r="A543" s="405" t="inlineStr">
+      <c r="E509" s="193" t="n"/>
+    </row>
+    <row r="510" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A510" s="405" t="inlineStr">
         <is>
           <t>Мероприятие для сотрудников 10+ лет</t>
         </is>
       </c>
-      <c r="B543" s="406" t="n"/>
-      <c r="C543" s="407" t="inlineStr">
+      <c r="B510" s="406" t="n"/>
+      <c r="C510" s="407" t="inlineStr">
         <is>
           <t>Повышение лояльности персонала</t>
         </is>
       </c>
-      <c r="D543" s="407" t="inlineStr">
+      <c r="D510" s="407" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.
 Шибалкова Ю.</t>
         </is>
       </c>
-      <c r="E543" s="193" t="n"/>
-    </row>
-    <row r="544">
-      <c r="A544" s="825" t="inlineStr">
+      <c r="E510" s="193" t="n"/>
+    </row>
+    <row r="511" customFormat="1" s="38">
+      <c r="A511" s="825" t="inlineStr">
         <is>
           <t>Развитие  HR-бренда</t>
         </is>
       </c>
-      <c r="B544" s="805" t="n"/>
-      <c r="C544" s="805" t="n"/>
-      <c r="D544" s="805" t="n"/>
-      <c r="E544" s="747" t="n"/>
-    </row>
-    <row r="545" ht="55.2" customHeight="1">
-      <c r="A545" s="405" t="inlineStr">
+      <c r="B511" s="805" t="n"/>
+      <c r="C511" s="805" t="n"/>
+      <c r="D511" s="805" t="n"/>
+      <c r="E511" s="747" t="n"/>
+    </row>
+    <row r="512" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A512" s="405" t="inlineStr">
         <is>
           <t>Happy Job</t>
         </is>
       </c>
-      <c r="B545" s="406" t="inlineStr">
+      <c r="B512" s="406" t="inlineStr">
         <is>
           <t>Органиация,проведение встреч с руководителями/сотрудниками подразделений по результатам опроса вовлеченности персонала Happy Job</t>
         </is>
       </c>
-      <c r="C545" s="407" t="inlineStr">
+      <c r="C512" s="407" t="inlineStr">
         <is>
           <t>Повышение показателей вовлеченности и лояльности</t>
         </is>
       </c>
-      <c r="D545" s="409" t="inlineStr">
+      <c r="D512" s="409" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.Г.</t>
         </is>
       </c>
-      <c r="E545" s="407" t="n"/>
-    </row>
-    <row r="546" ht="55.2" customHeight="1">
-      <c r="A546" s="706" t="inlineStr">
+      <c r="E512" s="407" t="n"/>
+    </row>
+    <row r="513" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A513" s="706" t="inlineStr">
         <is>
           <t>Встречи с сотрудниками по запросу от руководителей/размещенному резюме/exit-интервью</t>
         </is>
       </c>
-      <c r="B546" s="701" t="inlineStr">
+      <c r="B513" s="701" t="inlineStr">
         <is>
           <t xml:space="preserve">По запросу
 </t>
         </is>
       </c>
-      <c r="C546" s="181" t="inlineStr">
+      <c r="C513" s="181" t="inlineStr">
         <is>
           <t>Сбор информации о причинах увольнений и проблемах компании для проработки и устранения проблем</t>
         </is>
       </c>
-      <c r="D546" s="182" t="inlineStr">
+      <c r="D513" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -27934,64 +27355,64 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E546" s="182" t="n"/>
-    </row>
-    <row r="547" ht="55.2" customHeight="1">
-      <c r="A547" s="833" t="inlineStr">
+      <c r="E513" s="182" t="n"/>
+    </row>
+    <row r="514" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A514" s="833" t="inlineStr">
         <is>
           <t>Поздравления с ДР сотрудников</t>
         </is>
       </c>
-      <c r="B547" s="701" t="inlineStr">
+      <c r="B514" s="701" t="inlineStr">
         <is>
           <t xml:space="preserve">Актуализация списков именинников на будущий месяц, сбор фотографий для поздравлений. Сбор/отправка в филиалы подарков на ДР для сотрудников </t>
         </is>
       </c>
-      <c r="C547" s="834" t="inlineStr">
+      <c r="C514" s="834" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D547" s="181" t="inlineStr">
+      <c r="D514" s="181" t="inlineStr">
         <is>
           <t>Шибалкова Ю. Котов И.</t>
         </is>
       </c>
-      <c r="E547" s="181" t="n"/>
-    </row>
-    <row r="548" ht="27.6" customHeight="1">
-      <c r="A548" s="753" t="n"/>
-      <c r="B548" s="701" t="inlineStr">
+      <c r="E514" s="181" t="n"/>
+    </row>
+    <row r="515" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A515" s="753" t="n"/>
+      <c r="B515" s="701" t="inlineStr">
         <is>
           <t>Составление, подписание приказов, списков, ведомостей, договоров дарения на подарки</t>
         </is>
       </c>
-      <c r="C548" s="753" t="n"/>
-      <c r="D548" s="181" t="inlineStr">
+      <c r="C515" s="753" t="n"/>
+      <c r="D515" s="181" t="inlineStr">
         <is>
           <t>Котов И.
 Исматова В.</t>
         </is>
       </c>
-      <c r="E548" s="181" t="n"/>
-    </row>
-    <row r="549" ht="55.2" customHeight="1">
-      <c r="A549" s="508" t="inlineStr">
+      <c r="E515" s="181" t="n"/>
+    </row>
+    <row r="516" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A516" s="508" t="inlineStr">
         <is>
           <t>Работа с СУЗами, ВУЗами, ярмарки вакансий</t>
         </is>
       </c>
-      <c r="B549" s="509" t="inlineStr">
+      <c r="B516" s="509" t="inlineStr">
         <is>
           <t>Актуализация информации по сотрудничеству, участие в ярмарках вакансий</t>
         </is>
       </c>
-      <c r="C549" s="510" t="inlineStr">
+      <c r="C516" s="510" t="inlineStr">
         <is>
           <t>Привлечь молодых специалистов на открытые вакансии , повышение узнаваемости бренда АИ СН</t>
         </is>
       </c>
-      <c r="D549" s="510" t="inlineStr">
+      <c r="D516" s="510" t="inlineStr">
         <is>
           <t>Осипова В.,
 Исматова В.
@@ -27999,59 +27420,59 @@
 Блинова А.</t>
         </is>
       </c>
-      <c r="E549" s="510" t="n"/>
-    </row>
-    <row r="550">
-      <c r="A550" s="825" t="inlineStr">
+      <c r="E516" s="510" t="n"/>
+    </row>
+    <row r="517" customFormat="1" s="38">
+      <c r="A517" s="825" t="inlineStr">
         <is>
           <t>Автоматизация процессов и аналитика</t>
         </is>
       </c>
-      <c r="B550" s="805" t="n"/>
-      <c r="C550" s="805" t="n"/>
-      <c r="D550" s="805" t="n"/>
-      <c r="E550" s="747" t="n"/>
-    </row>
-    <row r="551" ht="41.4" customHeight="1">
-      <c r="A551" s="691" t="inlineStr">
+      <c r="B517" s="805" t="n"/>
+      <c r="C517" s="805" t="n"/>
+      <c r="D517" s="805" t="n"/>
+      <c r="E517" s="747" t="n"/>
+    </row>
+    <row r="518" ht="41.4" customFormat="1" customHeight="1" s="38">
+      <c r="A518" s="691" t="inlineStr">
         <is>
           <t>Аудит Хантфлоу</t>
         </is>
       </c>
-      <c r="B551" s="691" t="inlineStr">
+      <c r="B518" s="691" t="inlineStr">
         <is>
           <t>Проведение аудит по качеству ведения базы согласно нашей инструкции, фиксация замечаний и дальнейшая отработка</t>
         </is>
       </c>
-      <c r="C551" s="691" t="inlineStr">
+      <c r="C518" s="691" t="inlineStr">
         <is>
           <t>Повышение качества подбора, снижение сроков</t>
         </is>
       </c>
-      <c r="D551" s="195" t="inlineStr">
+      <c r="D518" s="195" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В. </t>
         </is>
       </c>
-      <c r="E551" s="691" t="n"/>
-    </row>
-    <row r="552" ht="69" customHeight="1">
-      <c r="A552" s="691" t="inlineStr">
+      <c r="E518" s="691" t="n"/>
+    </row>
+    <row r="519" ht="69" customFormat="1" customHeight="1" s="38">
+      <c r="A519" s="691" t="inlineStr">
         <is>
           <t xml:space="preserve"> Хантфлоу</t>
         </is>
       </c>
-      <c r="B552" s="701" t="inlineStr">
+      <c r="B519" s="701" t="inlineStr">
         <is>
           <t>Ведение базы кандидатов, отслеживание воронки подбора.</t>
         </is>
       </c>
-      <c r="C552" s="182" t="inlineStr">
+      <c r="C519" s="182" t="inlineStr">
         <is>
           <t>Повышение качества подбора, снижение сроков</t>
         </is>
       </c>
-      <c r="D552" s="182" t="inlineStr">
+      <c r="D519" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -28060,25 +27481,25 @@
 Новикова Ю.</t>
         </is>
       </c>
-      <c r="E552" s="182" t="n"/>
-    </row>
-    <row r="553" ht="55.2" customHeight="1">
-      <c r="A553" s="691" t="inlineStr">
+      <c r="E519" s="182" t="n"/>
+    </row>
+    <row r="520" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A520" s="691" t="inlineStr">
         <is>
           <t>Аналитика резюме кандидатов. Работающих сотрудников, обновляющих резюме</t>
         </is>
       </c>
-      <c r="B553" s="184" t="inlineStr">
+      <c r="B520" s="184" t="inlineStr">
         <is>
           <t>Отслеживание баз резюме, аналитика</t>
         </is>
       </c>
-      <c r="C553" s="182" t="inlineStr">
+      <c r="C520" s="182" t="inlineStr">
         <is>
           <t>Удержание персонала</t>
         </is>
       </c>
-      <c r="D553" s="182" t="inlineStr">
+      <c r="D520" s="182" t="inlineStr">
         <is>
           <t>Шибалкова Ю. 
 Ковалева Е.
@@ -28086,273 +27507,273 @@
 Исматова В.</t>
         </is>
       </c>
-      <c r="E553" s="182" t="n"/>
-    </row>
-    <row r="554" ht="27.6" customHeight="1">
-      <c r="A554" s="691" t="inlineStr">
+      <c r="E520" s="182" t="n"/>
+    </row>
+    <row r="521" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A521" s="691" t="inlineStr">
         <is>
           <t>Бюджет 2027</t>
         </is>
       </c>
-      <c r="B554" s="184" t="inlineStr">
+      <c r="B521" s="184" t="inlineStr">
         <is>
           <t>Сбор информации</t>
         </is>
       </c>
-      <c r="C554" s="182" t="inlineStr">
+      <c r="C521" s="182" t="inlineStr">
         <is>
           <t>Планирование 2027, передача данных в финансовый блок</t>
         </is>
       </c>
-      <c r="D554" s="182" t="inlineStr">
+      <c r="D521" s="182" t="inlineStr">
         <is>
           <t>Пенский А.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E554" s="182" t="n"/>
-    </row>
-    <row r="555">
-      <c r="A555" s="825" t="inlineStr">
+      <c r="E521" s="182" t="n"/>
+    </row>
+    <row r="522" customFormat="1" s="38">
+      <c r="A522" s="825" t="inlineStr">
         <is>
           <t>Развитие и обучение</t>
         </is>
       </c>
-      <c r="B555" s="805" t="n"/>
-      <c r="C555" s="805" t="n"/>
-      <c r="D555" s="805" t="n"/>
-      <c r="E555" s="747" t="n"/>
-    </row>
-    <row r="556" ht="27.6" customHeight="1">
-      <c r="A556" s="370" t="inlineStr">
+      <c r="B522" s="805" t="n"/>
+      <c r="C522" s="805" t="n"/>
+      <c r="D522" s="805" t="n"/>
+      <c r="E522" s="747" t="n"/>
+    </row>
+    <row r="523" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A523" s="370" t="inlineStr">
         <is>
           <t>Актуализация процесса планирования обучения</t>
         </is>
       </c>
-      <c r="B556" s="370" t="inlineStr">
+      <c r="B523" s="370" t="inlineStr">
         <is>
           <t>подготовка к бюджетированию 2027</t>
         </is>
       </c>
-      <c r="C556" s="371" t="inlineStr">
+      <c r="C523" s="371" t="inlineStr">
         <is>
           <t xml:space="preserve">Развитие процессов </t>
         </is>
       </c>
-      <c r="D556" s="371" t="inlineStr">
+      <c r="D523" s="371" t="inlineStr">
         <is>
           <t>Пенский А., ОсиповаВ.</t>
         </is>
       </c>
-      <c r="E556" s="371" t="n"/>
-    </row>
-    <row r="557" ht="27.6" customHeight="1">
-      <c r="A557" s="417" t="inlineStr">
+      <c r="E523" s="371" t="n"/>
+    </row>
+    <row r="524" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A524" s="417" t="inlineStr">
         <is>
           <t>Разработка програаммы и Организация обучения кадрового резерва</t>
         </is>
       </c>
-      <c r="B557" s="417" t="inlineStr">
+      <c r="B524" s="417" t="inlineStr">
         <is>
           <t>повышение управленческих компетенций резервистов</t>
         </is>
       </c>
-      <c r="C557" s="418" t="inlineStr">
+      <c r="C524" s="418" t="inlineStr">
         <is>
           <t>развитие потенциала Компании</t>
         </is>
       </c>
-      <c r="D557" s="418" t="inlineStr">
+      <c r="D524" s="418" t="inlineStr">
         <is>
           <t>Пенский А., Осипова В.</t>
         </is>
       </c>
-      <c r="E557" s="418" t="n"/>
-    </row>
-    <row r="558">
-      <c r="A558" s="825" t="inlineStr">
+      <c r="E524" s="418" t="n"/>
+    </row>
+    <row r="525" customFormat="1" s="38">
+      <c r="A525" s="825" t="inlineStr">
         <is>
           <t>ЛНА и регламентация процессов</t>
         </is>
       </c>
-      <c r="B558" s="805" t="n"/>
-      <c r="C558" s="805" t="n"/>
-      <c r="D558" s="805" t="n"/>
-      <c r="E558" s="747" t="n"/>
-    </row>
-    <row r="559" ht="82.8" customHeight="1">
-      <c r="A559" s="691" t="inlineStr">
+      <c r="B525" s="805" t="n"/>
+      <c r="C525" s="805" t="n"/>
+      <c r="D525" s="805" t="n"/>
+      <c r="E525" s="747" t="n"/>
+    </row>
+    <row r="526" ht="82.8" customFormat="1" customHeight="1" s="38">
+      <c r="A526" s="691" t="inlineStr">
         <is>
           <t>ЛНА</t>
         </is>
       </c>
-      <c r="B559" s="701" t="inlineStr">
+      <c r="B526" s="701" t="inlineStr">
         <is>
           <t>Внедрение Положений об адаптации и наставничестве</t>
         </is>
       </c>
-      <c r="C559" s="181" t="inlineStr">
+      <c r="C526" s="181" t="inlineStr">
         <is>
           <t>Систематизация процесса, инструктирование руководителей.</t>
         </is>
       </c>
-      <c r="D559" s="181" t="inlineStr">
+      <c r="D526" s="181" t="inlineStr">
         <is>
           <t>Осипова В.</t>
         </is>
       </c>
-      <c r="E559" s="419" t="inlineStr">
+      <c r="E526" s="419" t="inlineStr">
         <is>
           <t>Участие в проработке системы мотивации для наставников, для утверждения в Положении об оплате труда
 По итогам 2 итерация нового процесса соглсования ЛНА по ГК - отработаны все замечания, переданы на 3 круг согласования</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" s="844" t="inlineStr">
+    <row r="527" customFormat="1" s="38">
+      <c r="A527" s="844" t="inlineStr">
         <is>
           <t>Корпоративные коммуникации</t>
         </is>
       </c>
-      <c r="B560" s="832" t="n"/>
-      <c r="C560" s="832" t="n"/>
-      <c r="D560" s="832" t="n"/>
-      <c r="E560" s="749" t="n"/>
-    </row>
-    <row r="561" ht="43.2" customHeight="1">
-      <c r="A561" s="390" t="inlineStr">
+      <c r="B527" s="832" t="n"/>
+      <c r="C527" s="832" t="n"/>
+      <c r="D527" s="832" t="n"/>
+      <c r="E527" s="749" t="n"/>
+    </row>
+    <row r="528" ht="43.2" customFormat="1" customHeight="1" s="38">
+      <c r="A528" s="390" t="inlineStr">
         <is>
           <t>Развитие каналов коммуникаций в компании</t>
         </is>
       </c>
-      <c r="B561" s="391" t="inlineStr">
+      <c r="B528" s="391" t="inlineStr">
         <is>
           <t>Использование текущих каналов и продвижение, предложения по развитию (почтовые рассылки, инфодоски, чаты)</t>
         </is>
       </c>
-      <c r="C561" s="392" t="inlineStr">
+      <c r="C528" s="392" t="inlineStr">
         <is>
           <t>Повышение качества коммуникаций и обмен новостями в компании</t>
         </is>
       </c>
-      <c r="D561" s="393" t="inlineStr">
+      <c r="D528" s="393" t="inlineStr">
         <is>
           <t>Котов И.
 Осипова В.</t>
         </is>
       </c>
-      <c r="E561" s="392" t="n"/>
-    </row>
-    <row r="562">
-      <c r="A562" s="374" t="inlineStr">
+      <c r="E528" s="392" t="n"/>
+    </row>
+    <row r="529" customFormat="1" s="38">
+      <c r="A529" s="374" t="inlineStr">
         <is>
           <t>Корпоративные рассылки и ТВ</t>
         </is>
       </c>
-      <c r="B562" s="394" t="inlineStr">
+      <c r="B529" s="394" t="inlineStr">
         <is>
           <t>Плановые и внеплановые коммуникации: дни рождения, выходы новых сотрудников, реферальная программа и другие инфоповоды</t>
         </is>
       </c>
-      <c r="C562" s="374" t="inlineStr">
+      <c r="C529" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D562" s="376" t="inlineStr">
+      <c r="D529" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E562" s="392" t="n"/>
-    </row>
-    <row r="563" ht="27.6" customHeight="1">
-      <c r="A563" s="374" t="inlineStr">
+      <c r="E529" s="392" t="n"/>
+    </row>
+    <row r="530" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A530" s="374" t="inlineStr">
         <is>
           <t>Настольный теннис ЛЧБ</t>
         </is>
       </c>
-      <c r="B563" s="395" t="inlineStr">
+      <c r="B530" s="395" t="inlineStr">
         <is>
           <t>Организация участия сотрудников в турнирах по настольному теннису, ведение информационной кампании</t>
         </is>
       </c>
-      <c r="C563" s="374" t="inlineStr">
+      <c r="C530" s="374" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D563" s="292" t="inlineStr">
+      <c r="D530" s="292" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.</t>
         </is>
       </c>
-      <c r="E563" s="397" t="n"/>
-    </row>
-    <row r="564">
-      <c r="A564" s="374" t="inlineStr">
+      <c r="E530" s="397" t="n"/>
+    </row>
+    <row r="531" customFormat="1" s="38">
+      <c r="A531" s="374" t="inlineStr">
         <is>
           <t>Волейбол</t>
         </is>
       </c>
-      <c r="B564" s="389" t="inlineStr">
+      <c r="B531" s="389" t="inlineStr">
         <is>
           <t>Освещение нового вида корпоративного спорта</t>
         </is>
       </c>
-      <c r="C564" s="374" t="inlineStr">
+      <c r="C531" s="374" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D564" s="376" t="inlineStr">
+      <c r="D531" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E564" s="390" t="n"/>
-    </row>
-    <row r="565">
-      <c r="A565" s="374" t="inlineStr">
+      <c r="E531" s="390" t="n"/>
+    </row>
+    <row r="532" customFormat="1" s="38">
+      <c r="A532" s="374" t="inlineStr">
         <is>
           <t>Видео-контент</t>
         </is>
       </c>
-      <c r="B565" s="395" t="inlineStr">
+      <c r="B532" s="395" t="inlineStr">
         <is>
           <t>Съёмка, монтаж и озвучка корпоративных роликов: фильмы, интервью, ОТ, мероприятия</t>
         </is>
       </c>
-      <c r="C565" s="374" t="inlineStr">
+      <c r="C532" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D565" s="376" t="inlineStr">
+      <c r="D532" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E565" s="390" t="n"/>
-    </row>
-    <row r="566">
-      <c r="A566" s="374" t="inlineStr">
+      <c r="E532" s="390" t="n"/>
+    </row>
+    <row r="533" customFormat="1" s="38">
+      <c r="A533" s="374" t="inlineStr">
         <is>
           <t>Детские новогодние подарки</t>
         </is>
       </c>
-      <c r="B566" s="395" t="inlineStr">
+      <c r="B533" s="395" t="inlineStr">
         <is>
           <t>Раздача детских подарков для сотрудников</t>
         </is>
       </c>
-      <c r="C566" s="374" t="inlineStr">
+      <c r="C533" s="374" t="inlineStr">
         <is>
           <t>Нематериальная мотивация, поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D566" s="376" t="inlineStr">
+      <c r="D533" s="376" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.
@@ -28362,25 +27783,25 @@
 Шибалкова Ю.</t>
         </is>
       </c>
-      <c r="E566" s="390" t="n"/>
-    </row>
-    <row r="567" ht="55.2" customHeight="1">
-      <c r="A567" s="290" t="inlineStr">
+      <c r="E533" s="390" t="n"/>
+    </row>
+    <row r="534" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A534" s="290" t="inlineStr">
         <is>
           <t>Горящие вакансии</t>
         </is>
       </c>
-      <c r="B567" s="290" t="inlineStr">
+      <c r="B534" s="290" t="inlineStr">
         <is>
           <t>Ежемесячная информационная кампания</t>
         </is>
       </c>
-      <c r="C567" s="290" t="inlineStr">
+      <c r="C534" s="290" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций, распространение активных вакансий</t>
         </is>
       </c>
-      <c r="D567" s="292" t="inlineStr">
+      <c r="D534" s="292" t="inlineStr">
         <is>
           <t xml:space="preserve">Осипова В.
    Котов И.
@@ -28388,342 +27809,331 @@
 </t>
         </is>
       </c>
-      <c r="E567" s="290" t="n"/>
-    </row>
-    <row r="568" ht="33.9" customHeight="1">
-      <c r="A568" s="374" t="inlineStr">
+      <c r="E534" s="290" t="n"/>
+    </row>
+    <row r="535" ht="33.9" customFormat="1" customHeight="1" s="38">
+      <c r="A535" s="374" t="inlineStr">
         <is>
           <t>Корпоративный портал</t>
         </is>
       </c>
-      <c r="B568" s="455" t="inlineStr">
+      <c r="B535" s="455" t="inlineStr">
         <is>
           <t>Развитие корпоративного портала, добавление новых функций, администрирование</t>
         </is>
       </c>
-      <c r="C568" s="374" t="inlineStr">
+      <c r="C535" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций, распространение активных вакансий</t>
         </is>
       </c>
-      <c r="D568" s="376" t="inlineStr">
+      <c r="D535" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E568" s="390" t="n"/>
-    </row>
-    <row r="569" ht="28.8" customHeight="1">
-      <c r="A569" s="374" t="inlineStr">
+      <c r="E535" s="390" t="n"/>
+    </row>
+    <row r="536" ht="28.8" customFormat="1" customHeight="1" s="38">
+      <c r="A536" s="374" t="inlineStr">
         <is>
           <t>Тайный санта</t>
         </is>
       </c>
-      <c r="B569" s="455" t="inlineStr">
+      <c r="B536" s="455" t="inlineStr">
         <is>
           <t>Проведение корпоративной игры среди сотрудников</t>
         </is>
       </c>
-      <c r="C569" s="374" t="inlineStr">
+      <c r="C536" s="374" t="inlineStr">
         <is>
           <t>Нематериальная мотивация, поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D569" s="376" t="inlineStr">
+      <c r="D536" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E569" s="390" t="n"/>
-    </row>
-    <row r="570" ht="55.2" customHeight="1">
-      <c r="A570" s="845" t="inlineStr">
+      <c r="E536" s="390" t="n"/>
+    </row>
+    <row r="537" ht="55.2" customFormat="1" customHeight="1" s="38">
+      <c r="A537" s="845" t="inlineStr">
         <is>
           <t>Поздравления с ДР сотрудников</t>
         </is>
       </c>
-      <c r="B570" s="290" t="inlineStr">
+      <c r="B537" s="290" t="inlineStr">
         <is>
           <t xml:space="preserve">Актуализация списков именинников на будущий месяц, сбор фотографий для поздравлений. Сбор/отправка в филиалы подарков на ДР для сотрудников </t>
         </is>
       </c>
-      <c r="C570" s="290" t="inlineStr">
+      <c r="C537" s="290" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D570" s="292" t="inlineStr">
+      <c r="D537" s="292" t="inlineStr">
         <is>
           <t xml:space="preserve">Котов И.
 </t>
         </is>
       </c>
-      <c r="E570" s="290" t="n"/>
-    </row>
-    <row r="571" ht="27.6" customHeight="1">
-      <c r="A571" s="754" t="n"/>
-      <c r="B571" s="290" t="inlineStr">
+      <c r="E537" s="290" t="n"/>
+    </row>
+    <row r="538" ht="27.6" customFormat="1" customHeight="1" s="38">
+      <c r="A538" s="754" t="n"/>
+      <c r="B538" s="290" t="inlineStr">
         <is>
           <t>Составление, подписание приказов, списков, ведомостей, договоров дарения на подарки</t>
         </is>
       </c>
-      <c r="C571" s="290" t="inlineStr">
+      <c r="C538" s="290" t="inlineStr">
         <is>
           <t>Поддержание корп. культуры</t>
         </is>
       </c>
-      <c r="D571" s="292" t="n"/>
-      <c r="E571" s="290" t="n"/>
-    </row>
-    <row r="572">
-      <c r="A572" s="753" t="n"/>
-      <c r="B572" s="387" t="inlineStr">
+      <c r="D538" s="292" t="n"/>
+      <c r="E538" s="290" t="n"/>
+    </row>
+    <row r="539" customFormat="1" s="38">
+      <c r="A539" s="753" t="n"/>
+      <c r="B539" s="387" t="inlineStr">
         <is>
           <t>Выдача подарков сотрудникам</t>
         </is>
       </c>
-      <c r="C572" s="387" t="n"/>
-      <c r="D572" s="388" t="inlineStr">
+      <c r="C539" s="387" t="n"/>
+      <c r="D539" s="388" t="inlineStr">
         <is>
           <t>Исматова В.</t>
         </is>
       </c>
-      <c r="E572" s="387" t="n"/>
-    </row>
-    <row r="573">
-      <c r="A573" s="374" t="inlineStr">
+      <c r="E539" s="387" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="374" t="inlineStr">
         <is>
           <t>Кадровый резерв</t>
         </is>
       </c>
-      <c r="B573" s="395" t="inlineStr">
+      <c r="B540" s="395" t="inlineStr">
         <is>
           <t>Разработка плана коммуникаций и освещение программы на портале и в чатах</t>
         </is>
       </c>
-      <c r="C573" s="374" t="inlineStr">
+      <c r="C540" s="374" t="inlineStr">
         <is>
           <t>Развитие корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D573" s="376" t="inlineStr">
+      <c r="D540" s="376" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.</t>
         </is>
       </c>
-      <c r="E573" s="390" t="n"/>
-    </row>
-    <row r="574">
-      <c r="A574" s="374" t="inlineStr">
+      <c r="E540" s="390" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="374" t="inlineStr">
         <is>
           <t>ИИ-вебинар</t>
         </is>
       </c>
-      <c r="B574" s="395" t="inlineStr">
+      <c r="B541" s="395" t="inlineStr">
         <is>
           <t>Освещение ИИ-вебинара для сотрудников ГК</t>
         </is>
       </c>
-      <c r="C574" s="374" t="inlineStr">
+      <c r="C541" s="374" t="inlineStr">
         <is>
           <t>Развитие корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D574" s="376" t="inlineStr">
+      <c r="D541" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E574" s="390" t="n"/>
-    </row>
-    <row r="575">
-      <c r="A575" s="374" t="inlineStr">
+      <c r="E541" s="390" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="374" t="inlineStr">
         <is>
           <t>КЭДО</t>
         </is>
       </c>
-      <c r="B575" s="395" t="inlineStr">
+      <c r="B542" s="395" t="inlineStr">
         <is>
           <t>Освещение КЭДО для сотрудников, унификация инструкций и загрузка на портал</t>
         </is>
       </c>
-      <c r="C575" s="374" t="inlineStr">
+      <c r="C542" s="374" t="inlineStr">
         <is>
           <t>Поддержание корпоративных коммуникаций</t>
         </is>
       </c>
-      <c r="D575" s="376" t="inlineStr">
+      <c r="D542" s="376" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E575" s="390" t="n"/>
-    </row>
-    <row r="576" ht="27.6" customHeight="1">
-      <c r="A576" s="290" t="inlineStr">
+      <c r="E542" s="390" t="n"/>
+    </row>
+    <row r="543" ht="27.6" customHeight="1">
+      <c r="A543" s="290" t="inlineStr">
         <is>
           <t>Видео-экскурсия по ГК</t>
         </is>
       </c>
-      <c r="B576" s="290" t="inlineStr">
+      <c r="B543" s="290" t="inlineStr">
         <is>
           <t>планирование нового элемента адаптации сотрудников</t>
         </is>
       </c>
-      <c r="C576" s="290" t="inlineStr">
+      <c r="C543" s="290" t="inlineStr">
         <is>
           <t>Развитие корп. Культуры</t>
         </is>
       </c>
-      <c r="D576" s="292" t="inlineStr">
+      <c r="D543" s="292" t="inlineStr">
         <is>
           <t>Котов И.
    Осипова В.</t>
         </is>
       </c>
-      <c r="E576" s="290" t="n"/>
-    </row>
-    <row r="577">
-      <c r="A577" s="290" t="inlineStr">
+      <c r="E543" s="290" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="290" t="inlineStr">
         <is>
           <t>Корпоративный помощник</t>
         </is>
       </c>
-      <c r="B577" s="290" t="inlineStr">
+      <c r="B544" s="290" t="inlineStr">
         <is>
           <t>проект по внедрению ИИ</t>
         </is>
       </c>
-      <c r="C577" s="290" t="inlineStr">
+      <c r="C544" s="290" t="inlineStr">
         <is>
           <t>развитие ИИ в ГК</t>
         </is>
       </c>
-      <c r="D577" s="292" t="inlineStr">
+      <c r="D544" s="292" t="inlineStr">
         <is>
           <t>Котов И.</t>
         </is>
       </c>
-      <c r="E577" s="290" t="n"/>
+      <c r="E544" s="290" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="116">
+  <mergeCells count="105">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A402:E402"/>
-    <mergeCell ref="A389"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A216:E216"/>
     <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A387:E387"/>
-    <mergeCell ref="A346:A349"/>
-    <mergeCell ref="A531:A532"/>
     <mergeCell ref="A236:A237"/>
     <mergeCell ref="C236:C237"/>
-    <mergeCell ref="A516:E516"/>
     <mergeCell ref="A54:A59"/>
     <mergeCell ref="A208:E208"/>
-    <mergeCell ref="A484:E484"/>
     <mergeCell ref="A219:A220"/>
-    <mergeCell ref="A499:E499"/>
+    <mergeCell ref="A376:E376"/>
+    <mergeCell ref="A443:E443"/>
+    <mergeCell ref="A415:E415"/>
     <mergeCell ref="A247:E247"/>
     <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A342:A345"/>
+    <mergeCell ref="A483:E483"/>
     <mergeCell ref="A190:A191"/>
-    <mergeCell ref="C405:C406"/>
-    <mergeCell ref="A470:E470"/>
+    <mergeCell ref="A356"/>
     <mergeCell ref="A165:E165"/>
     <mergeCell ref="A299:E299"/>
     <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A368:A371"/>
     <mergeCell ref="A261:E261"/>
     <mergeCell ref="A70:A71"/>
     <mergeCell ref="A284:E284"/>
-    <mergeCell ref="A489:A493"/>
-    <mergeCell ref="A435:A437"/>
-    <mergeCell ref="A560:E560"/>
-    <mergeCell ref="A547:A548"/>
+    <mergeCell ref="A496:E496"/>
+    <mergeCell ref="A430:E430"/>
+    <mergeCell ref="A345:A346"/>
     <mergeCell ref="A289:A293"/>
+    <mergeCell ref="A354:E354"/>
     <mergeCell ref="A246:E246"/>
-    <mergeCell ref="A409:E409"/>
-    <mergeCell ref="A418:E418"/>
+    <mergeCell ref="A522:E522"/>
+    <mergeCell ref="A369:E369"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A405:A406"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A393:E393"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="A253:A254"/>
     <mergeCell ref="A68:A69"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A451:E451"/>
     <mergeCell ref="A274:E274"/>
     <mergeCell ref="A161:E161"/>
     <mergeCell ref="C68:C69"/>
-    <mergeCell ref="A550:E550"/>
+    <mergeCell ref="C372:C373"/>
+    <mergeCell ref="A525:E525"/>
     <mergeCell ref="E68:E69"/>
-    <mergeCell ref="A335:A341"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="A536:E536"/>
-    <mergeCell ref="A378:A379"/>
+    <mergeCell ref="A456:A460"/>
+    <mergeCell ref="A432:E432"/>
+    <mergeCell ref="A537:A539"/>
+    <mergeCell ref="C514:C515"/>
+    <mergeCell ref="A437:E437"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="A511:E511"/>
+    <mergeCell ref="A360:E360"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A463:E463"/>
-    <mergeCell ref="A358:A367"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="A447:E447"/>
     <mergeCell ref="D68:D69"/>
-    <mergeCell ref="A425:E425"/>
+    <mergeCell ref="A385:E385"/>
     <mergeCell ref="A223:E223"/>
     <mergeCell ref="C70:C71"/>
-    <mergeCell ref="A465:E465"/>
     <mergeCell ref="C219:C220"/>
-    <mergeCell ref="A317:A322"/>
-    <mergeCell ref="A331:A334"/>
-    <mergeCell ref="A570:A572"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="D236:D237"/>
     <mergeCell ref="A278:E278"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A449:E449"/>
     <mergeCell ref="A175:A180"/>
-    <mergeCell ref="C547:C548"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A263:E263"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A350:A356"/>
     <mergeCell ref="A199:E199"/>
     <mergeCell ref="A372:A373"/>
-    <mergeCell ref="A323:A328"/>
-    <mergeCell ref="A455:A456"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="A169:E169"/>
-    <mergeCell ref="A555:E555"/>
-    <mergeCell ref="A476:E476"/>
+    <mergeCell ref="A527:E527"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A422:A423"/>
     <mergeCell ref="A133:A134"/>
+    <mergeCell ref="A517:E517"/>
     <mergeCell ref="A227:E227"/>
     <mergeCell ref="C133:C134"/>
+    <mergeCell ref="A487:A488"/>
     <mergeCell ref="A268:E268"/>
     <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A448:E448"/>
     <mergeCell ref="A145:E145"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A503:E503"/>
+    <mergeCell ref="A341:E341"/>
+    <mergeCell ref="A514:A515"/>
+    <mergeCell ref="A402:A404"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A374:E374"/>
-    <mergeCell ref="A558:E558"/>
     <mergeCell ref="A96:A97"/>
     <mergeCell ref="A414:E414"/>
     <mergeCell ref="C96:C97"/>
     <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A529:E529"/>
-    <mergeCell ref="A329:A330"/>
+    <mergeCell ref="A466:E466"/>
+    <mergeCell ref="A416:E416"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A544:E544"/>
+    <mergeCell ref="A392:E392"/>
     <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A480:E480"/>
     <mergeCell ref="A245:E245"/>
   </mergeCells>
   <hyperlinks>
